--- a/web/app/spreadsheet_templates/students_export_template.xlsx
+++ b/web/app/spreadsheet_templates/students_export_template.xlsx
@@ -7,10 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Tentang Ekspor" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="instructions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="students" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="classes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'instructions'!$A$1:$H$48</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
 </file>
@@ -142,7 +145,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -358,6 +361,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFEFCFD2"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFEFCFD2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFEFCFD2"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFEFCFD2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -369,7 +401,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -508,6 +540,41 @@
     </xf>
     <xf numFmtId="49" fontId="5" fillId="8" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="8" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="8" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -664,15 +731,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="StudentsExportTable" displayName="StudentsExportTable" ref="A1:F2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:F2"/>
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="StudentsExportTable" displayName="StudentsExportTable" ref="A1:H2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:H2"/>
+  <tableColumns count="8">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="NAMA"/>
-    <tableColumn id="3" name="ID KELAS"/>
-    <tableColumn id="4" name="NISN"/>
-    <tableColumn id="5" name="STATUS"/>
-    <tableColumn id="6" name="NOMOR WALI"/>
+    <tableColumn id="3" name="NISN"/>
+    <tableColumn id="4" name="STATUS"/>
+    <tableColumn id="5" name="NOMOR WALI"/>
+    <tableColumn id="6" name="JENJANG"/>
+    <tableColumn id="7" name="NAMA KELAS"/>
+    <tableColumn id="8" name="ID KELAS"/>
+  </tableColumns>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClassesExportTable" displayName="ClassesExportTable" ref="A1:C2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:C2"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="ID KELAS"/>
+    <tableColumn id="2" name="JENJANG"/>
+    <tableColumn id="3" name="NAMA KELAS"/>
   </tableColumns>
 </table>
 </file>
@@ -853,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.7578125" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3.42" customWidth="1" style="21" min="1" max="1"/>
@@ -876,7 +956,7 @@
       <c r="A2" s="23" t="n"/>
       <c r="B2" s="24" t="inlineStr">
         <is>
-          <t>Ekspor &amp; Impor Data Siswa</t>
+          <t>Ekspor &amp; Impor Siswa dan Kelas</t>
         </is>
       </c>
       <c r="G2" s="25" t="inlineStr">
@@ -914,7 +994,7 @@
       <c r="A5" s="23" t="n"/>
       <c r="B5" s="29" t="inlineStr">
         <is>
-          <t>Template ekspor dan impor untuk mengedit data lama atau membuat data baru.</t>
+          <t>Workbook ini dibuat oleh Absensa untuk ekspor serta penyuntingan massal dan impor kembali.</t>
         </is>
       </c>
     </row>
@@ -982,7 +1062,7 @@
       <c r="C9" s="26" t="n"/>
       <c r="D9" s="32" t="inlineStr">
         <is>
-          <t>students</t>
+          <t>students dan classes</t>
         </is>
       </c>
       <c r="E9" s="28" t="n"/>
@@ -1000,7 +1080,7 @@
       <c r="C10" s="26" t="n"/>
       <c r="D10" s="33" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>ID siswa dan ID KELAS (dilindungi)</t>
         </is>
       </c>
       <c r="E10" s="28" t="n"/>
@@ -1018,11 +1098,11 @@
       <c r="G11" s="23" t="n"/>
       <c r="H11" s="23" t="n"/>
     </row>
-    <row r="12" ht="23" customHeight="1" s="22">
+    <row r="12" ht="24" customHeight="1" s="22">
       <c r="A12" s="23" t="n"/>
-      <c r="B12" s="27" t="inlineStr">
-        <is>
-          <t>Mengedit atau menambah data</t>
+      <c r="B12" s="53" t="inlineStr">
+        <is>
+          <t>Isi workbook</t>
         </is>
       </c>
       <c r="C12" s="28" t="n"/>
@@ -1032,21 +1112,17 @@
       <c r="G12" s="28" t="n"/>
       <c r="H12" s="26" t="n"/>
     </row>
-    <row r="13" ht="34" customHeight="1" s="22">
+    <row r="13" ht="62" customHeight="1" s="22">
       <c r="A13" s="23" t="n"/>
       <c r="B13" s="29" t="inlineStr">
         <is>
-          <t>1. Edit data yang sudah ada: ubah kolom yang diperlukan dan pertahankan ID aslinya.</t>
+          <t>students berisi data siswa sesuai filter ekspor di atas. classes selalu berisi seluruh kelas dari semua jenjang, tanpa mengikuti filter siswa, dan menjadi sumber pilihan dropdown.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1" s="22">
       <c r="A14" s="23" t="n"/>
-      <c r="B14" s="29" t="inlineStr">
-        <is>
-          <t>2. Buat siswa baru: isi baris kosong di bawah data terakhir dan biarkan ID kosong.</t>
-        </is>
-      </c>
+      <c r="B14" s="29" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1" s="22">
       <c r="A15" s="23" t="n"/>
@@ -1058,11 +1134,11 @@
       <c r="G15" s="23" t="n"/>
       <c r="H15" s="23" t="n"/>
     </row>
-    <row r="16" ht="23" customHeight="1" s="22">
+    <row r="16" ht="24" customHeight="1" s="22">
       <c r="A16" s="23" t="n"/>
-      <c r="B16" s="27" t="inlineStr">
-        <is>
-          <t>Sebelum mengimpor</t>
+      <c r="B16" s="53" t="inlineStr">
+        <is>
+          <t>Jangan mengubah identitas</t>
         </is>
       </c>
       <c r="C16" s="28" t="n"/>
@@ -1072,33 +1148,23 @@
       <c r="G16" s="28" t="n"/>
       <c r="H16" s="26" t="n"/>
     </row>
-    <row r="17" ht="34" customHeight="1" s="22">
+    <row r="17" ht="62" customHeight="1" s="22">
       <c r="A17" s="23" t="n"/>
-      <c r="B17" s="34" t="inlineStr">
-        <is>
-          <t>1. Jangan mengubah nama sheet atau judul kolom. Baris kosong bukan data baru.</t>
-        </is>
-      </c>
-      <c r="C17" s="35" t="n"/>
-      <c r="D17" s="35" t="n"/>
-      <c r="E17" s="35" t="n"/>
-      <c r="F17" s="35" t="n"/>
-      <c r="G17" s="35" t="n"/>
-      <c r="H17" s="36" t="n"/>
+      <c r="B17" s="62" t="inlineStr">
+        <is>
+          <t>Jangan mengganti nama sheet atau judul kolom. ID siswa mengidentifikasi siswa; ID KELAS mengidentifikasi kelas. ID dilindungi dan tidak boleh diubah. Di students, ID kelas disembunyikan sebagai metadata internal; Anda tidak perlu mengetahui atau mengeditnya.</t>
+        </is>
+      </c>
+      <c r="C17" s="63" t="n"/>
+      <c r="D17" s="63" t="n"/>
+      <c r="E17" s="63" t="n"/>
+      <c r="F17" s="63" t="n"/>
+      <c r="G17" s="63" t="n"/>
+      <c r="H17" s="64" t="n"/>
     </row>
     <row r="18" ht="34" customHeight="1" s="22">
       <c r="A18" s="23" t="n"/>
-      <c r="B18" s="34" t="inlineStr">
-        <is>
-          <t>2. Simpan sebagai .xlsx. ID terisi untuk pembaruan; ID kosong untuk pembuatan data.</t>
-        </is>
-      </c>
-      <c r="C18" s="35" t="n"/>
-      <c r="D18" s="35" t="n"/>
-      <c r="E18" s="35" t="n"/>
-      <c r="F18" s="35" t="n"/>
-      <c r="G18" s="35" t="n"/>
-      <c r="H18" s="36" t="n"/>
+      <c r="B18" s="34" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1" s="22">
       <c r="A19" s="23" t="n"/>
@@ -1110,11 +1176,11 @@
       <c r="G19" s="23" t="n"/>
       <c r="H19" s="23" t="n"/>
     </row>
-    <row r="20" ht="23" customHeight="1" s="22">
+    <row r="20" ht="24" customHeight="1" s="22">
       <c r="A20" s="23" t="n"/>
-      <c r="B20" s="27" t="inlineStr">
-        <is>
-          <t>Mengisi baris baru</t>
+      <c r="B20" s="53" t="inlineStr">
+        <is>
+          <t>Menentukan kelas siswa</t>
         </is>
       </c>
       <c r="C20" s="28" t="n"/>
@@ -1124,29 +1190,22 @@
       <c r="G20" s="28" t="n"/>
       <c r="H20" s="26" t="n"/>
     </row>
-    <row r="21" ht="64" customHeight="1" s="22">
+    <row r="21" ht="62" customHeight="1" s="22">
       <c r="A21" s="23" t="n"/>
-      <c r="B21" s="37" t="inlineStr">
-        <is>
-          <t>Validasi tersedia sampai baris terakhir sheet. NISN: tepat 10 digit (termasuk nol di depan). STATUS: pilih Aktif atau Tidak aktif. ID KELAS boleh kosong jika belum memiliki kelas. NOMOR WALI opsional: angka saja, diawali 08 atau 628, maksimal 32 digit. Isi langsung pada baris kosong; saat menyalin data, tempel nilai saja agar format dan validasi tetap terjaga.</t>
-        </is>
-      </c>
-      <c r="C21" s="38" t="n"/>
-      <c r="D21" s="38" t="n"/>
-      <c r="E21" s="38" t="n"/>
-      <c r="F21" s="38" t="n"/>
-      <c r="G21" s="38" t="n"/>
-      <c r="H21" s="39" t="n"/>
+      <c r="B21" s="65" t="inlineStr">
+        <is>
+          <t>Di students, pilih JENJANG dan NAMA KELAS melalui dropdown. Pilihan berasal dari classes. Untuk siswa baru, keduanya wajib diisi dan kelas harus tercantum pada classes. Untuk siswa lama, kosongkan kedua nilai jika ingin melepas kelas. Nilai yang hanya terisi sebagian ditolak.</t>
+        </is>
+      </c>
+      <c r="C21" s="41" t="n"/>
+      <c r="D21" s="41" t="n"/>
+      <c r="E21" s="41" t="n"/>
+      <c r="F21" s="41" t="n"/>
+      <c r="G21" s="41" t="n"/>
+      <c r="H21" s="42" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1" s="22">
       <c r="A22" s="23" t="n"/>
-      <c r="B22" s="40" t="n"/>
-      <c r="C22" s="41" t="n"/>
-      <c r="D22" s="41" t="n"/>
-      <c r="E22" s="41" t="n"/>
-      <c r="F22" s="41" t="n"/>
-      <c r="G22" s="41" t="n"/>
-      <c r="H22" s="42" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1" s="22">
       <c r="A23" s="23" t="n"/>
@@ -1158,40 +1217,161 @@
       <c r="G23" s="23" t="n"/>
       <c r="H23" s="23" t="n"/>
     </row>
-    <row r="24" ht="15" customHeight="1" s="22">
+    <row r="24" ht="24" customHeight="1" s="22">
       <c r="A24" s="23" t="n"/>
-      <c r="B24" s="43" t="n"/>
-      <c r="C24" s="43" t="n"/>
-      <c r="D24" s="43" t="n"/>
-      <c r="E24" s="43" t="n"/>
-      <c r="F24" s="43" t="n"/>
-      <c r="G24" s="43" t="n"/>
-      <c r="H24" s="43" t="n"/>
+      <c r="B24" s="53" t="inlineStr">
+        <is>
+          <t>Membuat kelas hanya melalui classes</t>
+        </is>
+      </c>
+      <c r="C24" s="28" t="n"/>
+      <c r="D24" s="28" t="n"/>
+      <c r="E24" s="28" t="n"/>
+      <c r="F24" s="28" t="n"/>
+      <c r="G24" s="28" t="n"/>
+      <c r="H24" s="26" t="n"/>
+    </row>
+    <row r="25" ht="74" customHeight="1" s="22">
+      <c r="B25" s="29" t="inlineStr">
+        <is>
+          <t>Tambahkan baris pada classes dengan ID KELAS kosong, lalu isi JENJANG dan NAMA KELAS. Siswa dapat merujuk pasangan itu dalam impor yang sama. Satu kelas baru akan dipakai bersama oleh semua siswa yang merujuknya. Salah ketik pada students tidak akan membuat kelas baru.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1" s="22">
+      <c r="B28" s="53" t="inlineStr">
+        <is>
+          <t>Mengganti nama atau jenjang kelas</t>
+        </is>
+      </c>
+      <c r="C28" s="28" t="n"/>
+      <c r="D28" s="28" t="n"/>
+      <c r="E28" s="28" t="n"/>
+      <c r="F28" s="28" t="n"/>
+      <c r="G28" s="28" t="n"/>
+      <c r="H28" s="26" t="n"/>
+    </row>
+    <row r="29" ht="86" customHeight="1" s="22">
+      <c r="B29" s="29" t="inlineStr">
+        <is>
+          <t>Edit JENJANG dan/atau NAMA KELAS pada classes dengan mempertahankan ID yang dilindungi. Contoh: 10 / IPA 1 menjadi 10 / IPA A. Siswa tetap mengikuti kelas yang sama meskipun nilai lama di students belum diedit; tidak perlu mengubah setiap siswa. Untuk memindahkan siswa, ubah pasangan jenjang dan nama kelasnya ke kelas lain yang tercantum pada classes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1" s="22">
+      <c r="B32" s="53" t="inlineStr">
+        <is>
+          <t>Menghapus baris BUKAN menghapus kelas</t>
+        </is>
+      </c>
+      <c r="C32" s="28" t="n"/>
+      <c r="D32" s="28" t="n"/>
+      <c r="E32" s="28" t="n"/>
+      <c r="F32" s="28" t="n"/>
+      <c r="G32" s="28" t="n"/>
+      <c r="H32" s="26" t="n"/>
+    </row>
+    <row r="33" ht="62" customHeight="1" s="22">
+      <c r="B33" s="29" t="inlineStr">
+        <is>
+          <t>Menghapus baris kelas hanya menghapusnya dari workbook dan pilihan kelasnya, bukan dari Absensa. Siswa yang masih merujuk kelas tersebut perlu disesuaikan atau baris kelas dikembalikan. Penghapusan kelas dari database dilakukan secara eksplisit melalui halaman/dashboard Kelas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1" s="22">
+      <c r="B36" s="53" t="inlineStr">
+        <is>
+          <t>Impor bersifat semua-atau-tidak-sama-sekali</t>
+        </is>
+      </c>
+      <c r="C36" s="28" t="n"/>
+      <c r="D36" s="28" t="n"/>
+      <c r="E36" s="28" t="n"/>
+      <c r="F36" s="28" t="n"/>
+      <c r="G36" s="28" t="n"/>
+      <c r="H36" s="26" t="n"/>
+    </row>
+    <row r="37" ht="62" customHeight="1" s="22">
+      <c r="B37" s="29" t="inlineStr">
+        <is>
+          <t>Absensa memvalidasi seluruh workbook sebelum menyimpan apa pun. Jika satu baris saja salah, seluruh impor ditolak: tidak ada siswa yang diubah dan tidak ada kelas yang diubah atau dibuat. Perbaiki semua kesalahan yang dilaporkan, lalu impor kembali.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1" s="22">
+      <c r="B40" s="53" t="inlineStr">
+        <is>
+          <t>Mengisi data siswa</t>
+        </is>
+      </c>
+      <c r="C40" s="28" t="n"/>
+      <c r="D40" s="28" t="n"/>
+      <c r="E40" s="28" t="n"/>
+      <c r="F40" s="28" t="n"/>
+      <c r="G40" s="28" t="n"/>
+      <c r="H40" s="26" t="n"/>
+    </row>
+    <row r="41" ht="62" customHeight="1" s="22">
+      <c r="B41" s="29" t="inlineStr">
+        <is>
+          <t>Pertahankan ID siswa untuk pembaruan; kosongkan ID untuk siswa baru. NISN wajib tepat 10 digit dan disimpan sebagai teks agar nol di depan tidak hilang. STATUS: Aktif atau Tidak aktif. NOMOR WALI opsional, angka saja diawali 08 atau 628, maksimal 32 digit. Baris kosong diabaikan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="24" customHeight="1" s="22">
+      <c r="B44" s="53" t="inlineStr">
+        <is>
+          <t>Pilihan Excel dan baris baru</t>
+        </is>
+      </c>
+      <c r="C44" s="28" t="n"/>
+      <c r="D44" s="28" t="n"/>
+      <c r="E44" s="28" t="n"/>
+      <c r="F44" s="28" t="n"/>
+      <c r="G44" s="28" t="n"/>
+      <c r="H44" s="26" t="n"/>
+    </row>
+    <row r="45" ht="86" customHeight="1" s="22">
+      <c r="B45" s="29" t="inlineStr">
+        <is>
+          <t>Dropdown memakai jenjang dan nama kelas dari classes saat file dibuat. Jika kelas baru belum muncul di pilihan, ketik nilainya setelah menambahkannya pada classes. Kombinasi jenjang dan nama kelas harus unik; jenjang 1–20 dan nama maksimal 20 karakter. Kolom data dapat diedit; ID dan metadata dilindungi. Tersedia 100 baris entri kosong. Simpan sebagai .xlsx tanpa makro.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="32">
+    <mergeCell ref="B40:H40"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="D10:H10"/>
+    <mergeCell ref="B24:H24"/>
+    <mergeCell ref="B33:H33"/>
     <mergeCell ref="B5:H5"/>
     <mergeCell ref="B20:H20"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="B32:H32"/>
     <mergeCell ref="D6:H6"/>
+    <mergeCell ref="B41:H41"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="B16:H16"/>
+    <mergeCell ref="B25:H25"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="D7:H7"/>
-    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="B21:H21"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B12:H12"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="D9:H9"/>
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B14:H14"/>
     <mergeCell ref="D8:H8"/>
     <mergeCell ref="B17:H17"/>
     <mergeCell ref="B13:H13"/>
-    <mergeCell ref="B21:H22"/>
+    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="B29:H29"/>
+    <mergeCell ref="B37:H37"/>
+    <mergeCell ref="B28:H28"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1206,15 +1386,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F102"/>
+  <dimension ref="A1:H102"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.7578125" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14.76" customWidth="1" style="44" min="1" max="1"/>
     <col width="38.6" customWidth="1" style="21" min="2" max="2"/>
-    <col width="15.89" customWidth="1" style="44" min="3" max="3"/>
-    <col width="20.43" customWidth="1" style="45" min="4" max="4"/>
-    <col width="15.89" customWidth="1" style="45" min="5" max="5"/>
-    <col width="28.38" customWidth="1" style="45" min="6" max="6"/>
+    <col width="20.43" customWidth="1" style="45" min="3" max="3"/>
+    <col width="15.89" customWidth="1" style="45" min="4" max="4"/>
+    <col width="28.38" customWidth="1" style="45" min="5" max="5"/>
+    <col width="15.89" customWidth="1" style="22" min="6" max="6"/>
+    <col width="34.06" customWidth="1" style="22" min="7" max="7"/>
+    <col hidden="1" width="15.89" customWidth="1" style="44" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1" s="22">
@@ -1230,832 +1412,1044 @@
       </c>
       <c r="C1" s="47" t="inlineStr">
         <is>
+          <t>NISN</t>
+        </is>
+      </c>
+      <c r="D1" s="47" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="E1" s="48" t="inlineStr">
+        <is>
+          <t>NOMOR WALI</t>
+        </is>
+      </c>
+      <c r="F1" s="48" t="inlineStr">
+        <is>
+          <t>JENJANG</t>
+        </is>
+      </c>
+      <c r="G1" s="48" t="inlineStr">
+        <is>
+          <t>NAMA KELAS</t>
+        </is>
+      </c>
+      <c r="H1" s="47" t="inlineStr">
+        <is>
           <t>ID KELAS</t>
-        </is>
-      </c>
-      <c r="D1" s="47" t="inlineStr">
-        <is>
-          <t>NISN</t>
-        </is>
-      </c>
-      <c r="E1" s="47" t="inlineStr">
-        <is>
-          <t>STATUS</t>
-        </is>
-      </c>
-      <c r="F1" s="48" t="inlineStr">
-        <is>
-          <t>NOMOR WALI</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" s="22">
       <c r="A2" s="49" t="n"/>
       <c r="B2" s="50" t="n"/>
-      <c r="C2" s="51" t="n"/>
+      <c r="C2" s="52" t="n"/>
       <c r="D2" s="52" t="n"/>
       <c r="E2" s="52" t="n"/>
-      <c r="F2" s="52" t="n"/>
+      <c r="F2" s="54" t="n"/>
+      <c r="G2" s="55" t="n"/>
+      <c r="H2" s="51" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="49" t="n"/>
       <c r="B3" s="50" t="n"/>
-      <c r="C3" s="51" t="n"/>
+      <c r="C3" s="52" t="n"/>
       <c r="D3" s="52" t="n"/>
       <c r="E3" s="52" t="n"/>
       <c r="F3" s="52" t="n"/>
+      <c r="G3" s="52" t="n"/>
+      <c r="H3" s="51" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="49" t="n"/>
       <c r="B4" s="50" t="n"/>
-      <c r="C4" s="51" t="n"/>
+      <c r="C4" s="52" t="n"/>
       <c r="D4" s="52" t="n"/>
       <c r="E4" s="52" t="n"/>
       <c r="F4" s="52" t="n"/>
+      <c r="G4" s="52" t="n"/>
+      <c r="H4" s="51" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="49" t="n"/>
       <c r="B5" s="50" t="n"/>
-      <c r="C5" s="51" t="n"/>
+      <c r="C5" s="52" t="n"/>
       <c r="D5" s="52" t="n"/>
       <c r="E5" s="52" t="n"/>
       <c r="F5" s="52" t="n"/>
+      <c r="G5" s="52" t="n"/>
+      <c r="H5" s="51" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="49" t="n"/>
       <c r="B6" s="50" t="n"/>
-      <c r="C6" s="51" t="n"/>
+      <c r="C6" s="52" t="n"/>
       <c r="D6" s="52" t="n"/>
       <c r="E6" s="52" t="n"/>
       <c r="F6" s="52" t="n"/>
+      <c r="G6" s="52" t="n"/>
+      <c r="H6" s="51" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="49" t="n"/>
       <c r="B7" s="50" t="n"/>
-      <c r="C7" s="51" t="n"/>
+      <c r="C7" s="52" t="n"/>
       <c r="D7" s="52" t="n"/>
       <c r="E7" s="52" t="n"/>
       <c r="F7" s="52" t="n"/>
+      <c r="G7" s="52" t="n"/>
+      <c r="H7" s="51" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="49" t="n"/>
       <c r="B8" s="50" t="n"/>
-      <c r="C8" s="51" t="n"/>
+      <c r="C8" s="52" t="n"/>
       <c r="D8" s="52" t="n"/>
       <c r="E8" s="52" t="n"/>
       <c r="F8" s="52" t="n"/>
+      <c r="G8" s="52" t="n"/>
+      <c r="H8" s="51" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="49" t="n"/>
       <c r="B9" s="50" t="n"/>
-      <c r="C9" s="51" t="n"/>
+      <c r="C9" s="52" t="n"/>
       <c r="D9" s="52" t="n"/>
       <c r="E9" s="52" t="n"/>
       <c r="F9" s="52" t="n"/>
+      <c r="G9" s="52" t="n"/>
+      <c r="H9" s="51" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="49" t="n"/>
       <c r="B10" s="50" t="n"/>
-      <c r="C10" s="51" t="n"/>
+      <c r="C10" s="52" t="n"/>
       <c r="D10" s="52" t="n"/>
       <c r="E10" s="52" t="n"/>
       <c r="F10" s="52" t="n"/>
+      <c r="G10" s="52" t="n"/>
+      <c r="H10" s="51" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="49" t="n"/>
       <c r="B11" s="50" t="n"/>
-      <c r="C11" s="51" t="n"/>
+      <c r="C11" s="52" t="n"/>
       <c r="D11" s="52" t="n"/>
       <c r="E11" s="52" t="n"/>
       <c r="F11" s="52" t="n"/>
+      <c r="G11" s="52" t="n"/>
+      <c r="H11" s="51" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="49" t="n"/>
       <c r="B12" s="50" t="n"/>
-      <c r="C12" s="51" t="n"/>
+      <c r="C12" s="52" t="n"/>
       <c r="D12" s="52" t="n"/>
       <c r="E12" s="52" t="n"/>
       <c r="F12" s="52" t="n"/>
+      <c r="G12" s="52" t="n"/>
+      <c r="H12" s="51" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="49" t="n"/>
       <c r="B13" s="50" t="n"/>
-      <c r="C13" s="51" t="n"/>
+      <c r="C13" s="52" t="n"/>
       <c r="D13" s="52" t="n"/>
       <c r="E13" s="52" t="n"/>
       <c r="F13" s="52" t="n"/>
+      <c r="G13" s="52" t="n"/>
+      <c r="H13" s="51" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="49" t="n"/>
       <c r="B14" s="50" t="n"/>
-      <c r="C14" s="51" t="n"/>
+      <c r="C14" s="52" t="n"/>
       <c r="D14" s="52" t="n"/>
       <c r="E14" s="52" t="n"/>
       <c r="F14" s="52" t="n"/>
+      <c r="G14" s="52" t="n"/>
+      <c r="H14" s="51" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="49" t="n"/>
       <c r="B15" s="50" t="n"/>
-      <c r="C15" s="51" t="n"/>
+      <c r="C15" s="52" t="n"/>
       <c r="D15" s="52" t="n"/>
       <c r="E15" s="52" t="n"/>
       <c r="F15" s="52" t="n"/>
+      <c r="G15" s="52" t="n"/>
+      <c r="H15" s="51" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="49" t="n"/>
       <c r="B16" s="50" t="n"/>
-      <c r="C16" s="51" t="n"/>
+      <c r="C16" s="52" t="n"/>
       <c r="D16" s="52" t="n"/>
       <c r="E16" s="52" t="n"/>
       <c r="F16" s="52" t="n"/>
+      <c r="G16" s="52" t="n"/>
+      <c r="H16" s="51" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="49" t="n"/>
       <c r="B17" s="50" t="n"/>
-      <c r="C17" s="51" t="n"/>
+      <c r="C17" s="52" t="n"/>
       <c r="D17" s="52" t="n"/>
       <c r="E17" s="52" t="n"/>
       <c r="F17" s="52" t="n"/>
+      <c r="G17" s="52" t="n"/>
+      <c r="H17" s="51" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="49" t="n"/>
       <c r="B18" s="50" t="n"/>
-      <c r="C18" s="51" t="n"/>
+      <c r="C18" s="52" t="n"/>
       <c r="D18" s="52" t="n"/>
       <c r="E18" s="52" t="n"/>
       <c r="F18" s="52" t="n"/>
+      <c r="G18" s="52" t="n"/>
+      <c r="H18" s="51" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="49" t="n"/>
       <c r="B19" s="50" t="n"/>
-      <c r="C19" s="51" t="n"/>
+      <c r="C19" s="52" t="n"/>
       <c r="D19" s="52" t="n"/>
       <c r="E19" s="52" t="n"/>
       <c r="F19" s="52" t="n"/>
+      <c r="G19" s="52" t="n"/>
+      <c r="H19" s="51" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="49" t="n"/>
       <c r="B20" s="50" t="n"/>
-      <c r="C20" s="51" t="n"/>
+      <c r="C20" s="52" t="n"/>
       <c r="D20" s="52" t="n"/>
       <c r="E20" s="52" t="n"/>
       <c r="F20" s="52" t="n"/>
+      <c r="G20" s="52" t="n"/>
+      <c r="H20" s="51" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="49" t="n"/>
       <c r="B21" s="50" t="n"/>
-      <c r="C21" s="51" t="n"/>
+      <c r="C21" s="52" t="n"/>
       <c r="D21" s="52" t="n"/>
       <c r="E21" s="52" t="n"/>
       <c r="F21" s="52" t="n"/>
+      <c r="G21" s="52" t="n"/>
+      <c r="H21" s="51" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="49" t="n"/>
       <c r="B22" s="50" t="n"/>
-      <c r="C22" s="51" t="n"/>
+      <c r="C22" s="52" t="n"/>
       <c r="D22" s="52" t="n"/>
       <c r="E22" s="52" t="n"/>
       <c r="F22" s="52" t="n"/>
+      <c r="G22" s="52" t="n"/>
+      <c r="H22" s="51" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="49" t="n"/>
       <c r="B23" s="50" t="n"/>
-      <c r="C23" s="51" t="n"/>
+      <c r="C23" s="52" t="n"/>
       <c r="D23" s="52" t="n"/>
       <c r="E23" s="52" t="n"/>
       <c r="F23" s="52" t="n"/>
+      <c r="G23" s="52" t="n"/>
+      <c r="H23" s="51" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="49" t="n"/>
       <c r="B24" s="50" t="n"/>
-      <c r="C24" s="51" t="n"/>
+      <c r="C24" s="52" t="n"/>
       <c r="D24" s="52" t="n"/>
       <c r="E24" s="52" t="n"/>
       <c r="F24" s="52" t="n"/>
+      <c r="G24" s="52" t="n"/>
+      <c r="H24" s="51" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="49" t="n"/>
       <c r="B25" s="50" t="n"/>
-      <c r="C25" s="51" t="n"/>
+      <c r="C25" s="52" t="n"/>
       <c r="D25" s="52" t="n"/>
       <c r="E25" s="52" t="n"/>
       <c r="F25" s="52" t="n"/>
+      <c r="G25" s="52" t="n"/>
+      <c r="H25" s="51" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="49" t="n"/>
       <c r="B26" s="50" t="n"/>
-      <c r="C26" s="51" t="n"/>
+      <c r="C26" s="52" t="n"/>
       <c r="D26" s="52" t="n"/>
       <c r="E26" s="52" t="n"/>
       <c r="F26" s="52" t="n"/>
+      <c r="G26" s="52" t="n"/>
+      <c r="H26" s="51" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="49" t="n"/>
       <c r="B27" s="50" t="n"/>
-      <c r="C27" s="51" t="n"/>
+      <c r="C27" s="52" t="n"/>
       <c r="D27" s="52" t="n"/>
       <c r="E27" s="52" t="n"/>
       <c r="F27" s="52" t="n"/>
+      <c r="G27" s="52" t="n"/>
+      <c r="H27" s="51" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="49" t="n"/>
       <c r="B28" s="50" t="n"/>
-      <c r="C28" s="51" t="n"/>
+      <c r="C28" s="52" t="n"/>
       <c r="D28" s="52" t="n"/>
       <c r="E28" s="52" t="n"/>
       <c r="F28" s="52" t="n"/>
+      <c r="G28" s="52" t="n"/>
+      <c r="H28" s="51" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="49" t="n"/>
       <c r="B29" s="50" t="n"/>
-      <c r="C29" s="51" t="n"/>
+      <c r="C29" s="52" t="n"/>
       <c r="D29" s="52" t="n"/>
       <c r="E29" s="52" t="n"/>
       <c r="F29" s="52" t="n"/>
+      <c r="G29" s="52" t="n"/>
+      <c r="H29" s="51" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="49" t="n"/>
       <c r="B30" s="50" t="n"/>
-      <c r="C30" s="51" t="n"/>
+      <c r="C30" s="52" t="n"/>
       <c r="D30" s="52" t="n"/>
       <c r="E30" s="52" t="n"/>
       <c r="F30" s="52" t="n"/>
+      <c r="G30" s="52" t="n"/>
+      <c r="H30" s="51" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="49" t="n"/>
       <c r="B31" s="50" t="n"/>
-      <c r="C31" s="51" t="n"/>
+      <c r="C31" s="52" t="n"/>
       <c r="D31" s="52" t="n"/>
       <c r="E31" s="52" t="n"/>
       <c r="F31" s="52" t="n"/>
+      <c r="G31" s="52" t="n"/>
+      <c r="H31" s="51" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="49" t="n"/>
       <c r="B32" s="50" t="n"/>
-      <c r="C32" s="51" t="n"/>
+      <c r="C32" s="52" t="n"/>
       <c r="D32" s="52" t="n"/>
       <c r="E32" s="52" t="n"/>
       <c r="F32" s="52" t="n"/>
+      <c r="G32" s="52" t="n"/>
+      <c r="H32" s="51" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="49" t="n"/>
       <c r="B33" s="50" t="n"/>
-      <c r="C33" s="51" t="n"/>
+      <c r="C33" s="52" t="n"/>
       <c r="D33" s="52" t="n"/>
       <c r="E33" s="52" t="n"/>
       <c r="F33" s="52" t="n"/>
+      <c r="G33" s="52" t="n"/>
+      <c r="H33" s="51" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="49" t="n"/>
       <c r="B34" s="50" t="n"/>
-      <c r="C34" s="51" t="n"/>
+      <c r="C34" s="52" t="n"/>
       <c r="D34" s="52" t="n"/>
       <c r="E34" s="52" t="n"/>
       <c r="F34" s="52" t="n"/>
+      <c r="G34" s="52" t="n"/>
+      <c r="H34" s="51" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="49" t="n"/>
       <c r="B35" s="50" t="n"/>
-      <c r="C35" s="51" t="n"/>
+      <c r="C35" s="52" t="n"/>
       <c r="D35" s="52" t="n"/>
       <c r="E35" s="52" t="n"/>
       <c r="F35" s="52" t="n"/>
+      <c r="G35" s="52" t="n"/>
+      <c r="H35" s="51" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="49" t="n"/>
       <c r="B36" s="50" t="n"/>
-      <c r="C36" s="51" t="n"/>
+      <c r="C36" s="52" t="n"/>
       <c r="D36" s="52" t="n"/>
       <c r="E36" s="52" t="n"/>
       <c r="F36" s="52" t="n"/>
+      <c r="G36" s="52" t="n"/>
+      <c r="H36" s="51" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="49" t="n"/>
       <c r="B37" s="50" t="n"/>
-      <c r="C37" s="51" t="n"/>
+      <c r="C37" s="52" t="n"/>
       <c r="D37" s="52" t="n"/>
       <c r="E37" s="52" t="n"/>
       <c r="F37" s="52" t="n"/>
+      <c r="G37" s="52" t="n"/>
+      <c r="H37" s="51" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="49" t="n"/>
       <c r="B38" s="50" t="n"/>
-      <c r="C38" s="51" t="n"/>
+      <c r="C38" s="52" t="n"/>
       <c r="D38" s="52" t="n"/>
       <c r="E38" s="52" t="n"/>
       <c r="F38" s="52" t="n"/>
+      <c r="G38" s="52" t="n"/>
+      <c r="H38" s="51" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="49" t="n"/>
       <c r="B39" s="50" t="n"/>
-      <c r="C39" s="51" t="n"/>
+      <c r="C39" s="52" t="n"/>
       <c r="D39" s="52" t="n"/>
       <c r="E39" s="52" t="n"/>
       <c r="F39" s="52" t="n"/>
+      <c r="G39" s="52" t="n"/>
+      <c r="H39" s="51" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="49" t="n"/>
       <c r="B40" s="50" t="n"/>
-      <c r="C40" s="51" t="n"/>
+      <c r="C40" s="52" t="n"/>
       <c r="D40" s="52" t="n"/>
       <c r="E40" s="52" t="n"/>
       <c r="F40" s="52" t="n"/>
+      <c r="G40" s="52" t="n"/>
+      <c r="H40" s="51" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="49" t="n"/>
       <c r="B41" s="50" t="n"/>
-      <c r="C41" s="51" t="n"/>
+      <c r="C41" s="52" t="n"/>
       <c r="D41" s="52" t="n"/>
       <c r="E41" s="52" t="n"/>
       <c r="F41" s="52" t="n"/>
+      <c r="G41" s="52" t="n"/>
+      <c r="H41" s="51" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="49" t="n"/>
       <c r="B42" s="50" t="n"/>
-      <c r="C42" s="51" t="n"/>
+      <c r="C42" s="52" t="n"/>
       <c r="D42" s="52" t="n"/>
       <c r="E42" s="52" t="n"/>
       <c r="F42" s="52" t="n"/>
+      <c r="G42" s="52" t="n"/>
+      <c r="H42" s="51" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="49" t="n"/>
       <c r="B43" s="50" t="n"/>
-      <c r="C43" s="51" t="n"/>
+      <c r="C43" s="52" t="n"/>
       <c r="D43" s="52" t="n"/>
       <c r="E43" s="52" t="n"/>
       <c r="F43" s="52" t="n"/>
+      <c r="G43" s="52" t="n"/>
+      <c r="H43" s="51" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="49" t="n"/>
       <c r="B44" s="50" t="n"/>
-      <c r="C44" s="51" t="n"/>
+      <c r="C44" s="52" t="n"/>
       <c r="D44" s="52" t="n"/>
       <c r="E44" s="52" t="n"/>
       <c r="F44" s="52" t="n"/>
+      <c r="G44" s="52" t="n"/>
+      <c r="H44" s="51" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="49" t="n"/>
       <c r="B45" s="50" t="n"/>
-      <c r="C45" s="51" t="n"/>
+      <c r="C45" s="52" t="n"/>
       <c r="D45" s="52" t="n"/>
       <c r="E45" s="52" t="n"/>
       <c r="F45" s="52" t="n"/>
+      <c r="G45" s="52" t="n"/>
+      <c r="H45" s="51" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="49" t="n"/>
       <c r="B46" s="50" t="n"/>
-      <c r="C46" s="51" t="n"/>
+      <c r="C46" s="52" t="n"/>
       <c r="D46" s="52" t="n"/>
       <c r="E46" s="52" t="n"/>
       <c r="F46" s="52" t="n"/>
+      <c r="G46" s="52" t="n"/>
+      <c r="H46" s="51" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="49" t="n"/>
       <c r="B47" s="50" t="n"/>
-      <c r="C47" s="51" t="n"/>
+      <c r="C47" s="52" t="n"/>
       <c r="D47" s="52" t="n"/>
       <c r="E47" s="52" t="n"/>
       <c r="F47" s="52" t="n"/>
+      <c r="G47" s="52" t="n"/>
+      <c r="H47" s="51" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="49" t="n"/>
       <c r="B48" s="50" t="n"/>
-      <c r="C48" s="51" t="n"/>
+      <c r="C48" s="52" t="n"/>
       <c r="D48" s="52" t="n"/>
       <c r="E48" s="52" t="n"/>
       <c r="F48" s="52" t="n"/>
+      <c r="G48" s="52" t="n"/>
+      <c r="H48" s="51" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="49" t="n"/>
       <c r="B49" s="50" t="n"/>
-      <c r="C49" s="51" t="n"/>
+      <c r="C49" s="52" t="n"/>
       <c r="D49" s="52" t="n"/>
       <c r="E49" s="52" t="n"/>
       <c r="F49" s="52" t="n"/>
+      <c r="G49" s="52" t="n"/>
+      <c r="H49" s="51" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="49" t="n"/>
       <c r="B50" s="50" t="n"/>
-      <c r="C50" s="51" t="n"/>
+      <c r="C50" s="52" t="n"/>
       <c r="D50" s="52" t="n"/>
       <c r="E50" s="52" t="n"/>
       <c r="F50" s="52" t="n"/>
+      <c r="G50" s="52" t="n"/>
+      <c r="H50" s="51" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="49" t="n"/>
       <c r="B51" s="50" t="n"/>
-      <c r="C51" s="51" t="n"/>
+      <c r="C51" s="52" t="n"/>
       <c r="D51" s="52" t="n"/>
       <c r="E51" s="52" t="n"/>
       <c r="F51" s="52" t="n"/>
+      <c r="G51" s="52" t="n"/>
+      <c r="H51" s="51" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="49" t="n"/>
       <c r="B52" s="50" t="n"/>
-      <c r="C52" s="51" t="n"/>
+      <c r="C52" s="52" t="n"/>
       <c r="D52" s="52" t="n"/>
       <c r="E52" s="52" t="n"/>
       <c r="F52" s="52" t="n"/>
+      <c r="G52" s="52" t="n"/>
+      <c r="H52" s="51" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="49" t="n"/>
       <c r="B53" s="50" t="n"/>
-      <c r="C53" s="51" t="n"/>
+      <c r="C53" s="52" t="n"/>
       <c r="D53" s="52" t="n"/>
       <c r="E53" s="52" t="n"/>
       <c r="F53" s="52" t="n"/>
+      <c r="G53" s="52" t="n"/>
+      <c r="H53" s="51" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="49" t="n"/>
       <c r="B54" s="50" t="n"/>
-      <c r="C54" s="51" t="n"/>
+      <c r="C54" s="52" t="n"/>
       <c r="D54" s="52" t="n"/>
       <c r="E54" s="52" t="n"/>
       <c r="F54" s="52" t="n"/>
+      <c r="G54" s="52" t="n"/>
+      <c r="H54" s="51" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="49" t="n"/>
       <c r="B55" s="50" t="n"/>
-      <c r="C55" s="51" t="n"/>
+      <c r="C55" s="52" t="n"/>
       <c r="D55" s="52" t="n"/>
       <c r="E55" s="52" t="n"/>
       <c r="F55" s="52" t="n"/>
+      <c r="G55" s="52" t="n"/>
+      <c r="H55" s="51" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="49" t="n"/>
       <c r="B56" s="50" t="n"/>
-      <c r="C56" s="51" t="n"/>
+      <c r="C56" s="52" t="n"/>
       <c r="D56" s="52" t="n"/>
       <c r="E56" s="52" t="n"/>
       <c r="F56" s="52" t="n"/>
+      <c r="G56" s="52" t="n"/>
+      <c r="H56" s="51" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="49" t="n"/>
       <c r="B57" s="50" t="n"/>
-      <c r="C57" s="51" t="n"/>
+      <c r="C57" s="52" t="n"/>
       <c r="D57" s="52" t="n"/>
       <c r="E57" s="52" t="n"/>
       <c r="F57" s="52" t="n"/>
+      <c r="G57" s="52" t="n"/>
+      <c r="H57" s="51" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="49" t="n"/>
       <c r="B58" s="50" t="n"/>
-      <c r="C58" s="51" t="n"/>
+      <c r="C58" s="52" t="n"/>
       <c r="D58" s="52" t="n"/>
       <c r="E58" s="52" t="n"/>
       <c r="F58" s="52" t="n"/>
+      <c r="G58" s="52" t="n"/>
+      <c r="H58" s="51" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="49" t="n"/>
       <c r="B59" s="50" t="n"/>
-      <c r="C59" s="51" t="n"/>
+      <c r="C59" s="52" t="n"/>
       <c r="D59" s="52" t="n"/>
       <c r="E59" s="52" t="n"/>
       <c r="F59" s="52" t="n"/>
+      <c r="G59" s="52" t="n"/>
+      <c r="H59" s="51" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="49" t="n"/>
       <c r="B60" s="50" t="n"/>
-      <c r="C60" s="51" t="n"/>
+      <c r="C60" s="52" t="n"/>
       <c r="D60" s="52" t="n"/>
       <c r="E60" s="52" t="n"/>
       <c r="F60" s="52" t="n"/>
+      <c r="G60" s="52" t="n"/>
+      <c r="H60" s="51" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="49" t="n"/>
       <c r="B61" s="50" t="n"/>
-      <c r="C61" s="51" t="n"/>
+      <c r="C61" s="52" t="n"/>
       <c r="D61" s="52" t="n"/>
       <c r="E61" s="52" t="n"/>
       <c r="F61" s="52" t="n"/>
+      <c r="G61" s="52" t="n"/>
+      <c r="H61" s="51" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="49" t="n"/>
       <c r="B62" s="50" t="n"/>
-      <c r="C62" s="51" t="n"/>
+      <c r="C62" s="52" t="n"/>
       <c r="D62" s="52" t="n"/>
       <c r="E62" s="52" t="n"/>
       <c r="F62" s="52" t="n"/>
+      <c r="G62" s="52" t="n"/>
+      <c r="H62" s="51" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="49" t="n"/>
       <c r="B63" s="50" t="n"/>
-      <c r="C63" s="51" t="n"/>
+      <c r="C63" s="52" t="n"/>
       <c r="D63" s="52" t="n"/>
       <c r="E63" s="52" t="n"/>
       <c r="F63" s="52" t="n"/>
+      <c r="G63" s="52" t="n"/>
+      <c r="H63" s="51" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="49" t="n"/>
       <c r="B64" s="50" t="n"/>
-      <c r="C64" s="51" t="n"/>
+      <c r="C64" s="52" t="n"/>
       <c r="D64" s="52" t="n"/>
       <c r="E64" s="52" t="n"/>
       <c r="F64" s="52" t="n"/>
+      <c r="G64" s="52" t="n"/>
+      <c r="H64" s="51" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="49" t="n"/>
       <c r="B65" s="50" t="n"/>
-      <c r="C65" s="51" t="n"/>
+      <c r="C65" s="52" t="n"/>
       <c r="D65" s="52" t="n"/>
       <c r="E65" s="52" t="n"/>
       <c r="F65" s="52" t="n"/>
+      <c r="G65" s="52" t="n"/>
+      <c r="H65" s="51" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="49" t="n"/>
       <c r="B66" s="50" t="n"/>
-      <c r="C66" s="51" t="n"/>
+      <c r="C66" s="52" t="n"/>
       <c r="D66" s="52" t="n"/>
       <c r="E66" s="52" t="n"/>
       <c r="F66" s="52" t="n"/>
+      <c r="G66" s="52" t="n"/>
+      <c r="H66" s="51" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="49" t="n"/>
       <c r="B67" s="50" t="n"/>
-      <c r="C67" s="51" t="n"/>
+      <c r="C67" s="52" t="n"/>
       <c r="D67" s="52" t="n"/>
       <c r="E67" s="52" t="n"/>
       <c r="F67" s="52" t="n"/>
+      <c r="G67" s="52" t="n"/>
+      <c r="H67" s="51" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="49" t="n"/>
       <c r="B68" s="50" t="n"/>
-      <c r="C68" s="51" t="n"/>
+      <c r="C68" s="52" t="n"/>
       <c r="D68" s="52" t="n"/>
       <c r="E68" s="52" t="n"/>
       <c r="F68" s="52" t="n"/>
+      <c r="G68" s="52" t="n"/>
+      <c r="H68" s="51" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="49" t="n"/>
       <c r="B69" s="50" t="n"/>
-      <c r="C69" s="51" t="n"/>
+      <c r="C69" s="52" t="n"/>
       <c r="D69" s="52" t="n"/>
       <c r="E69" s="52" t="n"/>
       <c r="F69" s="52" t="n"/>
+      <c r="G69" s="52" t="n"/>
+      <c r="H69" s="51" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="49" t="n"/>
       <c r="B70" s="50" t="n"/>
-      <c r="C70" s="51" t="n"/>
+      <c r="C70" s="52" t="n"/>
       <c r="D70" s="52" t="n"/>
       <c r="E70" s="52" t="n"/>
       <c r="F70" s="52" t="n"/>
+      <c r="G70" s="52" t="n"/>
+      <c r="H70" s="51" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="49" t="n"/>
       <c r="B71" s="50" t="n"/>
-      <c r="C71" s="51" t="n"/>
+      <c r="C71" s="52" t="n"/>
       <c r="D71" s="52" t="n"/>
       <c r="E71" s="52" t="n"/>
       <c r="F71" s="52" t="n"/>
+      <c r="G71" s="52" t="n"/>
+      <c r="H71" s="51" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="49" t="n"/>
       <c r="B72" s="50" t="n"/>
-      <c r="C72" s="51" t="n"/>
+      <c r="C72" s="52" t="n"/>
       <c r="D72" s="52" t="n"/>
       <c r="E72" s="52" t="n"/>
       <c r="F72" s="52" t="n"/>
+      <c r="G72" s="52" t="n"/>
+      <c r="H72" s="51" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="49" t="n"/>
       <c r="B73" s="50" t="n"/>
-      <c r="C73" s="51" t="n"/>
+      <c r="C73" s="52" t="n"/>
       <c r="D73" s="52" t="n"/>
       <c r="E73" s="52" t="n"/>
       <c r="F73" s="52" t="n"/>
+      <c r="G73" s="52" t="n"/>
+      <c r="H73" s="51" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="49" t="n"/>
       <c r="B74" s="50" t="n"/>
-      <c r="C74" s="51" t="n"/>
+      <c r="C74" s="52" t="n"/>
       <c r="D74" s="52" t="n"/>
       <c r="E74" s="52" t="n"/>
       <c r="F74" s="52" t="n"/>
+      <c r="G74" s="52" t="n"/>
+      <c r="H74" s="51" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="49" t="n"/>
       <c r="B75" s="50" t="n"/>
-      <c r="C75" s="51" t="n"/>
+      <c r="C75" s="52" t="n"/>
       <c r="D75" s="52" t="n"/>
       <c r="E75" s="52" t="n"/>
       <c r="F75" s="52" t="n"/>
+      <c r="G75" s="52" t="n"/>
+      <c r="H75" s="51" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="49" t="n"/>
       <c r="B76" s="50" t="n"/>
-      <c r="C76" s="51" t="n"/>
+      <c r="C76" s="52" t="n"/>
       <c r="D76" s="52" t="n"/>
       <c r="E76" s="52" t="n"/>
       <c r="F76" s="52" t="n"/>
+      <c r="G76" s="52" t="n"/>
+      <c r="H76" s="51" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="49" t="n"/>
       <c r="B77" s="50" t="n"/>
-      <c r="C77" s="51" t="n"/>
+      <c r="C77" s="52" t="n"/>
       <c r="D77" s="52" t="n"/>
       <c r="E77" s="52" t="n"/>
       <c r="F77" s="52" t="n"/>
+      <c r="G77" s="52" t="n"/>
+      <c r="H77" s="51" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="49" t="n"/>
       <c r="B78" s="50" t="n"/>
-      <c r="C78" s="51" t="n"/>
+      <c r="C78" s="52" t="n"/>
       <c r="D78" s="52" t="n"/>
       <c r="E78" s="52" t="n"/>
       <c r="F78" s="52" t="n"/>
+      <c r="G78" s="52" t="n"/>
+      <c r="H78" s="51" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="49" t="n"/>
       <c r="B79" s="50" t="n"/>
-      <c r="C79" s="51" t="n"/>
+      <c r="C79" s="52" t="n"/>
       <c r="D79" s="52" t="n"/>
       <c r="E79" s="52" t="n"/>
       <c r="F79" s="52" t="n"/>
+      <c r="G79" s="52" t="n"/>
+      <c r="H79" s="51" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="49" t="n"/>
       <c r="B80" s="50" t="n"/>
-      <c r="C80" s="51" t="n"/>
+      <c r="C80" s="52" t="n"/>
       <c r="D80" s="52" t="n"/>
       <c r="E80" s="52" t="n"/>
       <c r="F80" s="52" t="n"/>
+      <c r="G80" s="52" t="n"/>
+      <c r="H80" s="51" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="49" t="n"/>
       <c r="B81" s="50" t="n"/>
-      <c r="C81" s="51" t="n"/>
+      <c r="C81" s="52" t="n"/>
       <c r="D81" s="52" t="n"/>
       <c r="E81" s="52" t="n"/>
       <c r="F81" s="52" t="n"/>
+      <c r="G81" s="52" t="n"/>
+      <c r="H81" s="51" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="49" t="n"/>
       <c r="B82" s="50" t="n"/>
-      <c r="C82" s="51" t="n"/>
+      <c r="C82" s="52" t="n"/>
       <c r="D82" s="52" t="n"/>
       <c r="E82" s="52" t="n"/>
       <c r="F82" s="52" t="n"/>
+      <c r="G82" s="52" t="n"/>
+      <c r="H82" s="51" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="49" t="n"/>
       <c r="B83" s="50" t="n"/>
-      <c r="C83" s="51" t="n"/>
+      <c r="C83" s="52" t="n"/>
       <c r="D83" s="52" t="n"/>
       <c r="E83" s="52" t="n"/>
       <c r="F83" s="52" t="n"/>
+      <c r="G83" s="52" t="n"/>
+      <c r="H83" s="51" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="49" t="n"/>
       <c r="B84" s="50" t="n"/>
-      <c r="C84" s="51" t="n"/>
+      <c r="C84" s="52" t="n"/>
       <c r="D84" s="52" t="n"/>
       <c r="E84" s="52" t="n"/>
       <c r="F84" s="52" t="n"/>
+      <c r="G84" s="52" t="n"/>
+      <c r="H84" s="51" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="49" t="n"/>
       <c r="B85" s="50" t="n"/>
-      <c r="C85" s="51" t="n"/>
+      <c r="C85" s="52" t="n"/>
       <c r="D85" s="52" t="n"/>
       <c r="E85" s="52" t="n"/>
       <c r="F85" s="52" t="n"/>
+      <c r="G85" s="52" t="n"/>
+      <c r="H85" s="51" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="49" t="n"/>
       <c r="B86" s="50" t="n"/>
-      <c r="C86" s="51" t="n"/>
+      <c r="C86" s="52" t="n"/>
       <c r="D86" s="52" t="n"/>
       <c r="E86" s="52" t="n"/>
       <c r="F86" s="52" t="n"/>
+      <c r="G86" s="52" t="n"/>
+      <c r="H86" s="51" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="49" t="n"/>
       <c r="B87" s="50" t="n"/>
-      <c r="C87" s="51" t="n"/>
+      <c r="C87" s="52" t="n"/>
       <c r="D87" s="52" t="n"/>
       <c r="E87" s="52" t="n"/>
       <c r="F87" s="52" t="n"/>
+      <c r="G87" s="52" t="n"/>
+      <c r="H87" s="51" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="49" t="n"/>
       <c r="B88" s="50" t="n"/>
-      <c r="C88" s="51" t="n"/>
+      <c r="C88" s="52" t="n"/>
       <c r="D88" s="52" t="n"/>
       <c r="E88" s="52" t="n"/>
       <c r="F88" s="52" t="n"/>
+      <c r="G88" s="52" t="n"/>
+      <c r="H88" s="51" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="49" t="n"/>
       <c r="B89" s="50" t="n"/>
-      <c r="C89" s="51" t="n"/>
+      <c r="C89" s="52" t="n"/>
       <c r="D89" s="52" t="n"/>
       <c r="E89" s="52" t="n"/>
       <c r="F89" s="52" t="n"/>
+      <c r="G89" s="52" t="n"/>
+      <c r="H89" s="51" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="49" t="n"/>
       <c r="B90" s="50" t="n"/>
-      <c r="C90" s="51" t="n"/>
+      <c r="C90" s="52" t="n"/>
       <c r="D90" s="52" t="n"/>
       <c r="E90" s="52" t="n"/>
       <c r="F90" s="52" t="n"/>
+      <c r="G90" s="52" t="n"/>
+      <c r="H90" s="51" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="49" t="n"/>
       <c r="B91" s="50" t="n"/>
-      <c r="C91" s="51" t="n"/>
+      <c r="C91" s="52" t="n"/>
       <c r="D91" s="52" t="n"/>
       <c r="E91" s="52" t="n"/>
       <c r="F91" s="52" t="n"/>
+      <c r="G91" s="52" t="n"/>
+      <c r="H91" s="51" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="49" t="n"/>
       <c r="B92" s="50" t="n"/>
-      <c r="C92" s="51" t="n"/>
+      <c r="C92" s="52" t="n"/>
       <c r="D92" s="52" t="n"/>
       <c r="E92" s="52" t="n"/>
       <c r="F92" s="52" t="n"/>
+      <c r="G92" s="52" t="n"/>
+      <c r="H92" s="51" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="49" t="n"/>
       <c r="B93" s="50" t="n"/>
-      <c r="C93" s="51" t="n"/>
+      <c r="C93" s="52" t="n"/>
       <c r="D93" s="52" t="n"/>
       <c r="E93" s="52" t="n"/>
       <c r="F93" s="52" t="n"/>
+      <c r="G93" s="52" t="n"/>
+      <c r="H93" s="51" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="49" t="n"/>
       <c r="B94" s="50" t="n"/>
-      <c r="C94" s="51" t="n"/>
+      <c r="C94" s="52" t="n"/>
       <c r="D94" s="52" t="n"/>
       <c r="E94" s="52" t="n"/>
       <c r="F94" s="52" t="n"/>
+      <c r="G94" s="52" t="n"/>
+      <c r="H94" s="51" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="49" t="n"/>
       <c r="B95" s="50" t="n"/>
-      <c r="C95" s="51" t="n"/>
+      <c r="C95" s="52" t="n"/>
       <c r="D95" s="52" t="n"/>
       <c r="E95" s="52" t="n"/>
       <c r="F95" s="52" t="n"/>
+      <c r="G95" s="52" t="n"/>
+      <c r="H95" s="51" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="49" t="n"/>
       <c r="B96" s="50" t="n"/>
-      <c r="C96" s="51" t="n"/>
+      <c r="C96" s="52" t="n"/>
       <c r="D96" s="52" t="n"/>
       <c r="E96" s="52" t="n"/>
       <c r="F96" s="52" t="n"/>
+      <c r="G96" s="52" t="n"/>
+      <c r="H96" s="51" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="49" t="n"/>
       <c r="B97" s="50" t="n"/>
-      <c r="C97" s="51" t="n"/>
+      <c r="C97" s="52" t="n"/>
       <c r="D97" s="52" t="n"/>
       <c r="E97" s="52" t="n"/>
       <c r="F97" s="52" t="n"/>
+      <c r="G97" s="52" t="n"/>
+      <c r="H97" s="51" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="49" t="n"/>
       <c r="B98" s="50" t="n"/>
-      <c r="C98" s="51" t="n"/>
+      <c r="C98" s="52" t="n"/>
       <c r="D98" s="52" t="n"/>
       <c r="E98" s="52" t="n"/>
       <c r="F98" s="52" t="n"/>
+      <c r="G98" s="52" t="n"/>
+      <c r="H98" s="51" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="49" t="n"/>
       <c r="B99" s="50" t="n"/>
-      <c r="C99" s="51" t="n"/>
+      <c r="C99" s="52" t="n"/>
       <c r="D99" s="52" t="n"/>
       <c r="E99" s="52" t="n"/>
       <c r="F99" s="52" t="n"/>
+      <c r="G99" s="52" t="n"/>
+      <c r="H99" s="51" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="49" t="n"/>
       <c r="B100" s="50" t="n"/>
-      <c r="C100" s="51" t="n"/>
+      <c r="C100" s="52" t="n"/>
       <c r="D100" s="52" t="n"/>
       <c r="E100" s="52" t="n"/>
       <c r="F100" s="52" t="n"/>
+      <c r="G100" s="52" t="n"/>
+      <c r="H100" s="51" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="49" t="n"/>
       <c r="B101" s="50" t="n"/>
-      <c r="C101" s="51" t="n"/>
+      <c r="C101" s="52" t="n"/>
       <c r="D101" s="52" t="n"/>
       <c r="E101" s="52" t="n"/>
       <c r="F101" s="52" t="n"/>
+      <c r="G101" s="52" t="n"/>
+      <c r="H101" s="51" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="49" t="n"/>
       <c r="B102" s="50" t="n"/>
-      <c r="C102" s="51" t="n"/>
+      <c r="C102" s="52" t="n"/>
       <c r="D102" s="52" t="n"/>
       <c r="E102" s="52" t="n"/>
       <c r="F102" s="52" t="n"/>
+      <c r="G102" s="52" t="n"/>
+      <c r="H102" s="51" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="6">
@@ -2067,20 +2461,20 @@
       <formula1>1</formula1>
       <formula2>255</formula2>
     </dataValidation>
-    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Data tidak valid" error="Isi ID kelas yang sudah ada, atau kosongkan jika belum memiliki kelas." promptTitle="ID kelas" prompt="Isi ID kelas yang sudah ada, atau kosongkan jika belum memiliki kelas." type="whole" errorStyle="stop" operator="greaterThanOrEqual">
+    <dataValidation sqref="H2:H1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Data tidak valid" error="Isi ID kelas yang sudah ada, atau kosongkan jika belum memiliki kelas." promptTitle="ID kelas" prompt="Isi ID kelas yang sudah ada, atau kosongkan jika belum memiliki kelas." type="whole" errorStyle="stop" operator="greaterThanOrEqual">
       <formula1>1</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Data tidak valid" error="Tepat 10 digit. Nol di depan harus dipertahankan. NISN harus unik." promptTitle="NISN" prompt="Tepat 10 digit. Nol di depan harus dipertahankan. NISN harus unik." type="custom" errorStyle="stop" operator="between">
-      <formula1>OR(D2="",AND(LEN(D2)=10,SUMPRODUCT(--ISNUMBER(FIND(MID(D2,ROW($1:$10),1),"0123456789")))=10,COUNTIF($D$2:$D$1048576,D2)=1))</formula1>
+    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Data tidak valid" error="Tepat 10 digit. Nol di depan harus dipertahankan. NISN harus unik." promptTitle="NISN" prompt="Tepat 10 digit. Nol di depan harus dipertahankan. NISN harus unik." type="custom" errorStyle="stop" operator="between">
+      <formula1>OR(C2="",AND(LEN(C2)=10,SUMPRODUCT(--ISNUMBER(FIND(MID(C2,ROW($1:$10),1),"0123456789")))=10,COUNTIF($C$2:$C$1048576,C2)=1))</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Data tidak valid" error="Pilih Aktif atau Tidak aktif." promptTitle="Status siswa" prompt="Pilih Aktif atau Tidak aktif." type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Data tidak valid" error="Pilih Aktif atau Tidak aktif." promptTitle="Status siswa" prompt="Pilih Aktif atau Tidak aktif." type="list" errorStyle="stop" operator="between">
       <formula1>"Aktif,Tidak aktif"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="F2:F1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Data tidak valid" error="Opsional. Angka saja, diawali 08 atau 628; maksimal 32 digit." promptTitle="Nomor wali" prompt="Opsional. Angka saja, diawali 08 atau 628; maksimal 32 digit." type="custom" errorStyle="stop">
-      <formula1>OR(F2="",AND(LEN(F2)&lt;=32,OR(LEFT(F2,2)="08",LEFT(F2,3)="628"),SUMPRODUCT(--ISNUMBER(FIND(MID(F2,ROW($1:$32),1),"0123456789")),--(ROW($1:$32)&lt;=LEN(F2)))=LEN(F2)))</formula1>
+    <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Data tidak valid" error="Opsional. Angka saja, diawali 08 atau 628; maksimal 32 digit." promptTitle="Nomor wali" prompt="Opsional. Angka saja, diawali 08 atau 628; maksimal 32 digit." type="custom" errorStyle="stop">
+      <formula1>OR(E2="",AND(LEN(E2)&lt;=32,OR(LEFT(E2,2)="08",LEFT(E2,3)="628"),SUMPRODUCT(--ISNUMBER(FIND(MID(E2,ROW($1:$32),1),"0123456789")),--(ROW($1:$32)&lt;=LEN(E2)))=LEN(E2)))</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -2091,4 +2485,565 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <tabColor rgb="FFD8EEEE"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:C102"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.7578125" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="13.35" customWidth="1" style="43" min="1" max="1"/>
+    <col width="15.89" customWidth="1" style="43" min="2" max="2"/>
+    <col width="34.06" customWidth="1" style="44" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25" customFormat="1" customHeight="1" s="21">
+      <c r="A1" s="56" t="inlineStr">
+        <is>
+          <t>ID KELAS</t>
+        </is>
+      </c>
+      <c r="B1" s="57" t="inlineStr">
+        <is>
+          <t>JENJANG</t>
+        </is>
+      </c>
+      <c r="C1" s="58" t="inlineStr">
+        <is>
+          <t>NAMA KELAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customFormat="1" customHeight="1" s="21">
+      <c r="A2" s="59" t="n"/>
+      <c r="B2" s="60" t="n"/>
+      <c r="C2" s="61" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="59" t="n"/>
+      <c r="B3" s="60" t="n"/>
+      <c r="C3" s="61" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="59" t="n"/>
+      <c r="B4" s="60" t="n"/>
+      <c r="C4" s="61" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="59" t="n"/>
+      <c r="B5" s="60" t="n"/>
+      <c r="C5" s="61" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="59" t="n"/>
+      <c r="B6" s="60" t="n"/>
+      <c r="C6" s="61" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="59" t="n"/>
+      <c r="B7" s="60" t="n"/>
+      <c r="C7" s="61" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="59" t="n"/>
+      <c r="B8" s="60" t="n"/>
+      <c r="C8" s="61" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="59" t="n"/>
+      <c r="B9" s="60" t="n"/>
+      <c r="C9" s="61" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="59" t="n"/>
+      <c r="B10" s="60" t="n"/>
+      <c r="C10" s="61" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="59" t="n"/>
+      <c r="B11" s="60" t="n"/>
+      <c r="C11" s="61" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="59" t="n"/>
+      <c r="B12" s="60" t="n"/>
+      <c r="C12" s="61" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="59" t="n"/>
+      <c r="B13" s="60" t="n"/>
+      <c r="C13" s="61" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="59" t="n"/>
+      <c r="B14" s="60" t="n"/>
+      <c r="C14" s="61" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="59" t="n"/>
+      <c r="B15" s="60" t="n"/>
+      <c r="C15" s="61" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="59" t="n"/>
+      <c r="B16" s="60" t="n"/>
+      <c r="C16" s="61" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="59" t="n"/>
+      <c r="B17" s="60" t="n"/>
+      <c r="C17" s="61" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="59" t="n"/>
+      <c r="B18" s="60" t="n"/>
+      <c r="C18" s="61" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="59" t="n"/>
+      <c r="B19" s="60" t="n"/>
+      <c r="C19" s="61" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="59" t="n"/>
+      <c r="B20" s="60" t="n"/>
+      <c r="C20" s="61" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="59" t="n"/>
+      <c r="B21" s="60" t="n"/>
+      <c r="C21" s="61" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="59" t="n"/>
+      <c r="B22" s="60" t="n"/>
+      <c r="C22" s="61" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="59" t="n"/>
+      <c r="B23" s="60" t="n"/>
+      <c r="C23" s="61" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="59" t="n"/>
+      <c r="B24" s="60" t="n"/>
+      <c r="C24" s="61" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="59" t="n"/>
+      <c r="B25" s="60" t="n"/>
+      <c r="C25" s="61" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="59" t="n"/>
+      <c r="B26" s="60" t="n"/>
+      <c r="C26" s="61" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="59" t="n"/>
+      <c r="B27" s="60" t="n"/>
+      <c r="C27" s="61" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="59" t="n"/>
+      <c r="B28" s="60" t="n"/>
+      <c r="C28" s="61" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="59" t="n"/>
+      <c r="B29" s="60" t="n"/>
+      <c r="C29" s="61" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="59" t="n"/>
+      <c r="B30" s="60" t="n"/>
+      <c r="C30" s="61" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="59" t="n"/>
+      <c r="B31" s="60" t="n"/>
+      <c r="C31" s="61" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="59" t="n"/>
+      <c r="B32" s="60" t="n"/>
+      <c r="C32" s="61" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="59" t="n"/>
+      <c r="B33" s="60" t="n"/>
+      <c r="C33" s="61" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="59" t="n"/>
+      <c r="B34" s="60" t="n"/>
+      <c r="C34" s="61" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="59" t="n"/>
+      <c r="B35" s="60" t="n"/>
+      <c r="C35" s="61" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="59" t="n"/>
+      <c r="B36" s="60" t="n"/>
+      <c r="C36" s="61" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="59" t="n"/>
+      <c r="B37" s="60" t="n"/>
+      <c r="C37" s="61" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="59" t="n"/>
+      <c r="B38" s="60" t="n"/>
+      <c r="C38" s="61" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="59" t="n"/>
+      <c r="B39" s="60" t="n"/>
+      <c r="C39" s="61" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="59" t="n"/>
+      <c r="B40" s="60" t="n"/>
+      <c r="C40" s="61" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="59" t="n"/>
+      <c r="B41" s="60" t="n"/>
+      <c r="C41" s="61" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="59" t="n"/>
+      <c r="B42" s="60" t="n"/>
+      <c r="C42" s="61" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="59" t="n"/>
+      <c r="B43" s="60" t="n"/>
+      <c r="C43" s="61" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="59" t="n"/>
+      <c r="B44" s="60" t="n"/>
+      <c r="C44" s="61" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="59" t="n"/>
+      <c r="B45" s="60" t="n"/>
+      <c r="C45" s="61" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="59" t="n"/>
+      <c r="B46" s="60" t="n"/>
+      <c r="C46" s="61" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="59" t="n"/>
+      <c r="B47" s="60" t="n"/>
+      <c r="C47" s="61" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="59" t="n"/>
+      <c r="B48" s="60" t="n"/>
+      <c r="C48" s="61" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="59" t="n"/>
+      <c r="B49" s="60" t="n"/>
+      <c r="C49" s="61" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="59" t="n"/>
+      <c r="B50" s="60" t="n"/>
+      <c r="C50" s="61" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="59" t="n"/>
+      <c r="B51" s="60" t="n"/>
+      <c r="C51" s="61" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="59" t="n"/>
+      <c r="B52" s="60" t="n"/>
+      <c r="C52" s="61" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="59" t="n"/>
+      <c r="B53" s="60" t="n"/>
+      <c r="C53" s="61" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="59" t="n"/>
+      <c r="B54" s="60" t="n"/>
+      <c r="C54" s="61" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="59" t="n"/>
+      <c r="B55" s="60" t="n"/>
+      <c r="C55" s="61" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="59" t="n"/>
+      <c r="B56" s="60" t="n"/>
+      <c r="C56" s="61" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="59" t="n"/>
+      <c r="B57" s="60" t="n"/>
+      <c r="C57" s="61" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="59" t="n"/>
+      <c r="B58" s="60" t="n"/>
+      <c r="C58" s="61" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="59" t="n"/>
+      <c r="B59" s="60" t="n"/>
+      <c r="C59" s="61" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="59" t="n"/>
+      <c r="B60" s="60" t="n"/>
+      <c r="C60" s="61" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="59" t="n"/>
+      <c r="B61" s="60" t="n"/>
+      <c r="C61" s="61" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="59" t="n"/>
+      <c r="B62" s="60" t="n"/>
+      <c r="C62" s="61" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="59" t="n"/>
+      <c r="B63" s="60" t="n"/>
+      <c r="C63" s="61" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="59" t="n"/>
+      <c r="B64" s="60" t="n"/>
+      <c r="C64" s="61" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="59" t="n"/>
+      <c r="B65" s="60" t="n"/>
+      <c r="C65" s="61" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="59" t="n"/>
+      <c r="B66" s="60" t="n"/>
+      <c r="C66" s="61" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="59" t="n"/>
+      <c r="B67" s="60" t="n"/>
+      <c r="C67" s="61" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="59" t="n"/>
+      <c r="B68" s="60" t="n"/>
+      <c r="C68" s="61" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="59" t="n"/>
+      <c r="B69" s="60" t="n"/>
+      <c r="C69" s="61" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="59" t="n"/>
+      <c r="B70" s="60" t="n"/>
+      <c r="C70" s="61" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="59" t="n"/>
+      <c r="B71" s="60" t="n"/>
+      <c r="C71" s="61" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="59" t="n"/>
+      <c r="B72" s="60" t="n"/>
+      <c r="C72" s="61" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="59" t="n"/>
+      <c r="B73" s="60" t="n"/>
+      <c r="C73" s="61" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="59" t="n"/>
+      <c r="B74" s="60" t="n"/>
+      <c r="C74" s="61" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="59" t="n"/>
+      <c r="B75" s="60" t="n"/>
+      <c r="C75" s="61" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="59" t="n"/>
+      <c r="B76" s="60" t="n"/>
+      <c r="C76" s="61" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="59" t="n"/>
+      <c r="B77" s="60" t="n"/>
+      <c r="C77" s="61" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="59" t="n"/>
+      <c r="B78" s="60" t="n"/>
+      <c r="C78" s="61" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="59" t="n"/>
+      <c r="B79" s="60" t="n"/>
+      <c r="C79" s="61" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="59" t="n"/>
+      <c r="B80" s="60" t="n"/>
+      <c r="C80" s="61" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="59" t="n"/>
+      <c r="B81" s="60" t="n"/>
+      <c r="C81" s="61" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="59" t="n"/>
+      <c r="B82" s="60" t="n"/>
+      <c r="C82" s="61" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="59" t="n"/>
+      <c r="B83" s="60" t="n"/>
+      <c r="C83" s="61" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="59" t="n"/>
+      <c r="B84" s="60" t="n"/>
+      <c r="C84" s="61" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="59" t="n"/>
+      <c r="B85" s="60" t="n"/>
+      <c r="C85" s="61" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="59" t="n"/>
+      <c r="B86" s="60" t="n"/>
+      <c r="C86" s="61" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="59" t="n"/>
+      <c r="B87" s="60" t="n"/>
+      <c r="C87" s="61" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="59" t="n"/>
+      <c r="B88" s="60" t="n"/>
+      <c r="C88" s="61" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="59" t="n"/>
+      <c r="B89" s="60" t="n"/>
+      <c r="C89" s="61" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="59" t="n"/>
+      <c r="B90" s="60" t="n"/>
+      <c r="C90" s="61" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="59" t="n"/>
+      <c r="B91" s="60" t="n"/>
+      <c r="C91" s="61" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="59" t="n"/>
+      <c r="B92" s="60" t="n"/>
+      <c r="C92" s="61" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="59" t="n"/>
+      <c r="B93" s="60" t="n"/>
+      <c r="C93" s="61" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="59" t="n"/>
+      <c r="B94" s="60" t="n"/>
+      <c r="C94" s="61" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="59" t="n"/>
+      <c r="B95" s="60" t="n"/>
+      <c r="C95" s="61" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="59" t="n"/>
+      <c r="B96" s="60" t="n"/>
+      <c r="C96" s="61" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="59" t="n"/>
+      <c r="B97" s="60" t="n"/>
+      <c r="C97" s="61" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="59" t="n"/>
+      <c r="B98" s="60" t="n"/>
+      <c r="C98" s="61" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="59" t="n"/>
+      <c r="B99" s="60" t="n"/>
+      <c r="C99" s="61" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="59" t="n"/>
+      <c r="B100" s="60" t="n"/>
+      <c r="C100" s="61" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="59" t="n"/>
+      <c r="B101" s="60" t="n"/>
+      <c r="C101" s="61" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="59" t="n"/>
+      <c r="B102" s="60" t="n"/>
+      <c r="C102" s="61" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Data tidak valid" error="Kosongkan untuk kelas baru. Pertahankan ID untuk mengedit kelas." promptTitle="ID kelas" prompt="Kosongkan untuk kelas baru. Pertahankan ID untuk mengedit kelas." type="custom" errorStyle="stop" operator="between">
+      <formula1>OR(A2="",AND(ISNUMBER(A2),A2=INT(A2),A2&gt;=1,COUNTIF($A$2:$A$1048576,A2)=1))</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Data tidak valid" error="Isi bilangan bulat antara 1 dan 20." promptTitle="Jenjang" prompt="Isi bilangan bulat antara 1 dan 20." type="whole" errorStyle="stop" operator="between">
+      <formula1>1</formula1>
+      <formula2>20</formula2>
+    </dataValidation>
+    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Data tidak valid" error="Isi 1–20 karakter. Kombinasi jenjang dan nama kelas harus unik." promptTitle="Nama kelas" prompt="Isi 1–20 karakter. Kombinasi jenjang dan nama kelas harus unik." type="custom" errorStyle="stop" operator="between">
+      <formula1>OR(C2="",AND(LEN(C2)&gt;=1,LEN(C2)&lt;=20,COUNTIFS($B$2:$B$1048576,B2,$C$2:$C$1048576,C2)=1))</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/web/app/spreadsheet_templates/students_export_template.xlsx
+++ b/web/app/spreadsheet_templates/students_export_template.xlsx
@@ -1152,7 +1152,7 @@
       <c r="A17" s="23" t="n"/>
       <c r="B17" s="62" t="inlineStr">
         <is>
-          <t>Jangan mengganti nama sheet atau judul kolom. ID siswa mengidentifikasi siswa; ID KELAS mengidentifikasi kelas. ID dilindungi dan tidak boleh diubah. Di students, ID kelas disembunyikan sebagai metadata internal; Anda tidak perlu mengetahui atau mengeditnya.</t>
+          <t>Jangan mengganti nama sheet, judul kolom, ID siswa, atau ID kelas yang sudah ada. ID kelas adalah identitas tetap meskipun jenjang/nama kelas berubah. ID siswa dan ID pada classes dilindungi. Pada students, ID KELAS dapat diketik untuk menentukan kelas siswa.</t>
         </is>
       </c>
       <c r="C17" s="63" t="n"/>
@@ -1180,7 +1180,7 @@
       <c r="A20" s="23" t="n"/>
       <c r="B20" s="53" t="inlineStr">
         <is>
-          <t>Menentukan kelas siswa</t>
+          <t>Menentukan kelas siswa dengan ID</t>
         </is>
       </c>
       <c r="C20" s="28" t="n"/>
@@ -1194,7 +1194,7 @@
       <c r="A21" s="23" t="n"/>
       <c r="B21" s="65" t="inlineStr">
         <is>
-          <t>Di students, pilih JENJANG dan NAMA KELAS melalui dropdown. Pilihan berasal dari classes. Untuk siswa baru, keduanya wajib diisi dan kelas harus tercantum pada classes. Untuk siswa lama, kosongkan kedua nilai jika ingin melepas kelas. Nilai yang hanya terisi sebagian ditolak.</t>
+          <t>Ketik ID KELAS dari classes, misalnya 17 atau N2; kolom ini tidak memiliki dropdown. Validasi memeriksa apakah ID tersebut ada. JENJANG dan NAMA KELAS adalah kolom rumus yang dikunci dan diberi tampilan berbeda. Ubah kedua nilai itu hanya pada classes. Siswa baru wajib memiliki kelas; siswa lama boleh dikosongkan ID kelasnya.</t>
         </is>
       </c>
       <c r="C21" s="41" t="n"/>
@@ -1221,7 +1221,7 @@
       <c r="A24" s="23" t="n"/>
       <c r="B24" s="53" t="inlineStr">
         <is>
-          <t>Membuat kelas hanya melalui classes</t>
+          <t>Kelas baru: ID sementara yang tetap</t>
         </is>
       </c>
       <c r="C24" s="28" t="n"/>
@@ -1231,17 +1231,17 @@
       <c r="G24" s="28" t="n"/>
       <c r="H24" s="26" t="n"/>
     </row>
-    <row r="25" ht="74" customHeight="1" s="22">
+    <row r="25" ht="90" customHeight="1" s="22">
       <c r="B25" s="29" t="inlineStr">
         <is>
-          <t>Tambahkan baris pada classes dengan ID KELAS kosong, lalu isi JENJANG dan NAMA KELAS. Siswa dapat merujuk pasangan itu dalam impor yang sama. Satu kelas baru akan dipakai bersama oleh semua siswa yang merujuknya. Salah ketik pada students tidak akan membuat kelas baru.</t>
+          <t>Absensa menyediakan 100 baris baru dengan ID tetap N1–N100. Isi JENJANG dan NAMA KELAS pada baris tersebut, lalu gunakan ID N itu pada students. ID sudah dialokasikan sebagai nilai tetap, bukan rumus nomor baris, sehingga tidak berubah saat baris lain diedit, dipindah, disisipkan, atau dihapus. Baris cadangan yang belum diisi diabaikan.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" s="22">
       <c r="B28" s="53" t="inlineStr">
         <is>
-          <t>Mengganti nama atau jenjang kelas</t>
+          <t>Rumus langsung mengikuti perubahan kelas</t>
         </is>
       </c>
       <c r="C28" s="28" t="n"/>
@@ -1254,7 +1254,7 @@
     <row r="29" ht="86" customHeight="1" s="22">
       <c r="B29" s="29" t="inlineStr">
         <is>
-          <t>Edit JENJANG dan/atau NAMA KELAS pada classes dengan mempertahankan ID yang dilindungi. Contoh: 10 / IPA 1 menjadi 10 / IPA A. Siswa tetap mengikuti kelas yang sama meskipun nilai lama di students belum diedit; tidak perlu mengubah setiap siswa. Untuk memindahkan siswa, ubah pasangan jenjang dan nama kelasnya ke kelas lain yang tercantum pada classes.</t>
+          <t>Contoh: N1 | 10 | X RPL 1 diubah menjadi N1 | 10 | X RPL A pada classes. Siswa dengan ID KELAS N1 langsung menampilkan nama X RPL A melalui VLOOKUP setelah spreadsheet menghitung ulang. ID tidak berubah. Saat impor, Absensa membuat kelas baru, memperoleh ID database, lalu menghubungkan semua siswa yang memakai N1 ke kelas itu.</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
     <row r="44" ht="24" customHeight="1" s="22">
       <c r="B44" s="53" t="inlineStr">
         <is>
-          <t>Pilihan Excel dan baris baru</t>
+          <t>Tanpa makro; finalisasi ID saat impor</t>
         </is>
       </c>
       <c r="C44" s="28" t="n"/>
@@ -1331,10 +1331,10 @@
       <c r="G44" s="28" t="n"/>
       <c r="H44" s="26" t="n"/>
     </row>
-    <row r="45" ht="86" customHeight="1" s="22">
+    <row r="45" ht="100" customHeight="1" s="22">
       <c r="B45" s="29" t="inlineStr">
         <is>
-          <t>Dropdown memakai jenjang dan nama kelas dari classes saat file dibuat. Jika kelas baru belum muncul di pilihan, ketik nilainya setelah menambahkannya pada classes. Kombinasi jenjang dan nama kelas harus unik; jenjang 1–20 dan nama maksimal 20 karakter. Kolom data dapat diedit; ID dan metadata dilindungi. Tersedia 100 baris entri kosong. Simpan sebagai .xlsx tanpa makro.</t>
+          <t>XLSX tanpa makro tidak dapat membuat ID otomatis saat pengisian lalu mengingatnya secara permanen. Karena itu ID N dialokasikan saat file dibuat dan difinalisasi oleh Absensa saat impor. Jika 100 baris habis, impor lalu unduh ulang untuk mendapat cadangan baru. Baris kelas tanpa ID tetap dapat diimpor, tetapi baru dapat dirujuk siswa setelah diekspor ulang. Jangan menimpa rumus siswa dengan nilai manual.</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
     <col width="28.38" customWidth="1" style="45" min="5" max="5"/>
     <col width="15.89" customWidth="1" style="22" min="6" max="6"/>
     <col width="34.06" customWidth="1" style="22" min="7" max="7"/>
-    <col hidden="1" width="15.89" customWidth="1" style="44" min="8" max="8"/>
+    <col width="15.89" customWidth="1" style="44" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1" s="22">

--- a/web/app/spreadsheet_templates/students_export_template.xlsx
+++ b/web/app/spreadsheet_templates/students_export_template.xlsx
@@ -12,7 +12,7 @@
     <sheet name="classes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'instructions'!$A$1:$H$48</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'instructions'!$B$2:$H$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Arial"/>
       <charset val="1"/>
@@ -93,6 +93,13 @@
       <family val="0"/>
       <color rgb="FF667370"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="9">
@@ -401,7 +408,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -575,6 +582,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
       <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="6" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="20">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="20">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="20">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="8" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="20">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="8" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -708,22 +754,32 @@
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Isi ID kelas yang sudah ada, atau kosongkan jika belum memiliki kelas.</t>
+        <t>Tepat 10 digit. Nol di depan harus dipertahankan. NISN harus unik.</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>Tepat 10 digit. Nol di depan harus dipertahankan. NISN harus unik.</t>
+        <t>Pilih Aktif atau Tidak aktif.</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>Pilih Aktif atau Tidak aktif.</t>
+        <t>Opsional. Angka saja, diawali 08 atau 628; maksimal 32 digit.</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
-        <t>Opsional. Angka saja, diawali 08 atau 628; maksimal 32 digit.</t>
+        <t>Ketik ID dari sheet classes, termasuk ID sementara N1, N2, dan seterusnya. Tidak ada dropdown.</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Kolom rumus, hanya baca. Nilai mengikuti ID KELAS.</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>Kolom rumus, hanya baca. Ubah nama kelas pada sheet classes.</t>
       </text>
     </comment>
   </commentList>
@@ -739,9 +795,9 @@
     <tableColumn id="3" name="NISN"/>
     <tableColumn id="4" name="STATUS"/>
     <tableColumn id="5" name="NOMOR WALI"/>
-    <tableColumn id="6" name="JENJANG"/>
-    <tableColumn id="7" name="NAMA KELAS"/>
-    <tableColumn id="8" name="ID KELAS"/>
+    <tableColumn id="6" name="ID KELAS"/>
+    <tableColumn id="7" name="JENJANG"/>
+    <tableColumn id="8" name="NAMA KELAS"/>
   </tableColumns>
 </table>
 </file>
@@ -956,7 +1012,7 @@
       <c r="A2" s="23" t="n"/>
       <c r="B2" s="24" t="inlineStr">
         <is>
-          <t>Ekspor &amp; Impor Siswa dan Kelas</t>
+          <t>Panduan Ekspor dan Impor Siswa</t>
         </is>
       </c>
       <c r="G2" s="25" t="inlineStr">
@@ -976,11 +1032,11 @@
       <c r="G3" s="23" t="n"/>
       <c r="H3" s="23" t="n"/>
     </row>
-    <row r="4" ht="23" customHeight="1" s="22">
+    <row r="4" ht="29" customHeight="1" s="22">
       <c r="A4" s="23" t="n"/>
-      <c r="B4" s="27" t="inlineStr">
-        <is>
-          <t>Tentang file ini</t>
+      <c r="B4" s="66" t="inlineStr">
+        <is>
+          <t>Dokumentasi lengkap: https://example.com</t>
         </is>
       </c>
       <c r="C4" s="28" t="n"/>
@@ -992,17 +1048,13 @@
     </row>
     <row r="5" ht="34" customHeight="1" s="22">
       <c r="A5" s="23" t="n"/>
-      <c r="B5" s="29" t="inlineStr">
-        <is>
-          <t>Workbook ini dibuat oleh Absensa untuk ekspor serta penyuntingan massal dan impor kembali.</t>
-        </is>
-      </c>
+      <c r="B5" s="29" t="n"/>
     </row>
     <row r="6" ht="23" customHeight="1" s="22">
       <c r="A6" s="23" t="n"/>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>Filter</t>
+          <t>Filter siswa</t>
         </is>
       </c>
       <c r="C6" s="26" t="n"/>
@@ -1020,11 +1072,11 @@
       <c r="A7" s="23" t="n"/>
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>Waktu ekspor</t>
+          <t>Waktu dibuat</t>
         </is>
       </c>
       <c r="C7" s="26" t="n"/>
-      <c r="D7" s="32" t="inlineStr">
+      <c r="D7" s="31" t="inlineStr">
         <is>
           <t>{{ exported_at }}</t>
         </is>
@@ -1038,11 +1090,11 @@
       <c r="A8" s="23" t="n"/>
       <c r="B8" s="30" t="inlineStr">
         <is>
-          <t>Jumlah data</t>
+          <t>Jumlah siswa</t>
         </is>
       </c>
       <c r="C8" s="26" t="n"/>
-      <c r="D8" s="32" t="inlineStr">
+      <c r="D8" s="31" t="inlineStr">
         <is>
           <t>{{ row_count }}</t>
         </is>
@@ -1054,75 +1106,56 @@
     </row>
     <row r="9" ht="23" customHeight="1" s="22">
       <c r="A9" s="23" t="n"/>
-      <c r="B9" s="30" t="inlineStr">
-        <is>
-          <t>Sheet data</t>
-        </is>
-      </c>
-      <c r="C9" s="26" t="n"/>
-      <c r="D9" s="32" t="inlineStr">
-        <is>
-          <t>students dan classes</t>
-        </is>
-      </c>
-      <c r="E9" s="28" t="n"/>
-      <c r="F9" s="28" t="n"/>
-      <c r="G9" s="28" t="n"/>
-      <c r="H9" s="26" t="n"/>
-    </row>
-    <row r="10" ht="23" customHeight="1" s="22">
+      <c r="B9" s="30" t="n"/>
+      <c r="D9" s="32" t="n"/>
+    </row>
+    <row r="10" ht="25" customHeight="1" s="22">
       <c r="A10" s="23" t="n"/>
-      <c r="B10" s="30" t="inlineStr">
-        <is>
-          <t>Kolom ID</t>
-        </is>
-      </c>
-      <c r="C10" s="26" t="n"/>
-      <c r="D10" s="33" t="inlineStr">
-        <is>
-          <t>ID siswa dan ID KELAS (dilindungi)</t>
-        </is>
-      </c>
+      <c r="B10" s="67" t="inlineStr">
+        <is>
+          <t>Tentang file ini</t>
+        </is>
+      </c>
+      <c r="C10" s="28" t="n"/>
+      <c r="D10" s="28" t="n"/>
       <c r="E10" s="28" t="n"/>
       <c r="F10" s="28" t="n"/>
       <c r="G10" s="28" t="n"/>
       <c r="H10" s="26" t="n"/>
     </row>
-    <row r="11" ht="15" customHeight="1" s="22">
+    <row r="11" ht="72" customHeight="1" s="22">
       <c r="A11" s="23" t="n"/>
-      <c r="B11" s="23" t="n"/>
-      <c r="C11" s="23" t="n"/>
-      <c r="D11" s="23" t="n"/>
-      <c r="E11" s="23" t="n"/>
-      <c r="F11" s="23" t="n"/>
-      <c r="G11" s="23" t="n"/>
-      <c r="H11" s="23" t="n"/>
+      <c r="B11" s="68" t="inlineStr">
+        <is>
+          <t>Workbook ini dibuat oleh Absensa untuk mengunduh data siswa dan mengimpor data untuk menambah atau mengedit siswa. Anda bisa mendapatkannya dari template impor atau melalui Ekspor di dashboard Siswa maupun dashboard Kelas. Data siswa pada hasil ekspor mengikuti filter yang dipilih; sheet classes selalu memuat semua kelas.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="24" customHeight="1" s="22">
       <c r="A12" s="23" t="n"/>
-      <c r="B12" s="53" t="inlineStr">
-        <is>
-          <t>Isi workbook</t>
-        </is>
-      </c>
-      <c r="C12" s="28" t="n"/>
-      <c r="D12" s="28" t="n"/>
-      <c r="E12" s="28" t="n"/>
-      <c r="F12" s="28" t="n"/>
-      <c r="G12" s="28" t="n"/>
-      <c r="H12" s="26" t="n"/>
-    </row>
-    <row r="13" ht="62" customHeight="1" s="22">
+      <c r="B12" s="53" t="n"/>
+    </row>
+    <row r="13" ht="25" customHeight="1" s="22">
       <c r="A13" s="23" t="n"/>
-      <c r="B13" s="29" t="inlineStr">
-        <is>
-          <t>students berisi data siswa sesuai filter ekspor di atas. classes selalu berisi seluruh kelas dari semua jenjang, tanpa mengikuti filter siswa, dan menjadi sumber pilihan dropdown.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="34" customHeight="1" s="22">
+      <c r="B13" s="67" t="inlineStr">
+        <is>
+          <t>Sebelum mengedit</t>
+        </is>
+      </c>
+      <c r="C13" s="28" t="n"/>
+      <c r="D13" s="28" t="n"/>
+      <c r="E13" s="28" t="n"/>
+      <c r="F13" s="28" t="n"/>
+      <c r="G13" s="28" t="n"/>
+      <c r="H13" s="26" t="n"/>
+    </row>
+    <row r="14" ht="72" customHeight="1" s="22">
       <c r="A14" s="23" t="n"/>
-      <c r="B14" s="29" t="n"/>
+      <c r="B14" s="68" t="inlineStr">
+        <is>
+          <t>Jika ingin mengedit siswa yang sudah ada, sebaiknya mulai dari Ekspor pada dashboard Siswa atau Kelas. Hasil ekspor sudah memuat ID dan data siswa saat ini. Pertahankan nilai pada kolom ID (student_id) agar perubahan masuk ke siswa yang benar, lalu lengkapi nilai yang diperlukan; sel kosong tidak berarti nilai lama akan dipertahankan.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="22">
       <c r="A15" s="23" t="n"/>
@@ -1134,11 +1167,11 @@
       <c r="G15" s="23" t="n"/>
       <c r="H15" s="23" t="n"/>
     </row>
-    <row r="16" ht="24" customHeight="1" s="22">
+    <row r="16" ht="25" customHeight="1" s="22">
       <c r="A16" s="23" t="n"/>
-      <c r="B16" s="53" t="inlineStr">
-        <is>
-          <t>Jangan mengubah identitas</t>
+      <c r="B16" s="67" t="inlineStr">
+        <is>
+          <t>Menambah siswa baru</t>
         </is>
       </c>
       <c r="C16" s="28" t="n"/>
@@ -1148,11 +1181,11 @@
       <c r="G16" s="28" t="n"/>
       <c r="H16" s="26" t="n"/>
     </row>
-    <row r="17" ht="62" customHeight="1" s="22">
+    <row r="17" ht="57" customHeight="1" s="22">
       <c r="A17" s="23" t="n"/>
-      <c r="B17" s="62" t="inlineStr">
-        <is>
-          <t>Jangan mengganti nama sheet, judul kolom, ID siswa, atau ID kelas yang sudah ada. ID kelas adalah identitas tetap meskipun jenjang/nama kelas berubah. ID siswa dan ID pada classes dilindungi. Pada students, ID KELAS dapat diketik untuk menentukan kelas siswa.</t>
+      <c r="B17" s="69" t="inlineStr">
+        <is>
+          <t>Untuk siswa baru, biarkan kolom ID (student_id) kosong lalu isi data pada satu baris. NISN harus tepat 10 digit; gunakan format teks agar angka nol di depan tetap ada. Pilih STATUS dari daftar yang tersedia. Isi ID KELAS (class_id) pada sel kosong dengan ID dari sheet classes, termasuk ID sementara seperti N1.</t>
         </is>
       </c>
       <c r="C17" s="63" t="n"/>
@@ -1166,82 +1199,88 @@
       <c r="A18" s="23" t="n"/>
       <c r="B18" s="34" t="n"/>
     </row>
-    <row r="19" ht="15" customHeight="1" s="22">
+    <row r="19" ht="25" customHeight="1" s="22">
       <c r="A19" s="23" t="n"/>
-      <c r="B19" s="23" t="n"/>
-      <c r="C19" s="23" t="n"/>
-      <c r="D19" s="23" t="n"/>
-      <c r="E19" s="23" t="n"/>
-      <c r="F19" s="23" t="n"/>
-      <c r="G19" s="23" t="n"/>
-      <c r="H19" s="23" t="n"/>
-    </row>
-    <row r="20" ht="24" customHeight="1" s="22">
+      <c r="B19" s="67" t="inlineStr">
+        <is>
+          <t>Mengedit siswa yang sudah ada</t>
+        </is>
+      </c>
+      <c r="C19" s="28" t="n"/>
+      <c r="D19" s="28" t="n"/>
+      <c r="E19" s="28" t="n"/>
+      <c r="F19" s="28" t="n"/>
+      <c r="G19" s="28" t="n"/>
+      <c r="H19" s="26" t="n"/>
+    </row>
+    <row r="20" ht="72" customHeight="1" s="22">
       <c r="A20" s="23" t="n"/>
-      <c r="B20" s="53" t="inlineStr">
-        <is>
-          <t>Menentukan kelas siswa dengan ID</t>
-        </is>
-      </c>
-      <c r="C20" s="28" t="n"/>
-      <c r="D20" s="28" t="n"/>
-      <c r="E20" s="28" t="n"/>
-      <c r="F20" s="28" t="n"/>
-      <c r="G20" s="28" t="n"/>
-      <c r="H20" s="26" t="n"/>
+      <c r="B20" s="70" t="inlineStr">
+        <is>
+          <t>Jika kolom ID (student_id) berisi ID siswa yang sudah terdaftar, baris itu akan mengubah data siswa tersebut. Jangan mengganti ID yang sudah ada secara tidak sengaja. Spreadsheet dapat memeriksa format, tetapi tidak dapat memastikan ID benar-benar ada di sistem. Absensa memeriksanya kembali saat impor dan akan melaporkan jika ID tidak ditemukan.</t>
+        </is>
+      </c>
+      <c r="C20" s="41" t="n"/>
+      <c r="D20" s="41" t="n"/>
+      <c r="E20" s="41" t="n"/>
+      <c r="F20" s="41" t="n"/>
+      <c r="G20" s="41" t="n"/>
+      <c r="H20" s="42" t="n"/>
     </row>
     <row r="21" ht="62" customHeight="1" s="22">
       <c r="A21" s="23" t="n"/>
-      <c r="B21" s="65" t="inlineStr">
-        <is>
-          <t>Ketik ID KELAS dari classes, misalnya 17 atau N2; kolom ini tidak memiliki dropdown. Validasi memeriksa apakah ID tersebut ada. JENJANG dan NAMA KELAS adalah kolom rumus yang dikunci dan diberi tampilan berbeda. Ubah kedua nilai itu hanya pada classes. Siswa baru wajib memiliki kelas; siswa lama boleh dikosongkan ID kelasnya.</t>
-        </is>
-      </c>
-      <c r="C21" s="41" t="n"/>
-      <c r="D21" s="41" t="n"/>
-      <c r="E21" s="41" t="n"/>
-      <c r="F21" s="41" t="n"/>
-      <c r="G21" s="41" t="n"/>
-      <c r="H21" s="42" t="n"/>
-    </row>
-    <row r="22" ht="30" customHeight="1" s="22">
+      <c r="B21" s="65" t="n"/>
+    </row>
+    <row r="22" ht="25" customHeight="1" s="22">
       <c r="A22" s="23" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="22">
+      <c r="B22" s="67" t="inlineStr">
+        <is>
+          <t>Kelas dan ID sementara</t>
+        </is>
+      </c>
+      <c r="C22" s="28" t="n"/>
+      <c r="D22" s="28" t="n"/>
+      <c r="E22" s="28" t="n"/>
+      <c r="F22" s="28" t="n"/>
+      <c r="G22" s="28" t="n"/>
+      <c r="H22" s="26" t="n"/>
+    </row>
+    <row r="23" ht="84" customHeight="1" s="22">
       <c r="A23" s="23" t="n"/>
-      <c r="B23" s="23" t="n"/>
-      <c r="C23" s="23" t="n"/>
-      <c r="D23" s="23" t="n"/>
-      <c r="E23" s="23" t="n"/>
-      <c r="F23" s="23" t="n"/>
-      <c r="G23" s="23" t="n"/>
-      <c r="H23" s="23" t="n"/>
+      <c r="B23" s="68" t="inlineStr">
+        <is>
+          <t>Isi ID KELAS (class_id) pada sel kosong untuk menentukan kelas siswa. ID kelas yang sudah terisi pada data ekspor dilindungi; sel kosong disediakan untuk pengisian siswa baru. Untuk kelas baru, gunakan baris cadangan di sheet classes yang sudah berisi ID seperti N1, N2, dan seterusnya: isi jenjang serta nama kelas pada baris itu, lalu gunakan ID N yang sama pada siswa baru. Absensa menyelesaikan ID sementara saat impor. Mengubah nama atau jenjang kelas pada baris ber-ID tetap akan memperbarui kelas tersebut.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="24" customHeight="1" s="22">
       <c r="A24" s="23" t="n"/>
-      <c r="B24" s="53" t="inlineStr">
-        <is>
-          <t>Kelas baru: ID sementara yang tetap</t>
-        </is>
-      </c>
-      <c r="C24" s="28" t="n"/>
-      <c r="D24" s="28" t="n"/>
-      <c r="E24" s="28" t="n"/>
-      <c r="F24" s="28" t="n"/>
-      <c r="G24" s="28" t="n"/>
-      <c r="H24" s="26" t="n"/>
-    </row>
-    <row r="25" ht="90" customHeight="1" s="22">
-      <c r="B25" s="29" t="inlineStr">
-        <is>
-          <t>Absensa menyediakan 100 baris baru dengan ID tetap N1–N100. Isi JENJANG dan NAMA KELAS pada baris tersebut, lalu gunakan ID N itu pada students. ID sudah dialokasikan sebagai nilai tetap, bukan rumus nomor baris, sehingga tidak berubah saat baris lain diedit, dipindah, disisipkan, atau dihapus. Baris cadangan yang belum diisi diabaikan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1" s="22">
-      <c r="B28" s="53" t="inlineStr">
-        <is>
-          <t>Rumus langsung mengikuti perubahan kelas</t>
+      <c r="B24" s="53" t="n"/>
+    </row>
+    <row r="25" ht="25" customHeight="1" s="22">
+      <c r="B25" s="67" t="inlineStr">
+        <is>
+          <t>Sel yang dilindungi dan pilihan isian</t>
+        </is>
+      </c>
+      <c r="C25" s="28" t="n"/>
+      <c r="D25" s="28" t="n"/>
+      <c r="E25" s="28" t="n"/>
+      <c r="F25" s="28" t="n"/>
+      <c r="G25" s="28" t="n"/>
+      <c r="H25" s="26" t="n"/>
+    </row>
+    <row r="26" ht="72" customHeight="1" s="22">
+      <c r="B26" s="68" t="inlineStr">
+        <is>
+          <t>Kolom JENJANG dan NAMA KELAS mengikuti ID KELAS (class_id) secara otomatis dan tidak untuk diedit. Ubah informasi kelas pada sheet classes. Proteksi dan daftar pilihan membantu mencegah perubahan yang membuat impor bermasalah. Jangan membuka proteksi, menghapus validasi, mengganti nama sheet atau judul kolom, maupun mengubah susunan workbook jika file akan diimpor kembali.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="25" customHeight="1" s="22">
+      <c r="B28" s="67" t="inlineStr">
+        <is>
+          <t>Jika baris tidak cukup</t>
         </is>
       </c>
       <c r="C28" s="28" t="n"/>
@@ -1251,57 +1290,89 @@
       <c r="G28" s="28" t="n"/>
       <c r="H28" s="26" t="n"/>
     </row>
-    <row r="29" ht="86" customHeight="1" s="22">
-      <c r="B29" s="29" t="inlineStr">
-        <is>
-          <t>Contoh: N1 | 10 | X RPL 1 diubah menjadi N1 | 10 | X RPL A pada classes. Siswa dengan ID KELAS N1 langsung menampilkan nama X RPL A melalui VLOOKUP setelah spreadsheet menghitung ulang. ID tidak berubah. Saat impor, Absensa membuat kelas baru, memperoleh ID database, lalu menghubungkan semua siswa yang memakai N1 ke kelas itu.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="24" customHeight="1" s="22">
-      <c r="B32" s="53" t="inlineStr">
-        <is>
-          <t>Menghapus baris BUKAN menghapus kelas</t>
-        </is>
-      </c>
-      <c r="C32" s="28" t="n"/>
-      <c r="D32" s="28" t="n"/>
-      <c r="E32" s="28" t="n"/>
-      <c r="F32" s="28" t="n"/>
-      <c r="G32" s="28" t="n"/>
-      <c r="H32" s="26" t="n"/>
+    <row r="29" ht="57" customHeight="1" s="22">
+      <c r="B29" s="68" t="inlineStr">
+        <is>
+          <t>Template biasanya menyediakan sekitar 100 baris siap isi. Jika habis, unduh template baru dari server, atau salin sheet siswa yang masih sesuai lalu lanjutkan pengisian di sheet salinan itu. Sheet salinan boleh diberi nama apa pun. Pertahankan kolom, validasi, dan proteksinya agar tetap dapat dikenali saat impor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="25" customHeight="1" s="22">
+      <c r="B31" s="67" t="inlineStr">
+        <is>
+          <t>Mengimpor beberapa file dengan ZIP</t>
+        </is>
+      </c>
+      <c r="C31" s="28" t="n"/>
+      <c r="D31" s="28" t="n"/>
+      <c r="E31" s="28" t="n"/>
+      <c r="F31" s="28" t="n"/>
+      <c r="G31" s="28" t="n"/>
+      <c r="H31" s="26" t="n"/>
+    </row>
+    <row r="32" ht="57" customHeight="1" s="22">
+      <c r="B32" s="70" t="inlineStr">
+        <is>
+          <t>Impor menerima satu file .xlsx atau arsip seperti .zip, .rar, .7z, atau .tar yang berisi satu atau beberapa file .xlsx. Jika data dibagi ke beberapa workbook, masukkan semua file Excel ke dalam satu ZIP lalu unggah ZIP tersebut melalui fitur impor massal.</t>
+        </is>
+      </c>
+      <c r="C32" s="41" t="n"/>
+      <c r="D32" s="41" t="n"/>
+      <c r="E32" s="41" t="n"/>
+      <c r="F32" s="41" t="n"/>
+      <c r="G32" s="41" t="n"/>
+      <c r="H32" s="42" t="n"/>
     </row>
     <row r="33" ht="62" customHeight="1" s="22">
-      <c r="B33" s="29" t="inlineStr">
-        <is>
-          <t>Menghapus baris kelas hanya menghapusnya dari workbook dan pilihan kelasnya, bukan dari Absensa. Siswa yang masih merujuk kelas tersebut perlu disesuaikan atau baris kelas dikembalikan. Penghapusan kelas dari database dilakukan secara eksplisit melalui halaman/dashboard Kelas.</t>
+      <c r="B33" s="29" t="n"/>
+    </row>
+    <row r="34" ht="25" customHeight="1" s="22">
+      <c r="B34" s="67" t="inlineStr">
+        <is>
+          <t>Menambahkan atau mengganti foto siswa</t>
+        </is>
+      </c>
+      <c r="C34" s="28" t="n"/>
+      <c r="D34" s="28" t="n"/>
+      <c r="E34" s="28" t="n"/>
+      <c r="F34" s="28" t="n"/>
+      <c r="G34" s="28" t="n"/>
+      <c r="H34" s="26" t="n"/>
+    </row>
+    <row r="35" ht="72" customHeight="1" s="22">
+      <c r="B35" s="68" t="inlineStr">
+        <is>
+          <t>Foto bersifat opsional. Untuk mengirim foto, masukkan file Excel dan folder bernama persis photos/ ke dalam ZIP. Nama file foto harus memakai NISN 10 digit, misalnya photos/0081234567.jpg. Format yang diterima: .jpg, .jpeg, .png, atau .webp. Foto dicocokkan dengan NISN, bukan student_id, dan dapat dipakai untuk siswa baru maupun yang sudah ada jika data siswanya ikut diimpor.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="24" customHeight="1" s="22">
-      <c r="B36" s="53" t="inlineStr">
-        <is>
-          <t>Impor bersifat semua-atau-tidak-sama-sekali</t>
-        </is>
-      </c>
-      <c r="C36" s="28" t="n"/>
-      <c r="D36" s="28" t="n"/>
-      <c r="E36" s="28" t="n"/>
-      <c r="F36" s="28" t="n"/>
-      <c r="G36" s="28" t="n"/>
-      <c r="H36" s="26" t="n"/>
-    </row>
-    <row r="37" ht="62" customHeight="1" s="22">
-      <c r="B37" s="29" t="inlineStr">
-        <is>
-          <t>Absensa memvalidasi seluruh workbook sebelum menyimpan apa pun. Jika satu baris saja salah, seluruh impor ditolak: tidak ada siswa yang diubah dan tidak ada kelas yang diubah atau dibuat. Perbaiki semua kesalahan yang dilaporkan, lalu impor kembali.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="24" customHeight="1" s="22">
-      <c r="B40" s="53" t="inlineStr">
-        <is>
-          <t>Mengisi data siswa</t>
+      <c r="B36" s="53" t="n"/>
+    </row>
+    <row r="37" ht="25" customHeight="1" s="22">
+      <c r="B37" s="67" t="inlineStr">
+        <is>
+          <t>Jika impor gagal</t>
+        </is>
+      </c>
+      <c r="C37" s="28" t="n"/>
+      <c r="D37" s="28" t="n"/>
+      <c r="E37" s="28" t="n"/>
+      <c r="F37" s="28" t="n"/>
+      <c r="G37" s="28" t="n"/>
+      <c r="H37" s="26" t="n"/>
+    </row>
+    <row r="38" ht="57" customHeight="1" s="22">
+      <c r="B38" s="68" t="inlineStr">
+        <is>
+          <t>Absensa memeriksa seluruh data sebelum menyimpan perubahan. Impor berlaku semua-atau-tidak-sama-sekali: jika ada data atau file yang tidak valid, seluruh impor ditolak dan tidak ada siswa atau kelas yang disimpan sebagian. Baca laporan kesalahan, perbaiki file, lalu unggah kembali.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="25" customHeight="1" s="22">
+      <c r="B40" s="67" t="inlineStr">
+        <is>
+          <t>Menggunakan data di luar Absensa</t>
         </is>
       </c>
       <c r="C40" s="28" t="n"/>
@@ -1311,68 +1382,56 @@
       <c r="G40" s="28" t="n"/>
       <c r="H40" s="26" t="n"/>
     </row>
-    <row r="41" ht="62" customHeight="1" s="22">
-      <c r="B41" s="29" t="inlineStr">
-        <is>
-          <t>Pertahankan ID siswa untuk pembaruan; kosongkan ID untuk siswa baru. NISN wajib tepat 10 digit dan disimpan sebagai teks agar nol di depan tidak hilang. STATUS: Aktif atau Tidak aktif. NOMOR WALI opsional, angka saja diawali 08 atau 628, maksimal 32 digit. Baris kosong diabaikan.</t>
+    <row r="41" ht="57" customHeight="1" s="22">
+      <c r="B41" s="68" t="inlineStr">
+        <is>
+          <t>Data hasil ekspor boleh digunakan untuk keperluan administrasi sekolah lainnya, seperti menyiapkan rapor atau mengolah data di sistem lain. Silakan salin dan olah data sesuai kebutuhan. Jika file akan diimpor kembali ke Absensa, pertahankan struktur, ID yang diperlukan, sel terlindungi, dan validasi yang tersedia.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1" s="22">
-      <c r="B44" s="53" t="inlineStr">
-        <is>
-          <t>Tanpa makro; finalisasi ID saat impor</t>
-        </is>
-      </c>
-      <c r="C44" s="28" t="n"/>
-      <c r="D44" s="28" t="n"/>
-      <c r="E44" s="28" t="n"/>
-      <c r="F44" s="28" t="n"/>
-      <c r="G44" s="28" t="n"/>
-      <c r="H44" s="26" t="n"/>
+      <c r="B44" s="53" t="n"/>
     </row>
     <row r="45" ht="100" customHeight="1" s="22">
-      <c r="B45" s="29" t="inlineStr">
-        <is>
-          <t>XLSX tanpa makro tidak dapat membuat ID otomatis saat pengisian lalu mengingatnya secara permanen. Karena itu ID N dialokasikan saat file dibuat dan difinalisasi oleh Absensa saat impor. Jika 100 baris habis, impor lalu unduh ulang untuk mendapat cadangan baru. Baris kelas tanpa ID tetap dapat diimpor, tetapi baru dapat dirujuk siswa setelah diekspor ulang. Jangan menimpa rumus siswa dengan nilai manual.</t>
-        </is>
-      </c>
+      <c r="B45" s="29" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="32">
+  <mergeCells count="31">
     <mergeCell ref="B40:H40"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="G2:H2"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="B24:H24"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B5:H5"/>
     <mergeCell ref="B20:H20"/>
-    <mergeCell ref="B45:H45"/>
-    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="B37:H37"/>
     <mergeCell ref="B32:H32"/>
     <mergeCell ref="D6:H6"/>
+    <mergeCell ref="B26:H26"/>
     <mergeCell ref="B41:H41"/>
     <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B35:H35"/>
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="B16:H16"/>
     <mergeCell ref="B25:H25"/>
     <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B31:H31"/>
+    <mergeCell ref="B22:H22"/>
     <mergeCell ref="D7:H7"/>
-    <mergeCell ref="B21:H21"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B12:H12"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="B23:H23"/>
     <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B14:H14"/>
     <mergeCell ref="D8:H8"/>
     <mergeCell ref="B17:H17"/>
     <mergeCell ref="B13:H13"/>
-    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="B38:H38"/>
     <mergeCell ref="B29:H29"/>
-    <mergeCell ref="B37:H37"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="B19:H19"/>
+    <mergeCell ref="B34:H34"/>
     <mergeCell ref="B28:H28"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId1"/>
+  </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1395,8 +1454,8 @@
     <col width="15.89" customWidth="1" style="45" min="4" max="4"/>
     <col width="28.38" customWidth="1" style="45" min="5" max="5"/>
     <col width="15.89" customWidth="1" style="22" min="6" max="6"/>
-    <col width="34.06" customWidth="1" style="22" min="7" max="7"/>
-    <col width="15.89" customWidth="1" style="44" min="8" max="8"/>
+    <col width="15.89" customWidth="1" style="22" min="7" max="7"/>
+    <col width="34.06" customWidth="1" style="44" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1" s="22">
@@ -1425,1033 +1484,1034 @@
           <t>NOMOR WALI</t>
         </is>
       </c>
-      <c r="F1" s="48" t="inlineStr">
+      <c r="F1" s="47" t="inlineStr">
+        <is>
+          <t>ID KELAS</t>
+        </is>
+      </c>
+      <c r="G1" s="48" t="inlineStr">
         <is>
           <t>JENJANG</t>
         </is>
       </c>
-      <c r="G1" s="48" t="inlineStr">
+      <c r="H1" s="48" t="inlineStr">
         <is>
           <t>NAMA KELAS</t>
         </is>
       </c>
-      <c r="H1" s="47" t="inlineStr">
-        <is>
-          <t>ID KELAS</t>
-        </is>
-      </c>
     </row>
     <row r="2" ht="24" customHeight="1" s="22">
-      <c r="A2" s="49" t="n"/>
-      <c r="B2" s="50" t="n"/>
-      <c r="C2" s="52" t="n"/>
-      <c r="D2" s="52" t="n"/>
-      <c r="E2" s="52" t="n"/>
-      <c r="F2" s="54" t="n"/>
-      <c r="G2" s="55" t="n"/>
-      <c r="H2" s="51" t="n"/>
+      <c r="A2" s="71" t="n"/>
+      <c r="B2" s="72" t="n"/>
+      <c r="C2" s="73" t="n"/>
+      <c r="D2" s="73" t="n"/>
+      <c r="E2" s="73" t="n"/>
+      <c r="F2" s="74" t="n"/>
+      <c r="G2" s="54" t="n"/>
+      <c r="H2" s="55" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="49" t="n"/>
-      <c r="B3" s="50" t="n"/>
-      <c r="C3" s="52" t="n"/>
-      <c r="D3" s="52" t="n"/>
-      <c r="E3" s="52" t="n"/>
-      <c r="F3" s="52" t="n"/>
+      <c r="A3" s="71" t="n"/>
+      <c r="B3" s="72" t="n"/>
+      <c r="C3" s="73" t="n"/>
+      <c r="D3" s="73" t="n"/>
+      <c r="E3" s="73" t="n"/>
+      <c r="F3" s="74" t="n"/>
       <c r="G3" s="52" t="n"/>
-      <c r="H3" s="51" t="n"/>
+      <c r="H3" s="52" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="49" t="n"/>
-      <c r="B4" s="50" t="n"/>
-      <c r="C4" s="52" t="n"/>
-      <c r="D4" s="52" t="n"/>
-      <c r="E4" s="52" t="n"/>
-      <c r="F4" s="52" t="n"/>
+      <c r="A4" s="71" t="n"/>
+      <c r="B4" s="72" t="n"/>
+      <c r="C4" s="73" t="n"/>
+      <c r="D4" s="73" t="n"/>
+      <c r="E4" s="73" t="n"/>
+      <c r="F4" s="74" t="n"/>
       <c r="G4" s="52" t="n"/>
-      <c r="H4" s="51" t="n"/>
+      <c r="H4" s="52" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="49" t="n"/>
-      <c r="B5" s="50" t="n"/>
-      <c r="C5" s="52" t="n"/>
-      <c r="D5" s="52" t="n"/>
-      <c r="E5" s="52" t="n"/>
-      <c r="F5" s="52" t="n"/>
+      <c r="A5" s="71" t="n"/>
+      <c r="B5" s="72" t="n"/>
+      <c r="C5" s="73" t="n"/>
+      <c r="D5" s="73" t="n"/>
+      <c r="E5" s="73" t="n"/>
+      <c r="F5" s="74" t="n"/>
       <c r="G5" s="52" t="n"/>
-      <c r="H5" s="51" t="n"/>
+      <c r="H5" s="52" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="49" t="n"/>
-      <c r="B6" s="50" t="n"/>
-      <c r="C6" s="52" t="n"/>
-      <c r="D6" s="52" t="n"/>
-      <c r="E6" s="52" t="n"/>
-      <c r="F6" s="52" t="n"/>
+      <c r="A6" s="71" t="n"/>
+      <c r="B6" s="72" t="n"/>
+      <c r="C6" s="73" t="n"/>
+      <c r="D6" s="73" t="n"/>
+      <c r="E6" s="73" t="n"/>
+      <c r="F6" s="74" t="n"/>
       <c r="G6" s="52" t="n"/>
-      <c r="H6" s="51" t="n"/>
+      <c r="H6" s="52" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="49" t="n"/>
-      <c r="B7" s="50" t="n"/>
-      <c r="C7" s="52" t="n"/>
-      <c r="D7" s="52" t="n"/>
-      <c r="E7" s="52" t="n"/>
-      <c r="F7" s="52" t="n"/>
+      <c r="A7" s="71" t="n"/>
+      <c r="B7" s="72" t="n"/>
+      <c r="C7" s="73" t="n"/>
+      <c r="D7" s="73" t="n"/>
+      <c r="E7" s="73" t="n"/>
+      <c r="F7" s="74" t="n"/>
       <c r="G7" s="52" t="n"/>
-      <c r="H7" s="51" t="n"/>
+      <c r="H7" s="52" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="49" t="n"/>
-      <c r="B8" s="50" t="n"/>
-      <c r="C8" s="52" t="n"/>
-      <c r="D8" s="52" t="n"/>
-      <c r="E8" s="52" t="n"/>
-      <c r="F8" s="52" t="n"/>
+      <c r="A8" s="71" t="n"/>
+      <c r="B8" s="72" t="n"/>
+      <c r="C8" s="73" t="n"/>
+      <c r="D8" s="73" t="n"/>
+      <c r="E8" s="73" t="n"/>
+      <c r="F8" s="74" t="n"/>
       <c r="G8" s="52" t="n"/>
-      <c r="H8" s="51" t="n"/>
+      <c r="H8" s="52" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="49" t="n"/>
-      <c r="B9" s="50" t="n"/>
-      <c r="C9" s="52" t="n"/>
-      <c r="D9" s="52" t="n"/>
-      <c r="E9" s="52" t="n"/>
-      <c r="F9" s="52" t="n"/>
+      <c r="A9" s="71" t="n"/>
+      <c r="B9" s="72" t="n"/>
+      <c r="C9" s="73" t="n"/>
+      <c r="D9" s="73" t="n"/>
+      <c r="E9" s="73" t="n"/>
+      <c r="F9" s="74" t="n"/>
       <c r="G9" s="52" t="n"/>
-      <c r="H9" s="51" t="n"/>
+      <c r="H9" s="52" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="49" t="n"/>
-      <c r="B10" s="50" t="n"/>
-      <c r="C10" s="52" t="n"/>
-      <c r="D10" s="52" t="n"/>
-      <c r="E10" s="52" t="n"/>
-      <c r="F10" s="52" t="n"/>
+      <c r="A10" s="71" t="n"/>
+      <c r="B10" s="72" t="n"/>
+      <c r="C10" s="73" t="n"/>
+      <c r="D10" s="73" t="n"/>
+      <c r="E10" s="73" t="n"/>
+      <c r="F10" s="74" t="n"/>
       <c r="G10" s="52" t="n"/>
-      <c r="H10" s="51" t="n"/>
+      <c r="H10" s="52" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="49" t="n"/>
-      <c r="B11" s="50" t="n"/>
-      <c r="C11" s="52" t="n"/>
-      <c r="D11" s="52" t="n"/>
-      <c r="E11" s="52" t="n"/>
-      <c r="F11" s="52" t="n"/>
+      <c r="A11" s="71" t="n"/>
+      <c r="B11" s="72" t="n"/>
+      <c r="C11" s="73" t="n"/>
+      <c r="D11" s="73" t="n"/>
+      <c r="E11" s="73" t="n"/>
+      <c r="F11" s="74" t="n"/>
       <c r="G11" s="52" t="n"/>
-      <c r="H11" s="51" t="n"/>
+      <c r="H11" s="52" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="49" t="n"/>
-      <c r="B12" s="50" t="n"/>
-      <c r="C12" s="52" t="n"/>
-      <c r="D12" s="52" t="n"/>
-      <c r="E12" s="52" t="n"/>
-      <c r="F12" s="52" t="n"/>
+      <c r="A12" s="71" t="n"/>
+      <c r="B12" s="72" t="n"/>
+      <c r="C12" s="73" t="n"/>
+      <c r="D12" s="73" t="n"/>
+      <c r="E12" s="73" t="n"/>
+      <c r="F12" s="74" t="n"/>
       <c r="G12" s="52" t="n"/>
-      <c r="H12" s="51" t="n"/>
+      <c r="H12" s="52" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="49" t="n"/>
-      <c r="B13" s="50" t="n"/>
-      <c r="C13" s="52" t="n"/>
-      <c r="D13" s="52" t="n"/>
-      <c r="E13" s="52" t="n"/>
-      <c r="F13" s="52" t="n"/>
+      <c r="A13" s="71" t="n"/>
+      <c r="B13" s="72" t="n"/>
+      <c r="C13" s="73" t="n"/>
+      <c r="D13" s="73" t="n"/>
+      <c r="E13" s="73" t="n"/>
+      <c r="F13" s="74" t="n"/>
       <c r="G13" s="52" t="n"/>
-      <c r="H13" s="51" t="n"/>
+      <c r="H13" s="52" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="49" t="n"/>
-      <c r="B14" s="50" t="n"/>
-      <c r="C14" s="52" t="n"/>
-      <c r="D14" s="52" t="n"/>
-      <c r="E14" s="52" t="n"/>
-      <c r="F14" s="52" t="n"/>
+      <c r="A14" s="71" t="n"/>
+      <c r="B14" s="72" t="n"/>
+      <c r="C14" s="73" t="n"/>
+      <c r="D14" s="73" t="n"/>
+      <c r="E14" s="73" t="n"/>
+      <c r="F14" s="74" t="n"/>
       <c r="G14" s="52" t="n"/>
-      <c r="H14" s="51" t="n"/>
+      <c r="H14" s="52" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="49" t="n"/>
-      <c r="B15" s="50" t="n"/>
-      <c r="C15" s="52" t="n"/>
-      <c r="D15" s="52" t="n"/>
-      <c r="E15" s="52" t="n"/>
-      <c r="F15" s="52" t="n"/>
+      <c r="A15" s="71" t="n"/>
+      <c r="B15" s="72" t="n"/>
+      <c r="C15" s="73" t="n"/>
+      <c r="D15" s="73" t="n"/>
+      <c r="E15" s="73" t="n"/>
+      <c r="F15" s="74" t="n"/>
       <c r="G15" s="52" t="n"/>
-      <c r="H15" s="51" t="n"/>
+      <c r="H15" s="52" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="49" t="n"/>
-      <c r="B16" s="50" t="n"/>
-      <c r="C16" s="52" t="n"/>
-      <c r="D16" s="52" t="n"/>
-      <c r="E16" s="52" t="n"/>
-      <c r="F16" s="52" t="n"/>
+      <c r="A16" s="71" t="n"/>
+      <c r="B16" s="72" t="n"/>
+      <c r="C16" s="73" t="n"/>
+      <c r="D16" s="73" t="n"/>
+      <c r="E16" s="73" t="n"/>
+      <c r="F16" s="74" t="n"/>
       <c r="G16" s="52" t="n"/>
-      <c r="H16" s="51" t="n"/>
+      <c r="H16" s="52" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="49" t="n"/>
-      <c r="B17" s="50" t="n"/>
-      <c r="C17" s="52" t="n"/>
-      <c r="D17" s="52" t="n"/>
-      <c r="E17" s="52" t="n"/>
-      <c r="F17" s="52" t="n"/>
+      <c r="A17" s="71" t="n"/>
+      <c r="B17" s="72" t="n"/>
+      <c r="C17" s="73" t="n"/>
+      <c r="D17" s="73" t="n"/>
+      <c r="E17" s="73" t="n"/>
+      <c r="F17" s="74" t="n"/>
       <c r="G17" s="52" t="n"/>
-      <c r="H17" s="51" t="n"/>
+      <c r="H17" s="52" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="49" t="n"/>
-      <c r="B18" s="50" t="n"/>
-      <c r="C18" s="52" t="n"/>
-      <c r="D18" s="52" t="n"/>
-      <c r="E18" s="52" t="n"/>
-      <c r="F18" s="52" t="n"/>
+      <c r="A18" s="71" t="n"/>
+      <c r="B18" s="72" t="n"/>
+      <c r="C18" s="73" t="n"/>
+      <c r="D18" s="73" t="n"/>
+      <c r="E18" s="73" t="n"/>
+      <c r="F18" s="74" t="n"/>
       <c r="G18" s="52" t="n"/>
-      <c r="H18" s="51" t="n"/>
+      <c r="H18" s="52" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="49" t="n"/>
-      <c r="B19" s="50" t="n"/>
-      <c r="C19" s="52" t="n"/>
-      <c r="D19" s="52" t="n"/>
-      <c r="E19" s="52" t="n"/>
-      <c r="F19" s="52" t="n"/>
+      <c r="A19" s="71" t="n"/>
+      <c r="B19" s="72" t="n"/>
+      <c r="C19" s="73" t="n"/>
+      <c r="D19" s="73" t="n"/>
+      <c r="E19" s="73" t="n"/>
+      <c r="F19" s="74" t="n"/>
       <c r="G19" s="52" t="n"/>
-      <c r="H19" s="51" t="n"/>
+      <c r="H19" s="52" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="49" t="n"/>
-      <c r="B20" s="50" t="n"/>
-      <c r="C20" s="52" t="n"/>
-      <c r="D20" s="52" t="n"/>
-      <c r="E20" s="52" t="n"/>
-      <c r="F20" s="52" t="n"/>
+      <c r="A20" s="71" t="n"/>
+      <c r="B20" s="72" t="n"/>
+      <c r="C20" s="73" t="n"/>
+      <c r="D20" s="73" t="n"/>
+      <c r="E20" s="73" t="n"/>
+      <c r="F20" s="74" t="n"/>
       <c r="G20" s="52" t="n"/>
-      <c r="H20" s="51" t="n"/>
+      <c r="H20" s="52" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="49" t="n"/>
-      <c r="B21" s="50" t="n"/>
-      <c r="C21" s="52" t="n"/>
-      <c r="D21" s="52" t="n"/>
-      <c r="E21" s="52" t="n"/>
-      <c r="F21" s="52" t="n"/>
+      <c r="A21" s="71" t="n"/>
+      <c r="B21" s="72" t="n"/>
+      <c r="C21" s="73" t="n"/>
+      <c r="D21" s="73" t="n"/>
+      <c r="E21" s="73" t="n"/>
+      <c r="F21" s="74" t="n"/>
       <c r="G21" s="52" t="n"/>
-      <c r="H21" s="51" t="n"/>
+      <c r="H21" s="52" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="49" t="n"/>
-      <c r="B22" s="50" t="n"/>
-      <c r="C22" s="52" t="n"/>
-      <c r="D22" s="52" t="n"/>
-      <c r="E22" s="52" t="n"/>
-      <c r="F22" s="52" t="n"/>
+      <c r="A22" s="71" t="n"/>
+      <c r="B22" s="72" t="n"/>
+      <c r="C22" s="73" t="n"/>
+      <c r="D22" s="73" t="n"/>
+      <c r="E22" s="73" t="n"/>
+      <c r="F22" s="74" t="n"/>
       <c r="G22" s="52" t="n"/>
-      <c r="H22" s="51" t="n"/>
+      <c r="H22" s="52" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="49" t="n"/>
-      <c r="B23" s="50" t="n"/>
-      <c r="C23" s="52" t="n"/>
-      <c r="D23" s="52" t="n"/>
-      <c r="E23" s="52" t="n"/>
-      <c r="F23" s="52" t="n"/>
+      <c r="A23" s="71" t="n"/>
+      <c r="B23" s="72" t="n"/>
+      <c r="C23" s="73" t="n"/>
+      <c r="D23" s="73" t="n"/>
+      <c r="E23" s="73" t="n"/>
+      <c r="F23" s="74" t="n"/>
       <c r="G23" s="52" t="n"/>
-      <c r="H23" s="51" t="n"/>
+      <c r="H23" s="52" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="49" t="n"/>
-      <c r="B24" s="50" t="n"/>
-      <c r="C24" s="52" t="n"/>
-      <c r="D24" s="52" t="n"/>
-      <c r="E24" s="52" t="n"/>
-      <c r="F24" s="52" t="n"/>
+      <c r="A24" s="71" t="n"/>
+      <c r="B24" s="72" t="n"/>
+      <c r="C24" s="73" t="n"/>
+      <c r="D24" s="73" t="n"/>
+      <c r="E24" s="73" t="n"/>
+      <c r="F24" s="74" t="n"/>
       <c r="G24" s="52" t="n"/>
-      <c r="H24" s="51" t="n"/>
+      <c r="H24" s="52" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="49" t="n"/>
-      <c r="B25" s="50" t="n"/>
-      <c r="C25" s="52" t="n"/>
-      <c r="D25" s="52" t="n"/>
-      <c r="E25" s="52" t="n"/>
-      <c r="F25" s="52" t="n"/>
+      <c r="A25" s="71" t="n"/>
+      <c r="B25" s="72" t="n"/>
+      <c r="C25" s="73" t="n"/>
+      <c r="D25" s="73" t="n"/>
+      <c r="E25" s="73" t="n"/>
+      <c r="F25" s="74" t="n"/>
       <c r="G25" s="52" t="n"/>
-      <c r="H25" s="51" t="n"/>
+      <c r="H25" s="52" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="49" t="n"/>
-      <c r="B26" s="50" t="n"/>
-      <c r="C26" s="52" t="n"/>
-      <c r="D26" s="52" t="n"/>
-      <c r="E26" s="52" t="n"/>
-      <c r="F26" s="52" t="n"/>
+      <c r="A26" s="71" t="n"/>
+      <c r="B26" s="72" t="n"/>
+      <c r="C26" s="73" t="n"/>
+      <c r="D26" s="73" t="n"/>
+      <c r="E26" s="73" t="n"/>
+      <c r="F26" s="74" t="n"/>
       <c r="G26" s="52" t="n"/>
-      <c r="H26" s="51" t="n"/>
+      <c r="H26" s="52" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="49" t="n"/>
-      <c r="B27" s="50" t="n"/>
-      <c r="C27" s="52" t="n"/>
-      <c r="D27" s="52" t="n"/>
-      <c r="E27" s="52" t="n"/>
-      <c r="F27" s="52" t="n"/>
+      <c r="A27" s="71" t="n"/>
+      <c r="B27" s="72" t="n"/>
+      <c r="C27" s="73" t="n"/>
+      <c r="D27" s="73" t="n"/>
+      <c r="E27" s="73" t="n"/>
+      <c r="F27" s="74" t="n"/>
       <c r="G27" s="52" t="n"/>
-      <c r="H27" s="51" t="n"/>
+      <c r="H27" s="52" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="49" t="n"/>
-      <c r="B28" s="50" t="n"/>
-      <c r="C28" s="52" t="n"/>
-      <c r="D28" s="52" t="n"/>
-      <c r="E28" s="52" t="n"/>
-      <c r="F28" s="52" t="n"/>
+      <c r="A28" s="71" t="n"/>
+      <c r="B28" s="72" t="n"/>
+      <c r="C28" s="73" t="n"/>
+      <c r="D28" s="73" t="n"/>
+      <c r="E28" s="73" t="n"/>
+      <c r="F28" s="74" t="n"/>
       <c r="G28" s="52" t="n"/>
-      <c r="H28" s="51" t="n"/>
+      <c r="H28" s="52" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="49" t="n"/>
-      <c r="B29" s="50" t="n"/>
-      <c r="C29" s="52" t="n"/>
-      <c r="D29" s="52" t="n"/>
-      <c r="E29" s="52" t="n"/>
-      <c r="F29" s="52" t="n"/>
+      <c r="A29" s="71" t="n"/>
+      <c r="B29" s="72" t="n"/>
+      <c r="C29" s="73" t="n"/>
+      <c r="D29" s="73" t="n"/>
+      <c r="E29" s="73" t="n"/>
+      <c r="F29" s="74" t="n"/>
       <c r="G29" s="52" t="n"/>
-      <c r="H29" s="51" t="n"/>
+      <c r="H29" s="52" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="49" t="n"/>
-      <c r="B30" s="50" t="n"/>
-      <c r="C30" s="52" t="n"/>
-      <c r="D30" s="52" t="n"/>
-      <c r="E30" s="52" t="n"/>
-      <c r="F30" s="52" t="n"/>
+      <c r="A30" s="71" t="n"/>
+      <c r="B30" s="72" t="n"/>
+      <c r="C30" s="73" t="n"/>
+      <c r="D30" s="73" t="n"/>
+      <c r="E30" s="73" t="n"/>
+      <c r="F30" s="74" t="n"/>
       <c r="G30" s="52" t="n"/>
-      <c r="H30" s="51" t="n"/>
+      <c r="H30" s="52" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="49" t="n"/>
-      <c r="B31" s="50" t="n"/>
-      <c r="C31" s="52" t="n"/>
-      <c r="D31" s="52" t="n"/>
-      <c r="E31" s="52" t="n"/>
-      <c r="F31" s="52" t="n"/>
+      <c r="A31" s="71" t="n"/>
+      <c r="B31" s="72" t="n"/>
+      <c r="C31" s="73" t="n"/>
+      <c r="D31" s="73" t="n"/>
+      <c r="E31" s="73" t="n"/>
+      <c r="F31" s="74" t="n"/>
       <c r="G31" s="52" t="n"/>
-      <c r="H31" s="51" t="n"/>
+      <c r="H31" s="52" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="49" t="n"/>
-      <c r="B32" s="50" t="n"/>
-      <c r="C32" s="52" t="n"/>
-      <c r="D32" s="52" t="n"/>
-      <c r="E32" s="52" t="n"/>
-      <c r="F32" s="52" t="n"/>
+      <c r="A32" s="71" t="n"/>
+      <c r="B32" s="72" t="n"/>
+      <c r="C32" s="73" t="n"/>
+      <c r="D32" s="73" t="n"/>
+      <c r="E32" s="73" t="n"/>
+      <c r="F32" s="74" t="n"/>
       <c r="G32" s="52" t="n"/>
-      <c r="H32" s="51" t="n"/>
+      <c r="H32" s="52" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="49" t="n"/>
-      <c r="B33" s="50" t="n"/>
-      <c r="C33" s="52" t="n"/>
-      <c r="D33" s="52" t="n"/>
-      <c r="E33" s="52" t="n"/>
-      <c r="F33" s="52" t="n"/>
+      <c r="A33" s="71" t="n"/>
+      <c r="B33" s="72" t="n"/>
+      <c r="C33" s="73" t="n"/>
+      <c r="D33" s="73" t="n"/>
+      <c r="E33" s="73" t="n"/>
+      <c r="F33" s="74" t="n"/>
       <c r="G33" s="52" t="n"/>
-      <c r="H33" s="51" t="n"/>
+      <c r="H33" s="52" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="49" t="n"/>
-      <c r="B34" s="50" t="n"/>
-      <c r="C34" s="52" t="n"/>
-      <c r="D34" s="52" t="n"/>
-      <c r="E34" s="52" t="n"/>
-      <c r="F34" s="52" t="n"/>
+      <c r="A34" s="71" t="n"/>
+      <c r="B34" s="72" t="n"/>
+      <c r="C34" s="73" t="n"/>
+      <c r="D34" s="73" t="n"/>
+      <c r="E34" s="73" t="n"/>
+      <c r="F34" s="74" t="n"/>
       <c r="G34" s="52" t="n"/>
-      <c r="H34" s="51" t="n"/>
+      <c r="H34" s="52" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="49" t="n"/>
-      <c r="B35" s="50" t="n"/>
-      <c r="C35" s="52" t="n"/>
-      <c r="D35" s="52" t="n"/>
-      <c r="E35" s="52" t="n"/>
-      <c r="F35" s="52" t="n"/>
+      <c r="A35" s="71" t="n"/>
+      <c r="B35" s="72" t="n"/>
+      <c r="C35" s="73" t="n"/>
+      <c r="D35" s="73" t="n"/>
+      <c r="E35" s="73" t="n"/>
+      <c r="F35" s="74" t="n"/>
       <c r="G35" s="52" t="n"/>
-      <c r="H35" s="51" t="n"/>
+      <c r="H35" s="52" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="49" t="n"/>
-      <c r="B36" s="50" t="n"/>
-      <c r="C36" s="52" t="n"/>
-      <c r="D36" s="52" t="n"/>
-      <c r="E36" s="52" t="n"/>
-      <c r="F36" s="52" t="n"/>
+      <c r="A36" s="71" t="n"/>
+      <c r="B36" s="72" t="n"/>
+      <c r="C36" s="73" t="n"/>
+      <c r="D36" s="73" t="n"/>
+      <c r="E36" s="73" t="n"/>
+      <c r="F36" s="74" t="n"/>
       <c r="G36" s="52" t="n"/>
-      <c r="H36" s="51" t="n"/>
+      <c r="H36" s="52" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="49" t="n"/>
-      <c r="B37" s="50" t="n"/>
-      <c r="C37" s="52" t="n"/>
-      <c r="D37" s="52" t="n"/>
-      <c r="E37" s="52" t="n"/>
-      <c r="F37" s="52" t="n"/>
+      <c r="A37" s="71" t="n"/>
+      <c r="B37" s="72" t="n"/>
+      <c r="C37" s="73" t="n"/>
+      <c r="D37" s="73" t="n"/>
+      <c r="E37" s="73" t="n"/>
+      <c r="F37" s="74" t="n"/>
       <c r="G37" s="52" t="n"/>
-      <c r="H37" s="51" t="n"/>
+      <c r="H37" s="52" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="49" t="n"/>
-      <c r="B38" s="50" t="n"/>
-      <c r="C38" s="52" t="n"/>
-      <c r="D38" s="52" t="n"/>
-      <c r="E38" s="52" t="n"/>
-      <c r="F38" s="52" t="n"/>
+      <c r="A38" s="71" t="n"/>
+      <c r="B38" s="72" t="n"/>
+      <c r="C38" s="73" t="n"/>
+      <c r="D38" s="73" t="n"/>
+      <c r="E38" s="73" t="n"/>
+      <c r="F38" s="74" t="n"/>
       <c r="G38" s="52" t="n"/>
-      <c r="H38" s="51" t="n"/>
+      <c r="H38" s="52" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="49" t="n"/>
-      <c r="B39" s="50" t="n"/>
-      <c r="C39" s="52" t="n"/>
-      <c r="D39" s="52" t="n"/>
-      <c r="E39" s="52" t="n"/>
-      <c r="F39" s="52" t="n"/>
+      <c r="A39" s="71" t="n"/>
+      <c r="B39" s="72" t="n"/>
+      <c r="C39" s="73" t="n"/>
+      <c r="D39" s="73" t="n"/>
+      <c r="E39" s="73" t="n"/>
+      <c r="F39" s="74" t="n"/>
       <c r="G39" s="52" t="n"/>
-      <c r="H39" s="51" t="n"/>
+      <c r="H39" s="52" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="49" t="n"/>
-      <c r="B40" s="50" t="n"/>
-      <c r="C40" s="52" t="n"/>
-      <c r="D40" s="52" t="n"/>
-      <c r="E40" s="52" t="n"/>
-      <c r="F40" s="52" t="n"/>
+      <c r="A40" s="71" t="n"/>
+      <c r="B40" s="72" t="n"/>
+      <c r="C40" s="73" t="n"/>
+      <c r="D40" s="73" t="n"/>
+      <c r="E40" s="73" t="n"/>
+      <c r="F40" s="74" t="n"/>
       <c r="G40" s="52" t="n"/>
-      <c r="H40" s="51" t="n"/>
+      <c r="H40" s="52" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="49" t="n"/>
-      <c r="B41" s="50" t="n"/>
-      <c r="C41" s="52" t="n"/>
-      <c r="D41" s="52" t="n"/>
-      <c r="E41" s="52" t="n"/>
-      <c r="F41" s="52" t="n"/>
+      <c r="A41" s="71" t="n"/>
+      <c r="B41" s="72" t="n"/>
+      <c r="C41" s="73" t="n"/>
+      <c r="D41" s="73" t="n"/>
+      <c r="E41" s="73" t="n"/>
+      <c r="F41" s="74" t="n"/>
       <c r="G41" s="52" t="n"/>
-      <c r="H41" s="51" t="n"/>
+      <c r="H41" s="52" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="49" t="n"/>
-      <c r="B42" s="50" t="n"/>
-      <c r="C42" s="52" t="n"/>
-      <c r="D42" s="52" t="n"/>
-      <c r="E42" s="52" t="n"/>
-      <c r="F42" s="52" t="n"/>
+      <c r="A42" s="71" t="n"/>
+      <c r="B42" s="72" t="n"/>
+      <c r="C42" s="73" t="n"/>
+      <c r="D42" s="73" t="n"/>
+      <c r="E42" s="73" t="n"/>
+      <c r="F42" s="74" t="n"/>
       <c r="G42" s="52" t="n"/>
-      <c r="H42" s="51" t="n"/>
+      <c r="H42" s="52" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="49" t="n"/>
-      <c r="B43" s="50" t="n"/>
-      <c r="C43" s="52" t="n"/>
-      <c r="D43" s="52" t="n"/>
-      <c r="E43" s="52" t="n"/>
-      <c r="F43" s="52" t="n"/>
+      <c r="A43" s="71" t="n"/>
+      <c r="B43" s="72" t="n"/>
+      <c r="C43" s="73" t="n"/>
+      <c r="D43" s="73" t="n"/>
+      <c r="E43" s="73" t="n"/>
+      <c r="F43" s="74" t="n"/>
       <c r="G43" s="52" t="n"/>
-      <c r="H43" s="51" t="n"/>
+      <c r="H43" s="52" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="49" t="n"/>
-      <c r="B44" s="50" t="n"/>
-      <c r="C44" s="52" t="n"/>
-      <c r="D44" s="52" t="n"/>
-      <c r="E44" s="52" t="n"/>
-      <c r="F44" s="52" t="n"/>
+      <c r="A44" s="71" t="n"/>
+      <c r="B44" s="72" t="n"/>
+      <c r="C44" s="73" t="n"/>
+      <c r="D44" s="73" t="n"/>
+      <c r="E44" s="73" t="n"/>
+      <c r="F44" s="74" t="n"/>
       <c r="G44" s="52" t="n"/>
-      <c r="H44" s="51" t="n"/>
+      <c r="H44" s="52" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="49" t="n"/>
-      <c r="B45" s="50" t="n"/>
-      <c r="C45" s="52" t="n"/>
-      <c r="D45" s="52" t="n"/>
-      <c r="E45" s="52" t="n"/>
-      <c r="F45" s="52" t="n"/>
+      <c r="A45" s="71" t="n"/>
+      <c r="B45" s="72" t="n"/>
+      <c r="C45" s="73" t="n"/>
+      <c r="D45" s="73" t="n"/>
+      <c r="E45" s="73" t="n"/>
+      <c r="F45" s="74" t="n"/>
       <c r="G45" s="52" t="n"/>
-      <c r="H45" s="51" t="n"/>
+      <c r="H45" s="52" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="49" t="n"/>
-      <c r="B46" s="50" t="n"/>
-      <c r="C46" s="52" t="n"/>
-      <c r="D46" s="52" t="n"/>
-      <c r="E46" s="52" t="n"/>
-      <c r="F46" s="52" t="n"/>
+      <c r="A46" s="71" t="n"/>
+      <c r="B46" s="72" t="n"/>
+      <c r="C46" s="73" t="n"/>
+      <c r="D46" s="73" t="n"/>
+      <c r="E46" s="73" t="n"/>
+      <c r="F46" s="74" t="n"/>
       <c r="G46" s="52" t="n"/>
-      <c r="H46" s="51" t="n"/>
+      <c r="H46" s="52" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="49" t="n"/>
-      <c r="B47" s="50" t="n"/>
-      <c r="C47" s="52" t="n"/>
-      <c r="D47" s="52" t="n"/>
-      <c r="E47" s="52" t="n"/>
-      <c r="F47" s="52" t="n"/>
+      <c r="A47" s="71" t="n"/>
+      <c r="B47" s="72" t="n"/>
+      <c r="C47" s="73" t="n"/>
+      <c r="D47" s="73" t="n"/>
+      <c r="E47" s="73" t="n"/>
+      <c r="F47" s="74" t="n"/>
       <c r="G47" s="52" t="n"/>
-      <c r="H47" s="51" t="n"/>
+      <c r="H47" s="52" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="49" t="n"/>
-      <c r="B48" s="50" t="n"/>
-      <c r="C48" s="52" t="n"/>
-      <c r="D48" s="52" t="n"/>
-      <c r="E48" s="52" t="n"/>
-      <c r="F48" s="52" t="n"/>
+      <c r="A48" s="71" t="n"/>
+      <c r="B48" s="72" t="n"/>
+      <c r="C48" s="73" t="n"/>
+      <c r="D48" s="73" t="n"/>
+      <c r="E48" s="73" t="n"/>
+      <c r="F48" s="74" t="n"/>
       <c r="G48" s="52" t="n"/>
-      <c r="H48" s="51" t="n"/>
+      <c r="H48" s="52" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="49" t="n"/>
-      <c r="B49" s="50" t="n"/>
-      <c r="C49" s="52" t="n"/>
-      <c r="D49" s="52" t="n"/>
-      <c r="E49" s="52" t="n"/>
-      <c r="F49" s="52" t="n"/>
+      <c r="A49" s="71" t="n"/>
+      <c r="B49" s="72" t="n"/>
+      <c r="C49" s="73" t="n"/>
+      <c r="D49" s="73" t="n"/>
+      <c r="E49" s="73" t="n"/>
+      <c r="F49" s="74" t="n"/>
       <c r="G49" s="52" t="n"/>
-      <c r="H49" s="51" t="n"/>
+      <c r="H49" s="52" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="49" t="n"/>
-      <c r="B50" s="50" t="n"/>
-      <c r="C50" s="52" t="n"/>
-      <c r="D50" s="52" t="n"/>
-      <c r="E50" s="52" t="n"/>
-      <c r="F50" s="52" t="n"/>
+      <c r="A50" s="71" t="n"/>
+      <c r="B50" s="72" t="n"/>
+      <c r="C50" s="73" t="n"/>
+      <c r="D50" s="73" t="n"/>
+      <c r="E50" s="73" t="n"/>
+      <c r="F50" s="74" t="n"/>
       <c r="G50" s="52" t="n"/>
-      <c r="H50" s="51" t="n"/>
+      <c r="H50" s="52" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="49" t="n"/>
-      <c r="B51" s="50" t="n"/>
-      <c r="C51" s="52" t="n"/>
-      <c r="D51" s="52" t="n"/>
-      <c r="E51" s="52" t="n"/>
-      <c r="F51" s="52" t="n"/>
+      <c r="A51" s="71" t="n"/>
+      <c r="B51" s="72" t="n"/>
+      <c r="C51" s="73" t="n"/>
+      <c r="D51" s="73" t="n"/>
+      <c r="E51" s="73" t="n"/>
+      <c r="F51" s="74" t="n"/>
       <c r="G51" s="52" t="n"/>
-      <c r="H51" s="51" t="n"/>
+      <c r="H51" s="52" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="49" t="n"/>
-      <c r="B52" s="50" t="n"/>
-      <c r="C52" s="52" t="n"/>
-      <c r="D52" s="52" t="n"/>
-      <c r="E52" s="52" t="n"/>
-      <c r="F52" s="52" t="n"/>
+      <c r="A52" s="71" t="n"/>
+      <c r="B52" s="72" t="n"/>
+      <c r="C52" s="73" t="n"/>
+      <c r="D52" s="73" t="n"/>
+      <c r="E52" s="73" t="n"/>
+      <c r="F52" s="74" t="n"/>
       <c r="G52" s="52" t="n"/>
-      <c r="H52" s="51" t="n"/>
+      <c r="H52" s="52" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="49" t="n"/>
-      <c r="B53" s="50" t="n"/>
-      <c r="C53" s="52" t="n"/>
-      <c r="D53" s="52" t="n"/>
-      <c r="E53" s="52" t="n"/>
-      <c r="F53" s="52" t="n"/>
+      <c r="A53" s="71" t="n"/>
+      <c r="B53" s="72" t="n"/>
+      <c r="C53" s="73" t="n"/>
+      <c r="D53" s="73" t="n"/>
+      <c r="E53" s="73" t="n"/>
+      <c r="F53" s="74" t="n"/>
       <c r="G53" s="52" t="n"/>
-      <c r="H53" s="51" t="n"/>
+      <c r="H53" s="52" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="49" t="n"/>
-      <c r="B54" s="50" t="n"/>
-      <c r="C54" s="52" t="n"/>
-      <c r="D54" s="52" t="n"/>
-      <c r="E54" s="52" t="n"/>
-      <c r="F54" s="52" t="n"/>
+      <c r="A54" s="71" t="n"/>
+      <c r="B54" s="72" t="n"/>
+      <c r="C54" s="73" t="n"/>
+      <c r="D54" s="73" t="n"/>
+      <c r="E54" s="73" t="n"/>
+      <c r="F54" s="74" t="n"/>
       <c r="G54" s="52" t="n"/>
-      <c r="H54" s="51" t="n"/>
+      <c r="H54" s="52" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="49" t="n"/>
-      <c r="B55" s="50" t="n"/>
-      <c r="C55" s="52" t="n"/>
-      <c r="D55" s="52" t="n"/>
-      <c r="E55" s="52" t="n"/>
-      <c r="F55" s="52" t="n"/>
+      <c r="A55" s="71" t="n"/>
+      <c r="B55" s="72" t="n"/>
+      <c r="C55" s="73" t="n"/>
+      <c r="D55" s="73" t="n"/>
+      <c r="E55" s="73" t="n"/>
+      <c r="F55" s="74" t="n"/>
       <c r="G55" s="52" t="n"/>
-      <c r="H55" s="51" t="n"/>
+      <c r="H55" s="52" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="49" t="n"/>
-      <c r="B56" s="50" t="n"/>
-      <c r="C56" s="52" t="n"/>
-      <c r="D56" s="52" t="n"/>
-      <c r="E56" s="52" t="n"/>
-      <c r="F56" s="52" t="n"/>
+      <c r="A56" s="71" t="n"/>
+      <c r="B56" s="72" t="n"/>
+      <c r="C56" s="73" t="n"/>
+      <c r="D56" s="73" t="n"/>
+      <c r="E56" s="73" t="n"/>
+      <c r="F56" s="74" t="n"/>
       <c r="G56" s="52" t="n"/>
-      <c r="H56" s="51" t="n"/>
+      <c r="H56" s="52" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="49" t="n"/>
-      <c r="B57" s="50" t="n"/>
-      <c r="C57" s="52" t="n"/>
-      <c r="D57" s="52" t="n"/>
-      <c r="E57" s="52" t="n"/>
-      <c r="F57" s="52" t="n"/>
+      <c r="A57" s="71" t="n"/>
+      <c r="B57" s="72" t="n"/>
+      <c r="C57" s="73" t="n"/>
+      <c r="D57" s="73" t="n"/>
+      <c r="E57" s="73" t="n"/>
+      <c r="F57" s="74" t="n"/>
       <c r="G57" s="52" t="n"/>
-      <c r="H57" s="51" t="n"/>
+      <c r="H57" s="52" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="49" t="n"/>
-      <c r="B58" s="50" t="n"/>
-      <c r="C58" s="52" t="n"/>
-      <c r="D58" s="52" t="n"/>
-      <c r="E58" s="52" t="n"/>
-      <c r="F58" s="52" t="n"/>
+      <c r="A58" s="71" t="n"/>
+      <c r="B58" s="72" t="n"/>
+      <c r="C58" s="73" t="n"/>
+      <c r="D58" s="73" t="n"/>
+      <c r="E58" s="73" t="n"/>
+      <c r="F58" s="74" t="n"/>
       <c r="G58" s="52" t="n"/>
-      <c r="H58" s="51" t="n"/>
+      <c r="H58" s="52" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="49" t="n"/>
-      <c r="B59" s="50" t="n"/>
-      <c r="C59" s="52" t="n"/>
-      <c r="D59" s="52" t="n"/>
-      <c r="E59" s="52" t="n"/>
-      <c r="F59" s="52" t="n"/>
+      <c r="A59" s="71" t="n"/>
+      <c r="B59" s="72" t="n"/>
+      <c r="C59" s="73" t="n"/>
+      <c r="D59" s="73" t="n"/>
+      <c r="E59" s="73" t="n"/>
+      <c r="F59" s="74" t="n"/>
       <c r="G59" s="52" t="n"/>
-      <c r="H59" s="51" t="n"/>
+      <c r="H59" s="52" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="49" t="n"/>
-      <c r="B60" s="50" t="n"/>
-      <c r="C60" s="52" t="n"/>
-      <c r="D60" s="52" t="n"/>
-      <c r="E60" s="52" t="n"/>
-      <c r="F60" s="52" t="n"/>
+      <c r="A60" s="71" t="n"/>
+      <c r="B60" s="72" t="n"/>
+      <c r="C60" s="73" t="n"/>
+      <c r="D60" s="73" t="n"/>
+      <c r="E60" s="73" t="n"/>
+      <c r="F60" s="74" t="n"/>
       <c r="G60" s="52" t="n"/>
-      <c r="H60" s="51" t="n"/>
+      <c r="H60" s="52" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="49" t="n"/>
-      <c r="B61" s="50" t="n"/>
-      <c r="C61" s="52" t="n"/>
-      <c r="D61" s="52" t="n"/>
-      <c r="E61" s="52" t="n"/>
-      <c r="F61" s="52" t="n"/>
+      <c r="A61" s="71" t="n"/>
+      <c r="B61" s="72" t="n"/>
+      <c r="C61" s="73" t="n"/>
+      <c r="D61" s="73" t="n"/>
+      <c r="E61" s="73" t="n"/>
+      <c r="F61" s="74" t="n"/>
       <c r="G61" s="52" t="n"/>
-      <c r="H61" s="51" t="n"/>
+      <c r="H61" s="52" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="49" t="n"/>
-      <c r="B62" s="50" t="n"/>
-      <c r="C62" s="52" t="n"/>
-      <c r="D62" s="52" t="n"/>
-      <c r="E62" s="52" t="n"/>
-      <c r="F62" s="52" t="n"/>
+      <c r="A62" s="71" t="n"/>
+      <c r="B62" s="72" t="n"/>
+      <c r="C62" s="73" t="n"/>
+      <c r="D62" s="73" t="n"/>
+      <c r="E62" s="73" t="n"/>
+      <c r="F62" s="74" t="n"/>
       <c r="G62" s="52" t="n"/>
-      <c r="H62" s="51" t="n"/>
+      <c r="H62" s="52" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="49" t="n"/>
-      <c r="B63" s="50" t="n"/>
-      <c r="C63" s="52" t="n"/>
-      <c r="D63" s="52" t="n"/>
-      <c r="E63" s="52" t="n"/>
-      <c r="F63" s="52" t="n"/>
+      <c r="A63" s="71" t="n"/>
+      <c r="B63" s="72" t="n"/>
+      <c r="C63" s="73" t="n"/>
+      <c r="D63" s="73" t="n"/>
+      <c r="E63" s="73" t="n"/>
+      <c r="F63" s="74" t="n"/>
       <c r="G63" s="52" t="n"/>
-      <c r="H63" s="51" t="n"/>
+      <c r="H63" s="52" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="49" t="n"/>
-      <c r="B64" s="50" t="n"/>
-      <c r="C64" s="52" t="n"/>
-      <c r="D64" s="52" t="n"/>
-      <c r="E64" s="52" t="n"/>
-      <c r="F64" s="52" t="n"/>
+      <c r="A64" s="71" t="n"/>
+      <c r="B64" s="72" t="n"/>
+      <c r="C64" s="73" t="n"/>
+      <c r="D64" s="73" t="n"/>
+      <c r="E64" s="73" t="n"/>
+      <c r="F64" s="74" t="n"/>
       <c r="G64" s="52" t="n"/>
-      <c r="H64" s="51" t="n"/>
+      <c r="H64" s="52" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="49" t="n"/>
-      <c r="B65" s="50" t="n"/>
-      <c r="C65" s="52" t="n"/>
-      <c r="D65" s="52" t="n"/>
-      <c r="E65" s="52" t="n"/>
-      <c r="F65" s="52" t="n"/>
+      <c r="A65" s="71" t="n"/>
+      <c r="B65" s="72" t="n"/>
+      <c r="C65" s="73" t="n"/>
+      <c r="D65" s="73" t="n"/>
+      <c r="E65" s="73" t="n"/>
+      <c r="F65" s="74" t="n"/>
       <c r="G65" s="52" t="n"/>
-      <c r="H65" s="51" t="n"/>
+      <c r="H65" s="52" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="49" t="n"/>
-      <c r="B66" s="50" t="n"/>
-      <c r="C66" s="52" t="n"/>
-      <c r="D66" s="52" t="n"/>
-      <c r="E66" s="52" t="n"/>
-      <c r="F66" s="52" t="n"/>
+      <c r="A66" s="71" t="n"/>
+      <c r="B66" s="72" t="n"/>
+      <c r="C66" s="73" t="n"/>
+      <c r="D66" s="73" t="n"/>
+      <c r="E66" s="73" t="n"/>
+      <c r="F66" s="74" t="n"/>
       <c r="G66" s="52" t="n"/>
-      <c r="H66" s="51" t="n"/>
+      <c r="H66" s="52" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="49" t="n"/>
-      <c r="B67" s="50" t="n"/>
-      <c r="C67" s="52" t="n"/>
-      <c r="D67" s="52" t="n"/>
-      <c r="E67" s="52" t="n"/>
-      <c r="F67" s="52" t="n"/>
+      <c r="A67" s="71" t="n"/>
+      <c r="B67" s="72" t="n"/>
+      <c r="C67" s="73" t="n"/>
+      <c r="D67" s="73" t="n"/>
+      <c r="E67" s="73" t="n"/>
+      <c r="F67" s="74" t="n"/>
       <c r="G67" s="52" t="n"/>
-      <c r="H67" s="51" t="n"/>
+      <c r="H67" s="52" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="49" t="n"/>
-      <c r="B68" s="50" t="n"/>
-      <c r="C68" s="52" t="n"/>
-      <c r="D68" s="52" t="n"/>
-      <c r="E68" s="52" t="n"/>
-      <c r="F68" s="52" t="n"/>
+      <c r="A68" s="71" t="n"/>
+      <c r="B68" s="72" t="n"/>
+      <c r="C68" s="73" t="n"/>
+      <c r="D68" s="73" t="n"/>
+      <c r="E68" s="73" t="n"/>
+      <c r="F68" s="74" t="n"/>
       <c r="G68" s="52" t="n"/>
-      <c r="H68" s="51" t="n"/>
+      <c r="H68" s="52" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="49" t="n"/>
-      <c r="B69" s="50" t="n"/>
-      <c r="C69" s="52" t="n"/>
-      <c r="D69" s="52" t="n"/>
-      <c r="E69" s="52" t="n"/>
-      <c r="F69" s="52" t="n"/>
+      <c r="A69" s="71" t="n"/>
+      <c r="B69" s="72" t="n"/>
+      <c r="C69" s="73" t="n"/>
+      <c r="D69" s="73" t="n"/>
+      <c r="E69" s="73" t="n"/>
+      <c r="F69" s="74" t="n"/>
       <c r="G69" s="52" t="n"/>
-      <c r="H69" s="51" t="n"/>
+      <c r="H69" s="52" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="49" t="n"/>
-      <c r="B70" s="50" t="n"/>
-      <c r="C70" s="52" t="n"/>
-      <c r="D70" s="52" t="n"/>
-      <c r="E70" s="52" t="n"/>
-      <c r="F70" s="52" t="n"/>
+      <c r="A70" s="71" t="n"/>
+      <c r="B70" s="72" t="n"/>
+      <c r="C70" s="73" t="n"/>
+      <c r="D70" s="73" t="n"/>
+      <c r="E70" s="73" t="n"/>
+      <c r="F70" s="74" t="n"/>
       <c r="G70" s="52" t="n"/>
-      <c r="H70" s="51" t="n"/>
+      <c r="H70" s="52" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="49" t="n"/>
-      <c r="B71" s="50" t="n"/>
-      <c r="C71" s="52" t="n"/>
-      <c r="D71" s="52" t="n"/>
-      <c r="E71" s="52" t="n"/>
-      <c r="F71" s="52" t="n"/>
+      <c r="A71" s="71" t="n"/>
+      <c r="B71" s="72" t="n"/>
+      <c r="C71" s="73" t="n"/>
+      <c r="D71" s="73" t="n"/>
+      <c r="E71" s="73" t="n"/>
+      <c r="F71" s="74" t="n"/>
       <c r="G71" s="52" t="n"/>
-      <c r="H71" s="51" t="n"/>
+      <c r="H71" s="52" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="49" t="n"/>
-      <c r="B72" s="50" t="n"/>
-      <c r="C72" s="52" t="n"/>
-      <c r="D72" s="52" t="n"/>
-      <c r="E72" s="52" t="n"/>
-      <c r="F72" s="52" t="n"/>
+      <c r="A72" s="71" t="n"/>
+      <c r="B72" s="72" t="n"/>
+      <c r="C72" s="73" t="n"/>
+      <c r="D72" s="73" t="n"/>
+      <c r="E72" s="73" t="n"/>
+      <c r="F72" s="74" t="n"/>
       <c r="G72" s="52" t="n"/>
-      <c r="H72" s="51" t="n"/>
+      <c r="H72" s="52" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="49" t="n"/>
-      <c r="B73" s="50" t="n"/>
-      <c r="C73" s="52" t="n"/>
-      <c r="D73" s="52" t="n"/>
-      <c r="E73" s="52" t="n"/>
-      <c r="F73" s="52" t="n"/>
+      <c r="A73" s="71" t="n"/>
+      <c r="B73" s="72" t="n"/>
+      <c r="C73" s="73" t="n"/>
+      <c r="D73" s="73" t="n"/>
+      <c r="E73" s="73" t="n"/>
+      <c r="F73" s="74" t="n"/>
       <c r="G73" s="52" t="n"/>
-      <c r="H73" s="51" t="n"/>
+      <c r="H73" s="52" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="49" t="n"/>
-      <c r="B74" s="50" t="n"/>
-      <c r="C74" s="52" t="n"/>
-      <c r="D74" s="52" t="n"/>
-      <c r="E74" s="52" t="n"/>
-      <c r="F74" s="52" t="n"/>
+      <c r="A74" s="71" t="n"/>
+      <c r="B74" s="72" t="n"/>
+      <c r="C74" s="73" t="n"/>
+      <c r="D74" s="73" t="n"/>
+      <c r="E74" s="73" t="n"/>
+      <c r="F74" s="74" t="n"/>
       <c r="G74" s="52" t="n"/>
-      <c r="H74" s="51" t="n"/>
+      <c r="H74" s="52" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="49" t="n"/>
-      <c r="B75" s="50" t="n"/>
-      <c r="C75" s="52" t="n"/>
-      <c r="D75" s="52" t="n"/>
-      <c r="E75" s="52" t="n"/>
-      <c r="F75" s="52" t="n"/>
+      <c r="A75" s="71" t="n"/>
+      <c r="B75" s="72" t="n"/>
+      <c r="C75" s="73" t="n"/>
+      <c r="D75" s="73" t="n"/>
+      <c r="E75" s="73" t="n"/>
+      <c r="F75" s="74" t="n"/>
       <c r="G75" s="52" t="n"/>
-      <c r="H75" s="51" t="n"/>
+      <c r="H75" s="52" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="49" t="n"/>
-      <c r="B76" s="50" t="n"/>
-      <c r="C76" s="52" t="n"/>
-      <c r="D76" s="52" t="n"/>
-      <c r="E76" s="52" t="n"/>
-      <c r="F76" s="52" t="n"/>
+      <c r="A76" s="71" t="n"/>
+      <c r="B76" s="72" t="n"/>
+      <c r="C76" s="73" t="n"/>
+      <c r="D76" s="73" t="n"/>
+      <c r="E76" s="73" t="n"/>
+      <c r="F76" s="74" t="n"/>
       <c r="G76" s="52" t="n"/>
-      <c r="H76" s="51" t="n"/>
+      <c r="H76" s="52" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="49" t="n"/>
-      <c r="B77" s="50" t="n"/>
-      <c r="C77" s="52" t="n"/>
-      <c r="D77" s="52" t="n"/>
-      <c r="E77" s="52" t="n"/>
-      <c r="F77" s="52" t="n"/>
+      <c r="A77" s="71" t="n"/>
+      <c r="B77" s="72" t="n"/>
+      <c r="C77" s="73" t="n"/>
+      <c r="D77" s="73" t="n"/>
+      <c r="E77" s="73" t="n"/>
+      <c r="F77" s="74" t="n"/>
       <c r="G77" s="52" t="n"/>
-      <c r="H77" s="51" t="n"/>
+      <c r="H77" s="52" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="49" t="n"/>
-      <c r="B78" s="50" t="n"/>
-      <c r="C78" s="52" t="n"/>
-      <c r="D78" s="52" t="n"/>
-      <c r="E78" s="52" t="n"/>
-      <c r="F78" s="52" t="n"/>
+      <c r="A78" s="71" t="n"/>
+      <c r="B78" s="72" t="n"/>
+      <c r="C78" s="73" t="n"/>
+      <c r="D78" s="73" t="n"/>
+      <c r="E78" s="73" t="n"/>
+      <c r="F78" s="74" t="n"/>
       <c r="G78" s="52" t="n"/>
-      <c r="H78" s="51" t="n"/>
+      <c r="H78" s="52" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="49" t="n"/>
-      <c r="B79" s="50" t="n"/>
-      <c r="C79" s="52" t="n"/>
-      <c r="D79" s="52" t="n"/>
-      <c r="E79" s="52" t="n"/>
-      <c r="F79" s="52" t="n"/>
+      <c r="A79" s="71" t="n"/>
+      <c r="B79" s="72" t="n"/>
+      <c r="C79" s="73" t="n"/>
+      <c r="D79" s="73" t="n"/>
+      <c r="E79" s="73" t="n"/>
+      <c r="F79" s="74" t="n"/>
       <c r="G79" s="52" t="n"/>
-      <c r="H79" s="51" t="n"/>
+      <c r="H79" s="52" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="49" t="n"/>
-      <c r="B80" s="50" t="n"/>
-      <c r="C80" s="52" t="n"/>
-      <c r="D80" s="52" t="n"/>
-      <c r="E80" s="52" t="n"/>
-      <c r="F80" s="52" t="n"/>
+      <c r="A80" s="71" t="n"/>
+      <c r="B80" s="72" t="n"/>
+      <c r="C80" s="73" t="n"/>
+      <c r="D80" s="73" t="n"/>
+      <c r="E80" s="73" t="n"/>
+      <c r="F80" s="74" t="n"/>
       <c r="G80" s="52" t="n"/>
-      <c r="H80" s="51" t="n"/>
+      <c r="H80" s="52" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="49" t="n"/>
-      <c r="B81" s="50" t="n"/>
-      <c r="C81" s="52" t="n"/>
-      <c r="D81" s="52" t="n"/>
-      <c r="E81" s="52" t="n"/>
-      <c r="F81" s="52" t="n"/>
+      <c r="A81" s="71" t="n"/>
+      <c r="B81" s="72" t="n"/>
+      <c r="C81" s="73" t="n"/>
+      <c r="D81" s="73" t="n"/>
+      <c r="E81" s="73" t="n"/>
+      <c r="F81" s="74" t="n"/>
       <c r="G81" s="52" t="n"/>
-      <c r="H81" s="51" t="n"/>
+      <c r="H81" s="52" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="49" t="n"/>
-      <c r="B82" s="50" t="n"/>
-      <c r="C82" s="52" t="n"/>
-      <c r="D82" s="52" t="n"/>
-      <c r="E82" s="52" t="n"/>
-      <c r="F82" s="52" t="n"/>
+      <c r="A82" s="71" t="n"/>
+      <c r="B82" s="72" t="n"/>
+      <c r="C82" s="73" t="n"/>
+      <c r="D82" s="73" t="n"/>
+      <c r="E82" s="73" t="n"/>
+      <c r="F82" s="74" t="n"/>
       <c r="G82" s="52" t="n"/>
-      <c r="H82" s="51" t="n"/>
+      <c r="H82" s="52" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="49" t="n"/>
-      <c r="B83" s="50" t="n"/>
-      <c r="C83" s="52" t="n"/>
-      <c r="D83" s="52" t="n"/>
-      <c r="E83" s="52" t="n"/>
-      <c r="F83" s="52" t="n"/>
+      <c r="A83" s="71" t="n"/>
+      <c r="B83" s="72" t="n"/>
+      <c r="C83" s="73" t="n"/>
+      <c r="D83" s="73" t="n"/>
+      <c r="E83" s="73" t="n"/>
+      <c r="F83" s="74" t="n"/>
       <c r="G83" s="52" t="n"/>
-      <c r="H83" s="51" t="n"/>
+      <c r="H83" s="52" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="49" t="n"/>
-      <c r="B84" s="50" t="n"/>
-      <c r="C84" s="52" t="n"/>
-      <c r="D84" s="52" t="n"/>
-      <c r="E84" s="52" t="n"/>
-      <c r="F84" s="52" t="n"/>
+      <c r="A84" s="71" t="n"/>
+      <c r="B84" s="72" t="n"/>
+      <c r="C84" s="73" t="n"/>
+      <c r="D84" s="73" t="n"/>
+      <c r="E84" s="73" t="n"/>
+      <c r="F84" s="74" t="n"/>
       <c r="G84" s="52" t="n"/>
-      <c r="H84" s="51" t="n"/>
+      <c r="H84" s="52" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="49" t="n"/>
-      <c r="B85" s="50" t="n"/>
-      <c r="C85" s="52" t="n"/>
-      <c r="D85" s="52" t="n"/>
-      <c r="E85" s="52" t="n"/>
-      <c r="F85" s="52" t="n"/>
+      <c r="A85" s="71" t="n"/>
+      <c r="B85" s="72" t="n"/>
+      <c r="C85" s="73" t="n"/>
+      <c r="D85" s="73" t="n"/>
+      <c r="E85" s="73" t="n"/>
+      <c r="F85" s="74" t="n"/>
       <c r="G85" s="52" t="n"/>
-      <c r="H85" s="51" t="n"/>
+      <c r="H85" s="52" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="49" t="n"/>
-      <c r="B86" s="50" t="n"/>
-      <c r="C86" s="52" t="n"/>
-      <c r="D86" s="52" t="n"/>
-      <c r="E86" s="52" t="n"/>
-      <c r="F86" s="52" t="n"/>
+      <c r="A86" s="71" t="n"/>
+      <c r="B86" s="72" t="n"/>
+      <c r="C86" s="73" t="n"/>
+      <c r="D86" s="73" t="n"/>
+      <c r="E86" s="73" t="n"/>
+      <c r="F86" s="74" t="n"/>
       <c r="G86" s="52" t="n"/>
-      <c r="H86" s="51" t="n"/>
+      <c r="H86" s="52" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="49" t="n"/>
-      <c r="B87" s="50" t="n"/>
-      <c r="C87" s="52" t="n"/>
-      <c r="D87" s="52" t="n"/>
-      <c r="E87" s="52" t="n"/>
-      <c r="F87" s="52" t="n"/>
+      <c r="A87" s="71" t="n"/>
+      <c r="B87" s="72" t="n"/>
+      <c r="C87" s="73" t="n"/>
+      <c r="D87" s="73" t="n"/>
+      <c r="E87" s="73" t="n"/>
+      <c r="F87" s="74" t="n"/>
       <c r="G87" s="52" t="n"/>
-      <c r="H87" s="51" t="n"/>
+      <c r="H87" s="52" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="49" t="n"/>
-      <c r="B88" s="50" t="n"/>
-      <c r="C88" s="52" t="n"/>
-      <c r="D88" s="52" t="n"/>
-      <c r="E88" s="52" t="n"/>
-      <c r="F88" s="52" t="n"/>
+      <c r="A88" s="71" t="n"/>
+      <c r="B88" s="72" t="n"/>
+      <c r="C88" s="73" t="n"/>
+      <c r="D88" s="73" t="n"/>
+      <c r="E88" s="73" t="n"/>
+      <c r="F88" s="74" t="n"/>
       <c r="G88" s="52" t="n"/>
-      <c r="H88" s="51" t="n"/>
+      <c r="H88" s="52" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="49" t="n"/>
-      <c r="B89" s="50" t="n"/>
-      <c r="C89" s="52" t="n"/>
-      <c r="D89" s="52" t="n"/>
-      <c r="E89" s="52" t="n"/>
-      <c r="F89" s="52" t="n"/>
+      <c r="A89" s="71" t="n"/>
+      <c r="B89" s="72" t="n"/>
+      <c r="C89" s="73" t="n"/>
+      <c r="D89" s="73" t="n"/>
+      <c r="E89" s="73" t="n"/>
+      <c r="F89" s="74" t="n"/>
       <c r="G89" s="52" t="n"/>
-      <c r="H89" s="51" t="n"/>
+      <c r="H89" s="52" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="49" t="n"/>
-      <c r="B90" s="50" t="n"/>
-      <c r="C90" s="52" t="n"/>
-      <c r="D90" s="52" t="n"/>
-      <c r="E90" s="52" t="n"/>
-      <c r="F90" s="52" t="n"/>
+      <c r="A90" s="71" t="n"/>
+      <c r="B90" s="72" t="n"/>
+      <c r="C90" s="73" t="n"/>
+      <c r="D90" s="73" t="n"/>
+      <c r="E90" s="73" t="n"/>
+      <c r="F90" s="74" t="n"/>
       <c r="G90" s="52" t="n"/>
-      <c r="H90" s="51" t="n"/>
+      <c r="H90" s="52" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="49" t="n"/>
-      <c r="B91" s="50" t="n"/>
-      <c r="C91" s="52" t="n"/>
-      <c r="D91" s="52" t="n"/>
-      <c r="E91" s="52" t="n"/>
-      <c r="F91" s="52" t="n"/>
+      <c r="A91" s="71" t="n"/>
+      <c r="B91" s="72" t="n"/>
+      <c r="C91" s="73" t="n"/>
+      <c r="D91" s="73" t="n"/>
+      <c r="E91" s="73" t="n"/>
+      <c r="F91" s="74" t="n"/>
       <c r="G91" s="52" t="n"/>
-      <c r="H91" s="51" t="n"/>
+      <c r="H91" s="52" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="49" t="n"/>
-      <c r="B92" s="50" t="n"/>
-      <c r="C92" s="52" t="n"/>
-      <c r="D92" s="52" t="n"/>
-      <c r="E92" s="52" t="n"/>
-      <c r="F92" s="52" t="n"/>
+      <c r="A92" s="71" t="n"/>
+      <c r="B92" s="72" t="n"/>
+      <c r="C92" s="73" t="n"/>
+      <c r="D92" s="73" t="n"/>
+      <c r="E92" s="73" t="n"/>
+      <c r="F92" s="74" t="n"/>
       <c r="G92" s="52" t="n"/>
-      <c r="H92" s="51" t="n"/>
+      <c r="H92" s="52" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="49" t="n"/>
-      <c r="B93" s="50" t="n"/>
-      <c r="C93" s="52" t="n"/>
-      <c r="D93" s="52" t="n"/>
-      <c r="E93" s="52" t="n"/>
-      <c r="F93" s="52" t="n"/>
+      <c r="A93" s="71" t="n"/>
+      <c r="B93" s="72" t="n"/>
+      <c r="C93" s="73" t="n"/>
+      <c r="D93" s="73" t="n"/>
+      <c r="E93" s="73" t="n"/>
+      <c r="F93" s="74" t="n"/>
       <c r="G93" s="52" t="n"/>
-      <c r="H93" s="51" t="n"/>
+      <c r="H93" s="52" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="49" t="n"/>
-      <c r="B94" s="50" t="n"/>
-      <c r="C94" s="52" t="n"/>
-      <c r="D94" s="52" t="n"/>
-      <c r="E94" s="52" t="n"/>
-      <c r="F94" s="52" t="n"/>
+      <c r="A94" s="71" t="n"/>
+      <c r="B94" s="72" t="n"/>
+      <c r="C94" s="73" t="n"/>
+      <c r="D94" s="73" t="n"/>
+      <c r="E94" s="73" t="n"/>
+      <c r="F94" s="74" t="n"/>
       <c r="G94" s="52" t="n"/>
-      <c r="H94" s="51" t="n"/>
+      <c r="H94" s="52" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="49" t="n"/>
-      <c r="B95" s="50" t="n"/>
-      <c r="C95" s="52" t="n"/>
-      <c r="D95" s="52" t="n"/>
-      <c r="E95" s="52" t="n"/>
-      <c r="F95" s="52" t="n"/>
+      <c r="A95" s="71" t="n"/>
+      <c r="B95" s="72" t="n"/>
+      <c r="C95" s="73" t="n"/>
+      <c r="D95" s="73" t="n"/>
+      <c r="E95" s="73" t="n"/>
+      <c r="F95" s="74" t="n"/>
       <c r="G95" s="52" t="n"/>
-      <c r="H95" s="51" t="n"/>
+      <c r="H95" s="52" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="49" t="n"/>
-      <c r="B96" s="50" t="n"/>
-      <c r="C96" s="52" t="n"/>
-      <c r="D96" s="52" t="n"/>
-      <c r="E96" s="52" t="n"/>
-      <c r="F96" s="52" t="n"/>
+      <c r="A96" s="71" t="n"/>
+      <c r="B96" s="72" t="n"/>
+      <c r="C96" s="73" t="n"/>
+      <c r="D96" s="73" t="n"/>
+      <c r="E96" s="73" t="n"/>
+      <c r="F96" s="74" t="n"/>
       <c r="G96" s="52" t="n"/>
-      <c r="H96" s="51" t="n"/>
+      <c r="H96" s="52" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="49" t="n"/>
-      <c r="B97" s="50" t="n"/>
-      <c r="C97" s="52" t="n"/>
-      <c r="D97" s="52" t="n"/>
-      <c r="E97" s="52" t="n"/>
-      <c r="F97" s="52" t="n"/>
+      <c r="A97" s="71" t="n"/>
+      <c r="B97" s="72" t="n"/>
+      <c r="C97" s="73" t="n"/>
+      <c r="D97" s="73" t="n"/>
+      <c r="E97" s="73" t="n"/>
+      <c r="F97" s="74" t="n"/>
       <c r="G97" s="52" t="n"/>
-      <c r="H97" s="51" t="n"/>
+      <c r="H97" s="52" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="49" t="n"/>
-      <c r="B98" s="50" t="n"/>
-      <c r="C98" s="52" t="n"/>
-      <c r="D98" s="52" t="n"/>
-      <c r="E98" s="52" t="n"/>
-      <c r="F98" s="52" t="n"/>
+      <c r="A98" s="71" t="n"/>
+      <c r="B98" s="72" t="n"/>
+      <c r="C98" s="73" t="n"/>
+      <c r="D98" s="73" t="n"/>
+      <c r="E98" s="73" t="n"/>
+      <c r="F98" s="74" t="n"/>
       <c r="G98" s="52" t="n"/>
-      <c r="H98" s="51" t="n"/>
+      <c r="H98" s="52" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="49" t="n"/>
-      <c r="B99" s="50" t="n"/>
-      <c r="C99" s="52" t="n"/>
-      <c r="D99" s="52" t="n"/>
-      <c r="E99" s="52" t="n"/>
-      <c r="F99" s="52" t="n"/>
+      <c r="A99" s="71" t="n"/>
+      <c r="B99" s="72" t="n"/>
+      <c r="C99" s="73" t="n"/>
+      <c r="D99" s="73" t="n"/>
+      <c r="E99" s="73" t="n"/>
+      <c r="F99" s="74" t="n"/>
       <c r="G99" s="52" t="n"/>
-      <c r="H99" s="51" t="n"/>
+      <c r="H99" s="52" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="49" t="n"/>
-      <c r="B100" s="50" t="n"/>
-      <c r="C100" s="52" t="n"/>
-      <c r="D100" s="52" t="n"/>
-      <c r="E100" s="52" t="n"/>
-      <c r="F100" s="52" t="n"/>
+      <c r="A100" s="71" t="n"/>
+      <c r="B100" s="72" t="n"/>
+      <c r="C100" s="73" t="n"/>
+      <c r="D100" s="73" t="n"/>
+      <c r="E100" s="73" t="n"/>
+      <c r="F100" s="74" t="n"/>
       <c r="G100" s="52" t="n"/>
-      <c r="H100" s="51" t="n"/>
+      <c r="H100" s="52" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="49" t="n"/>
-      <c r="B101" s="50" t="n"/>
-      <c r="C101" s="52" t="n"/>
-      <c r="D101" s="52" t="n"/>
-      <c r="E101" s="52" t="n"/>
-      <c r="F101" s="52" t="n"/>
+      <c r="A101" s="71" t="n"/>
+      <c r="B101" s="72" t="n"/>
+      <c r="C101" s="73" t="n"/>
+      <c r="D101" s="73" t="n"/>
+      <c r="E101" s="73" t="n"/>
+      <c r="F101" s="74" t="n"/>
       <c r="G101" s="52" t="n"/>
-      <c r="H101" s="51" t="n"/>
+      <c r="H101" s="52" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="49" t="n"/>
-      <c r="B102" s="50" t="n"/>
-      <c r="C102" s="52" t="n"/>
-      <c r="D102" s="52" t="n"/>
-      <c r="E102" s="52" t="n"/>
-      <c r="F102" s="52" t="n"/>
+      <c r="A102" s="71" t="n"/>
+      <c r="B102" s="72" t="n"/>
+      <c r="C102" s="73" t="n"/>
+      <c r="D102" s="73" t="n"/>
+      <c r="E102" s="73" t="n"/>
+      <c r="F102" s="74" t="n"/>
       <c r="G102" s="52" t="n"/>
-      <c r="H102" s="51" t="n"/>
+      <c r="H102" s="52" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="BB24"/>
   <dataValidations count="6">
     <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Data tidak valid" error="Kosongkan untuk siswa baru. Pertahankan ID untuk mengedit siswa." promptTitle="ID siswa" prompt="Kosongkan untuk siswa baru. Pertahankan ID untuk mengedit siswa." type="custom" errorStyle="stop" operator="between">
       <formula1>OR(A2="",AND(ISNUMBER(A2),A2=INT(A2),A2&gt;=1,COUNTIF($A$2:$A$1048576,A2)=1))</formula1>
@@ -2461,7 +2521,7 @@
       <formula1>1</formula1>
       <formula2>255</formula2>
     </dataValidation>
-    <dataValidation sqref="H2:H1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Data tidak valid" error="Isi ID kelas yang sudah ada, atau kosongkan jika belum memiliki kelas." promptTitle="ID kelas" prompt="Isi ID kelas yang sudah ada, atau kosongkan jika belum memiliki kelas." type="whole" errorStyle="stop" operator="greaterThanOrEqual">
+    <dataValidation sqref="F2:F1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Data tidak valid" error="Isi ID kelas yang sudah ada, atau kosongkan jika belum memiliki kelas." promptTitle="ID kelas" prompt="Isi ID kelas yang sudah ada, atau kosongkan jika belum memiliki kelas." type="whole" errorStyle="stop" operator="greaterThanOrEqual">
       <formula1>1</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -2521,510 +2581,511 @@
     </row>
     <row r="2" ht="24" customFormat="1" customHeight="1" s="21">
       <c r="A2" s="59" t="n"/>
-      <c r="B2" s="60" t="n"/>
-      <c r="C2" s="61" t="n"/>
+      <c r="B2" s="75" t="n"/>
+      <c r="C2" s="76" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="59" t="n"/>
-      <c r="B3" s="60" t="n"/>
-      <c r="C3" s="61" t="n"/>
+      <c r="B3" s="75" t="n"/>
+      <c r="C3" s="76" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="59" t="n"/>
-      <c r="B4" s="60" t="n"/>
-      <c r="C4" s="61" t="n"/>
+      <c r="B4" s="75" t="n"/>
+      <c r="C4" s="76" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="59" t="n"/>
-      <c r="B5" s="60" t="n"/>
-      <c r="C5" s="61" t="n"/>
+      <c r="B5" s="75" t="n"/>
+      <c r="C5" s="76" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="59" t="n"/>
-      <c r="B6" s="60" t="n"/>
-      <c r="C6" s="61" t="n"/>
+      <c r="B6" s="75" t="n"/>
+      <c r="C6" s="76" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="59" t="n"/>
-      <c r="B7" s="60" t="n"/>
-      <c r="C7" s="61" t="n"/>
+      <c r="B7" s="75" t="n"/>
+      <c r="C7" s="76" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="59" t="n"/>
-      <c r="B8" s="60" t="n"/>
-      <c r="C8" s="61" t="n"/>
+      <c r="B8" s="75" t="n"/>
+      <c r="C8" s="76" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="59" t="n"/>
-      <c r="B9" s="60" t="n"/>
-      <c r="C9" s="61" t="n"/>
+      <c r="B9" s="75" t="n"/>
+      <c r="C9" s="76" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="59" t="n"/>
-      <c r="B10" s="60" t="n"/>
-      <c r="C10" s="61" t="n"/>
+      <c r="B10" s="75" t="n"/>
+      <c r="C10" s="76" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="59" t="n"/>
-      <c r="B11" s="60" t="n"/>
-      <c r="C11" s="61" t="n"/>
+      <c r="B11" s="75" t="n"/>
+      <c r="C11" s="76" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="59" t="n"/>
-      <c r="B12" s="60" t="n"/>
-      <c r="C12" s="61" t="n"/>
+      <c r="B12" s="75" t="n"/>
+      <c r="C12" s="76" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="59" t="n"/>
-      <c r="B13" s="60" t="n"/>
-      <c r="C13" s="61" t="n"/>
+      <c r="B13" s="75" t="n"/>
+      <c r="C13" s="76" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="59" t="n"/>
-      <c r="B14" s="60" t="n"/>
-      <c r="C14" s="61" t="n"/>
+      <c r="B14" s="75" t="n"/>
+      <c r="C14" s="76" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="59" t="n"/>
-      <c r="B15" s="60" t="n"/>
-      <c r="C15" s="61" t="n"/>
+      <c r="B15" s="75" t="n"/>
+      <c r="C15" s="76" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="59" t="n"/>
-      <c r="B16" s="60" t="n"/>
-      <c r="C16" s="61" t="n"/>
+      <c r="B16" s="75" t="n"/>
+      <c r="C16" s="76" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="59" t="n"/>
-      <c r="B17" s="60" t="n"/>
-      <c r="C17" s="61" t="n"/>
+      <c r="B17" s="75" t="n"/>
+      <c r="C17" s="76" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="59" t="n"/>
-      <c r="B18" s="60" t="n"/>
-      <c r="C18" s="61" t="n"/>
+      <c r="B18" s="75" t="n"/>
+      <c r="C18" s="76" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="59" t="n"/>
-      <c r="B19" s="60" t="n"/>
-      <c r="C19" s="61" t="n"/>
+      <c r="B19" s="75" t="n"/>
+      <c r="C19" s="76" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="59" t="n"/>
-      <c r="B20" s="60" t="n"/>
-      <c r="C20" s="61" t="n"/>
+      <c r="B20" s="75" t="n"/>
+      <c r="C20" s="76" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="59" t="n"/>
-      <c r="B21" s="60" t="n"/>
-      <c r="C21" s="61" t="n"/>
+      <c r="B21" s="75" t="n"/>
+      <c r="C21" s="76" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="59" t="n"/>
-      <c r="B22" s="60" t="n"/>
-      <c r="C22" s="61" t="n"/>
+      <c r="B22" s="75" t="n"/>
+      <c r="C22" s="76" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="59" t="n"/>
-      <c r="B23" s="60" t="n"/>
-      <c r="C23" s="61" t="n"/>
+      <c r="B23" s="75" t="n"/>
+      <c r="C23" s="76" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="59" t="n"/>
-      <c r="B24" s="60" t="n"/>
-      <c r="C24" s="61" t="n"/>
+      <c r="B24" s="75" t="n"/>
+      <c r="C24" s="76" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="59" t="n"/>
-      <c r="B25" s="60" t="n"/>
-      <c r="C25" s="61" t="n"/>
+      <c r="B25" s="75" t="n"/>
+      <c r="C25" s="76" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="59" t="n"/>
-      <c r="B26" s="60" t="n"/>
-      <c r="C26" s="61" t="n"/>
+      <c r="B26" s="75" t="n"/>
+      <c r="C26" s="76" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="59" t="n"/>
-      <c r="B27" s="60" t="n"/>
-      <c r="C27" s="61" t="n"/>
+      <c r="B27" s="75" t="n"/>
+      <c r="C27" s="76" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="59" t="n"/>
-      <c r="B28" s="60" t="n"/>
-      <c r="C28" s="61" t="n"/>
+      <c r="B28" s="75" t="n"/>
+      <c r="C28" s="76" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="59" t="n"/>
-      <c r="B29" s="60" t="n"/>
-      <c r="C29" s="61" t="n"/>
+      <c r="B29" s="75" t="n"/>
+      <c r="C29" s="76" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="59" t="n"/>
-      <c r="B30" s="60" t="n"/>
-      <c r="C30" s="61" t="n"/>
+      <c r="B30" s="75" t="n"/>
+      <c r="C30" s="76" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="59" t="n"/>
-      <c r="B31" s="60" t="n"/>
-      <c r="C31" s="61" t="n"/>
+      <c r="B31" s="75" t="n"/>
+      <c r="C31" s="76" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="59" t="n"/>
-      <c r="B32" s="60" t="n"/>
-      <c r="C32" s="61" t="n"/>
+      <c r="B32" s="75" t="n"/>
+      <c r="C32" s="76" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="59" t="n"/>
-      <c r="B33" s="60" t="n"/>
-      <c r="C33" s="61" t="n"/>
+      <c r="B33" s="75" t="n"/>
+      <c r="C33" s="76" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="59" t="n"/>
-      <c r="B34" s="60" t="n"/>
-      <c r="C34" s="61" t="n"/>
+      <c r="B34" s="75" t="n"/>
+      <c r="C34" s="76" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="59" t="n"/>
-      <c r="B35" s="60" t="n"/>
-      <c r="C35" s="61" t="n"/>
+      <c r="B35" s="75" t="n"/>
+      <c r="C35" s="76" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="59" t="n"/>
-      <c r="B36" s="60" t="n"/>
-      <c r="C36" s="61" t="n"/>
+      <c r="B36" s="75" t="n"/>
+      <c r="C36" s="76" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="59" t="n"/>
-      <c r="B37" s="60" t="n"/>
-      <c r="C37" s="61" t="n"/>
+      <c r="B37" s="75" t="n"/>
+      <c r="C37" s="76" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="59" t="n"/>
-      <c r="B38" s="60" t="n"/>
-      <c r="C38" s="61" t="n"/>
+      <c r="B38" s="75" t="n"/>
+      <c r="C38" s="76" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="59" t="n"/>
-      <c r="B39" s="60" t="n"/>
-      <c r="C39" s="61" t="n"/>
+      <c r="B39" s="75" t="n"/>
+      <c r="C39" s="76" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="59" t="n"/>
-      <c r="B40" s="60" t="n"/>
-      <c r="C40" s="61" t="n"/>
+      <c r="B40" s="75" t="n"/>
+      <c r="C40" s="76" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="59" t="n"/>
-      <c r="B41" s="60" t="n"/>
-      <c r="C41" s="61" t="n"/>
+      <c r="B41" s="75" t="n"/>
+      <c r="C41" s="76" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="59" t="n"/>
-      <c r="B42" s="60" t="n"/>
-      <c r="C42" s="61" t="n"/>
+      <c r="B42" s="75" t="n"/>
+      <c r="C42" s="76" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="59" t="n"/>
-      <c r="B43" s="60" t="n"/>
-      <c r="C43" s="61" t="n"/>
+      <c r="B43" s="75" t="n"/>
+      <c r="C43" s="76" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="59" t="n"/>
-      <c r="B44" s="60" t="n"/>
-      <c r="C44" s="61" t="n"/>
+      <c r="B44" s="75" t="n"/>
+      <c r="C44" s="76" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="59" t="n"/>
-      <c r="B45" s="60" t="n"/>
-      <c r="C45" s="61" t="n"/>
+      <c r="B45" s="75" t="n"/>
+      <c r="C45" s="76" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="59" t="n"/>
-      <c r="B46" s="60" t="n"/>
-      <c r="C46" s="61" t="n"/>
+      <c r="B46" s="75" t="n"/>
+      <c r="C46" s="76" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="59" t="n"/>
-      <c r="B47" s="60" t="n"/>
-      <c r="C47" s="61" t="n"/>
+      <c r="B47" s="75" t="n"/>
+      <c r="C47" s="76" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="59" t="n"/>
-      <c r="B48" s="60" t="n"/>
-      <c r="C48" s="61" t="n"/>
+      <c r="B48" s="75" t="n"/>
+      <c r="C48" s="76" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="59" t="n"/>
-      <c r="B49" s="60" t="n"/>
-      <c r="C49" s="61" t="n"/>
+      <c r="B49" s="75" t="n"/>
+      <c r="C49" s="76" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="59" t="n"/>
-      <c r="B50" s="60" t="n"/>
-      <c r="C50" s="61" t="n"/>
+      <c r="B50" s="75" t="n"/>
+      <c r="C50" s="76" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="59" t="n"/>
-      <c r="B51" s="60" t="n"/>
-      <c r="C51" s="61" t="n"/>
+      <c r="B51" s="75" t="n"/>
+      <c r="C51" s="76" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="59" t="n"/>
-      <c r="B52" s="60" t="n"/>
-      <c r="C52" s="61" t="n"/>
+      <c r="B52" s="75" t="n"/>
+      <c r="C52" s="76" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="59" t="n"/>
-      <c r="B53" s="60" t="n"/>
-      <c r="C53" s="61" t="n"/>
+      <c r="B53" s="75" t="n"/>
+      <c r="C53" s="76" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="59" t="n"/>
-      <c r="B54" s="60" t="n"/>
-      <c r="C54" s="61" t="n"/>
+      <c r="B54" s="75" t="n"/>
+      <c r="C54" s="76" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="59" t="n"/>
-      <c r="B55" s="60" t="n"/>
-      <c r="C55" s="61" t="n"/>
+      <c r="B55" s="75" t="n"/>
+      <c r="C55" s="76" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="59" t="n"/>
-      <c r="B56" s="60" t="n"/>
-      <c r="C56" s="61" t="n"/>
+      <c r="B56" s="75" t="n"/>
+      <c r="C56" s="76" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="59" t="n"/>
-      <c r="B57" s="60" t="n"/>
-      <c r="C57" s="61" t="n"/>
+      <c r="B57" s="75" t="n"/>
+      <c r="C57" s="76" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="59" t="n"/>
-      <c r="B58" s="60" t="n"/>
-      <c r="C58" s="61" t="n"/>
+      <c r="B58" s="75" t="n"/>
+      <c r="C58" s="76" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="59" t="n"/>
-      <c r="B59" s="60" t="n"/>
-      <c r="C59" s="61" t="n"/>
+      <c r="B59" s="75" t="n"/>
+      <c r="C59" s="76" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="59" t="n"/>
-      <c r="B60" s="60" t="n"/>
-      <c r="C60" s="61" t="n"/>
+      <c r="B60" s="75" t="n"/>
+      <c r="C60" s="76" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="59" t="n"/>
-      <c r="B61" s="60" t="n"/>
-      <c r="C61" s="61" t="n"/>
+      <c r="B61" s="75" t="n"/>
+      <c r="C61" s="76" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="59" t="n"/>
-      <c r="B62" s="60" t="n"/>
-      <c r="C62" s="61" t="n"/>
+      <c r="B62" s="75" t="n"/>
+      <c r="C62" s="76" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="59" t="n"/>
-      <c r="B63" s="60" t="n"/>
-      <c r="C63" s="61" t="n"/>
+      <c r="B63" s="75" t="n"/>
+      <c r="C63" s="76" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="59" t="n"/>
-      <c r="B64" s="60" t="n"/>
-      <c r="C64" s="61" t="n"/>
+      <c r="B64" s="75" t="n"/>
+      <c r="C64" s="76" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="59" t="n"/>
-      <c r="B65" s="60" t="n"/>
-      <c r="C65" s="61" t="n"/>
+      <c r="B65" s="75" t="n"/>
+      <c r="C65" s="76" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="59" t="n"/>
-      <c r="B66" s="60" t="n"/>
-      <c r="C66" s="61" t="n"/>
+      <c r="B66" s="75" t="n"/>
+      <c r="C66" s="76" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="59" t="n"/>
-      <c r="B67" s="60" t="n"/>
-      <c r="C67" s="61" t="n"/>
+      <c r="B67" s="75" t="n"/>
+      <c r="C67" s="76" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="59" t="n"/>
-      <c r="B68" s="60" t="n"/>
-      <c r="C68" s="61" t="n"/>
+      <c r="B68" s="75" t="n"/>
+      <c r="C68" s="76" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="59" t="n"/>
-      <c r="B69" s="60" t="n"/>
-      <c r="C69" s="61" t="n"/>
+      <c r="B69" s="75" t="n"/>
+      <c r="C69" s="76" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="59" t="n"/>
-      <c r="B70" s="60" t="n"/>
-      <c r="C70" s="61" t="n"/>
+      <c r="B70" s="75" t="n"/>
+      <c r="C70" s="76" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="59" t="n"/>
-      <c r="B71" s="60" t="n"/>
-      <c r="C71" s="61" t="n"/>
+      <c r="B71" s="75" t="n"/>
+      <c r="C71" s="76" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="59" t="n"/>
-      <c r="B72" s="60" t="n"/>
-      <c r="C72" s="61" t="n"/>
+      <c r="B72" s="75" t="n"/>
+      <c r="C72" s="76" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="59" t="n"/>
-      <c r="B73" s="60" t="n"/>
-      <c r="C73" s="61" t="n"/>
+      <c r="B73" s="75" t="n"/>
+      <c r="C73" s="76" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="59" t="n"/>
-      <c r="B74" s="60" t="n"/>
-      <c r="C74" s="61" t="n"/>
+      <c r="B74" s="75" t="n"/>
+      <c r="C74" s="76" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="59" t="n"/>
-      <c r="B75" s="60" t="n"/>
-      <c r="C75" s="61" t="n"/>
+      <c r="B75" s="75" t="n"/>
+      <c r="C75" s="76" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="59" t="n"/>
-      <c r="B76" s="60" t="n"/>
-      <c r="C76" s="61" t="n"/>
+      <c r="B76" s="75" t="n"/>
+      <c r="C76" s="76" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="59" t="n"/>
-      <c r="B77" s="60" t="n"/>
-      <c r="C77" s="61" t="n"/>
+      <c r="B77" s="75" t="n"/>
+      <c r="C77" s="76" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="59" t="n"/>
-      <c r="B78" s="60" t="n"/>
-      <c r="C78" s="61" t="n"/>
+      <c r="B78" s="75" t="n"/>
+      <c r="C78" s="76" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="59" t="n"/>
-      <c r="B79" s="60" t="n"/>
-      <c r="C79" s="61" t="n"/>
+      <c r="B79" s="75" t="n"/>
+      <c r="C79" s="76" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="59" t="n"/>
-      <c r="B80" s="60" t="n"/>
-      <c r="C80" s="61" t="n"/>
+      <c r="B80" s="75" t="n"/>
+      <c r="C80" s="76" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="59" t="n"/>
-      <c r="B81" s="60" t="n"/>
-      <c r="C81" s="61" t="n"/>
+      <c r="B81" s="75" t="n"/>
+      <c r="C81" s="76" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="59" t="n"/>
-      <c r="B82" s="60" t="n"/>
-      <c r="C82" s="61" t="n"/>
+      <c r="B82" s="75" t="n"/>
+      <c r="C82" s="76" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="59" t="n"/>
-      <c r="B83" s="60" t="n"/>
-      <c r="C83" s="61" t="n"/>
+      <c r="B83" s="75" t="n"/>
+      <c r="C83" s="76" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="59" t="n"/>
-      <c r="B84" s="60" t="n"/>
-      <c r="C84" s="61" t="n"/>
+      <c r="B84" s="75" t="n"/>
+      <c r="C84" s="76" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="59" t="n"/>
-      <c r="B85" s="60" t="n"/>
-      <c r="C85" s="61" t="n"/>
+      <c r="B85" s="75" t="n"/>
+      <c r="C85" s="76" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="59" t="n"/>
-      <c r="B86" s="60" t="n"/>
-      <c r="C86" s="61" t="n"/>
+      <c r="B86" s="75" t="n"/>
+      <c r="C86" s="76" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="59" t="n"/>
-      <c r="B87" s="60" t="n"/>
-      <c r="C87" s="61" t="n"/>
+      <c r="B87" s="75" t="n"/>
+      <c r="C87" s="76" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="59" t="n"/>
-      <c r="B88" s="60" t="n"/>
-      <c r="C88" s="61" t="n"/>
+      <c r="B88" s="75" t="n"/>
+      <c r="C88" s="76" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="59" t="n"/>
-      <c r="B89" s="60" t="n"/>
-      <c r="C89" s="61" t="n"/>
+      <c r="B89" s="75" t="n"/>
+      <c r="C89" s="76" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="59" t="n"/>
-      <c r="B90" s="60" t="n"/>
-      <c r="C90" s="61" t="n"/>
+      <c r="B90" s="75" t="n"/>
+      <c r="C90" s="76" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="59" t="n"/>
-      <c r="B91" s="60" t="n"/>
-      <c r="C91" s="61" t="n"/>
+      <c r="B91" s="75" t="n"/>
+      <c r="C91" s="76" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="59" t="n"/>
-      <c r="B92" s="60" t="n"/>
-      <c r="C92" s="61" t="n"/>
+      <c r="B92" s="75" t="n"/>
+      <c r="C92" s="76" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="59" t="n"/>
-      <c r="B93" s="60" t="n"/>
-      <c r="C93" s="61" t="n"/>
+      <c r="B93" s="75" t="n"/>
+      <c r="C93" s="76" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="59" t="n"/>
-      <c r="B94" s="60" t="n"/>
-      <c r="C94" s="61" t="n"/>
+      <c r="B94" s="75" t="n"/>
+      <c r="C94" s="76" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="59" t="n"/>
-      <c r="B95" s="60" t="n"/>
-      <c r="C95" s="61" t="n"/>
+      <c r="B95" s="75" t="n"/>
+      <c r="C95" s="76" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="59" t="n"/>
-      <c r="B96" s="60" t="n"/>
-      <c r="C96" s="61" t="n"/>
+      <c r="B96" s="75" t="n"/>
+      <c r="C96" s="76" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="59" t="n"/>
-      <c r="B97" s="60" t="n"/>
-      <c r="C97" s="61" t="n"/>
+      <c r="B97" s="75" t="n"/>
+      <c r="C97" s="76" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="59" t="n"/>
-      <c r="B98" s="60" t="n"/>
-      <c r="C98" s="61" t="n"/>
+      <c r="B98" s="75" t="n"/>
+      <c r="C98" s="76" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="59" t="n"/>
-      <c r="B99" s="60" t="n"/>
-      <c r="C99" s="61" t="n"/>
+      <c r="B99" s="75" t="n"/>
+      <c r="C99" s="76" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="59" t="n"/>
-      <c r="B100" s="60" t="n"/>
-      <c r="C100" s="61" t="n"/>
+      <c r="B100" s="75" t="n"/>
+      <c r="C100" s="76" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="59" t="n"/>
-      <c r="B101" s="60" t="n"/>
-      <c r="C101" s="61" t="n"/>
+      <c r="B101" s="75" t="n"/>
+      <c r="C101" s="76" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="59" t="n"/>
-      <c r="B102" s="60" t="n"/>
-      <c r="C102" s="61" t="n"/>
+      <c r="B102" s="75" t="n"/>
+      <c r="C102" s="76" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="D2D4"/>
   <dataValidations count="3">
     <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Data tidak valid" error="Kosongkan untuk kelas baru. Pertahankan ID untuk mengedit kelas." promptTitle="ID kelas" prompt="Kosongkan untuk kelas baru. Pertahankan ID untuk mengedit kelas." type="custom" errorStyle="stop" operator="between">
       <formula1>OR(A2="",AND(ISNUMBER(A2),A2=INT(A2),A2&gt;=1,COUNTIF($A$2:$A$1048576,A2)=1))</formula1>

--- a/web/app/spreadsheet_templates/students_export_template.xlsx
+++ b/web/app/spreadsheet_templates/students_export_template.xlsx
@@ -1036,7 +1036,7 @@
       <c r="A4" s="23" t="n"/>
       <c r="B4" s="66" t="inlineStr">
         <is>
-          <t>Dokumentasi lengkap: https://example.com</t>
+          <t>Panduan impor dan ekspor data (klik untuk membuka)</t>
         </is>
       </c>
       <c r="C4" s="28" t="n"/>
@@ -1430,7 +1430,7 @@
     <mergeCell ref="B28:H28"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" tooltip="Buka panduan impor dan ekspor Absensa" r:id="rId1"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
